--- a/data/AU.xlsx
+++ b/data/AU.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -45,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,23 +50,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -446,27 +434,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -25129,21 +25117,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Australia WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Coverage: 2022-05-25 to 2026-03-22 | Publication days: 470</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -25151,22 +25139,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/AU.xlsx
+++ b/data/AU.xlsx
@@ -25068,7 +25068,9 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="B1398" t="inlineStr"/>
+      <c r="B1398" t="n">
+        <v>0</v>
+      </c>
       <c r="C1398" t="n">
         <v>0</v>
       </c>
@@ -25076,7 +25078,7 @@
         <v>0.2</v>
       </c>
       <c r="E1398" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1399">
@@ -25126,7 +25128,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-05-25 to 2026-03-22 | Publication days: 470</t>
+          <t>Coverage: 2022-05-25 to 2026-03-22 | Publication days: 471</t>
         </is>
       </c>
     </row>

--- a/data/AU.xlsx
+++ b/data/AU.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1399"/>
+  <dimension ref="A1:E1400"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -25095,6 +25095,23 @@
         <v>0.1333333333333333</v>
       </c>
       <c r="E1399" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="A1400" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B1400" t="inlineStr"/>
+      <c r="C1400" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1400" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="E1400" t="b">
         <v>0</v>
       </c>
     </row>
@@ -25128,7 +25145,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-05-25 to 2026-03-22 | Publication days: 471</t>
+          <t>Coverage: 2022-05-25 to 2026-03-23 | Publication days: 471</t>
         </is>
       </c>
     </row>

--- a/data/AU.xlsx
+++ b/data/AU.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1400"/>
+  <dimension ref="A1:E1401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -25112,6 +25112,23 @@
         <v>0.06666666666666667</v>
       </c>
       <c r="E1400" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B1401" t="inlineStr"/>
+      <c r="C1401" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1401" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1401" t="b">
         <v>0</v>
       </c>
     </row>
@@ -25145,7 +25162,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-05-25 to 2026-03-23 | Publication days: 471</t>
+          <t>Coverage: 2022-05-25 to 2026-03-24 | Publication days: 471</t>
         </is>
       </c>
     </row>

--- a/data/AU.xlsx
+++ b/data/AU.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1401"/>
+  <dimension ref="A1:E1402"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -25129,6 +25129,23 @@
         <v>0</v>
       </c>
       <c r="E1401" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B1402" t="inlineStr"/>
+      <c r="C1402" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1402" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1402" t="b">
         <v>0</v>
       </c>
     </row>
@@ -25162,7 +25179,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-05-25 to 2026-03-24 | Publication days: 471</t>
+          <t>Coverage: 2022-05-25 to 2026-03-25 | Publication days: 471</t>
         </is>
       </c>
     </row>

--- a/data/AU.xlsx
+++ b/data/AU.xlsx
@@ -25121,7 +25121,9 @@
           <t>2026-03-24</t>
         </is>
       </c>
-      <c r="B1401" t="inlineStr"/>
+      <c r="B1401" t="n">
+        <v>0</v>
+      </c>
       <c r="C1401" t="n">
         <v>0</v>
       </c>
@@ -25129,7 +25131,7 @@
         <v>0</v>
       </c>
       <c r="E1401" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1402">
@@ -25179,7 +25181,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-05-25 to 2026-03-25 | Publication days: 471</t>
+          <t>Coverage: 2022-05-25 to 2026-03-25 | Publication days: 472</t>
         </is>
       </c>
     </row>

--- a/data/AU.xlsx
+++ b/data/AU.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -42,7 +45,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -50,14 +53,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,27 +446,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -25172,21 +25184,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Australia WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Coverage: 2022-05-25 to 2026-03-25 | Publication days: 472</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -25194,22 +25206,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/AU.xlsx
+++ b/data/AU.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -45,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,23 +50,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1402"/>
+  <dimension ref="A1:E1403"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -446,27 +434,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -25160,6 +25148,23 @@
         <v>0</v>
       </c>
       <c r="E1402" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B1403" t="inlineStr"/>
+      <c r="C1403" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1403" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1403" t="b">
         <v>0</v>
       </c>
     </row>
@@ -25184,21 +25189,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Australia WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Coverage: 2022-05-25 to 2026-03-25 | Publication days: 472</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Coverage: 2022-05-25 to 2026-03-26 | Publication days: 472</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -25206,22 +25211,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/AU.xlsx
+++ b/data/AU.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -42,7 +45,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -50,14 +53,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,27 +446,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -25189,21 +25201,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Australia WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Coverage: 2022-05-25 to 2026-03-26 | Publication days: 472</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -25211,22 +25223,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/AU.xlsx
+++ b/data/AU.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -45,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,23 +50,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -446,27 +434,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -25201,21 +25189,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Australia WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Coverage: 2022-05-25 to 2026-03-26 | Publication days: 472</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -25223,22 +25211,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/AU.xlsx
+++ b/data/AU.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -45,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,23 +50,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1403"/>
+  <dimension ref="A1:E1404"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -446,27 +434,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -25177,6 +25165,23 @@
         <v>0</v>
       </c>
       <c r="E1403" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="A1404" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B1404" t="inlineStr"/>
+      <c r="C1404" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1404" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1404" t="b">
         <v>0</v>
       </c>
     </row>
@@ -25201,21 +25206,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Australia WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Coverage: 2022-05-25 to 2026-03-26 | Publication days: 472</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Coverage: 2022-05-25 to 2026-03-27 | Publication days: 472</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -25223,22 +25228,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/AU.xlsx
+++ b/data/AU.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1404"/>
+  <dimension ref="A1:E1405"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21899,13 +21899,13 @@
         </is>
       </c>
       <c r="B1218" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C1218" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D1218" t="n">
-        <v>-0.2</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1218" t="b">
         <v>1</v>
@@ -21919,10 +21919,10 @@
       </c>
       <c r="B1219" t="inlineStr"/>
       <c r="C1219" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D1219" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.2</v>
       </c>
       <c r="E1219" t="b">
         <v>0</v>
@@ -21936,10 +21936,10 @@
       </c>
       <c r="B1220" t="inlineStr"/>
       <c r="C1220" t="n">
-        <v>1</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D1220" t="n">
-        <v>0.06666666666666667</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1220" t="b">
         <v>0</v>
@@ -21953,10 +21953,10 @@
       </c>
       <c r="B1221" t="inlineStr"/>
       <c r="C1221" t="n">
-        <v>1.571428571428571</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D1221" t="n">
-        <v>0.2333333333333333</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E1221" t="b">
         <v>0</v>
@@ -21970,10 +21970,10 @@
       </c>
       <c r="B1222" t="inlineStr"/>
       <c r="C1222" t="n">
-        <v>1.857142857142857</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D1222" t="n">
-        <v>0.3</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E1222" t="b">
         <v>0</v>
@@ -21989,10 +21989,10 @@
         <v>2</v>
       </c>
       <c r="C1223" t="n">
-        <v>2.142857142857143</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D1223" t="n">
-        <v>0.3666666666666666</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1223" t="b">
         <v>1</v>
@@ -22006,10 +22006,10 @@
       </c>
       <c r="B1224" t="inlineStr"/>
       <c r="C1224" t="n">
-        <v>2</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D1224" t="n">
-        <v>0.4333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="E1224" t="b">
         <v>0</v>
@@ -22023,10 +22023,10 @@
       </c>
       <c r="B1225" t="inlineStr"/>
       <c r="C1225" t="n">
-        <v>2</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D1225" t="n">
-        <v>0.5</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E1225" t="b">
         <v>0</v>
@@ -22040,10 +22040,10 @@
       </c>
       <c r="B1226" t="inlineStr"/>
       <c r="C1226" t="n">
-        <v>2</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="D1226" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="E1226" t="b">
         <v>0</v>
@@ -22059,10 +22059,10 @@
         <v>0</v>
       </c>
       <c r="C1227" t="n">
-        <v>1.714285714285714</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="D1227" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="E1227" t="b">
         <v>1</v>
@@ -22076,10 +22076,10 @@
       </c>
       <c r="B1228" t="inlineStr"/>
       <c r="C1228" t="n">
-        <v>1.428571428571429</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="D1228" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="E1228" t="b">
         <v>0</v>
@@ -22096,7 +22096,7 @@
         <v>1.142857142857143</v>
       </c>
       <c r="D1229" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.3</v>
       </c>
       <c r="E1229" t="b">
         <v>0</v>
@@ -22113,7 +22113,7 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="D1230" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.3</v>
       </c>
       <c r="E1230" t="b">
         <v>0</v>
@@ -22130,7 +22130,7 @@
         <v>0.5714285714285714</v>
       </c>
       <c r="D1231" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.3</v>
       </c>
       <c r="E1231" t="b">
         <v>0</v>
@@ -22147,7 +22147,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1232" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.3</v>
       </c>
       <c r="E1232" t="b">
         <v>0</v>
@@ -22164,7 +22164,7 @@
         <v>0</v>
       </c>
       <c r="D1233" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.3</v>
       </c>
       <c r="E1233" t="b">
         <v>0</v>
@@ -22181,7 +22181,7 @@
         <v>0</v>
       </c>
       <c r="D1234" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.3</v>
       </c>
       <c r="E1234" t="b">
         <v>0</v>
@@ -22200,7 +22200,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1235" t="n">
-        <v>0.7</v>
+        <v>0.3666666666666666</v>
       </c>
       <c r="E1235" t="b">
         <v>1</v>
@@ -22217,7 +22217,7 @@
         <v>0.5714285714285714</v>
       </c>
       <c r="D1236" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="E1236" t="b">
         <v>0</v>
@@ -22234,7 +22234,7 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="D1237" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.5</v>
       </c>
       <c r="E1237" t="b">
         <v>0</v>
@@ -22251,7 +22251,7 @@
         <v>1.142857142857143</v>
       </c>
       <c r="D1238" t="n">
-        <v>0.9</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="E1238" t="b">
         <v>0</v>
@@ -22270,7 +22270,7 @@
         <v>1.142857142857143</v>
       </c>
       <c r="D1239" t="n">
-        <v>0.9</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="E1239" t="b">
         <v>1</v>
@@ -22289,7 +22289,7 @@
         <v>1.142857142857143</v>
       </c>
       <c r="D1240" t="n">
-        <v>0.9</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="E1240" t="b">
         <v>1</v>
@@ -22306,7 +22306,7 @@
         <v>1.142857142857143</v>
       </c>
       <c r="D1241" t="n">
-        <v>0.9</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="E1241" t="b">
         <v>0</v>
@@ -22325,7 +22325,7 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="D1242" t="n">
-        <v>0.9</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="E1242" t="b">
         <v>1</v>
@@ -22342,7 +22342,7 @@
         <v>0.5714285714285714</v>
       </c>
       <c r="D1243" t="n">
-        <v>0.9</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="E1243" t="b">
         <v>0</v>
@@ -22359,7 +22359,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1244" t="n">
-        <v>0.9666666666666667</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="E1244" t="b">
         <v>0</v>
@@ -22378,7 +22378,7 @@
         <v>0</v>
       </c>
       <c r="D1245" t="n">
-        <v>0.9666666666666667</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="E1245" t="b">
         <v>1</v>
@@ -22397,7 +22397,7 @@
         <v>0</v>
       </c>
       <c r="D1246" t="n">
-        <v>0.9666666666666667</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="E1246" t="b">
         <v>1</v>
@@ -22414,7 +22414,7 @@
         <v>0</v>
       </c>
       <c r="D1247" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="E1247" t="b">
         <v>0</v>
@@ -22431,7 +22431,7 @@
         <v>0</v>
       </c>
       <c r="D1248" t="n">
-        <v>0.8</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="E1248" t="b">
         <v>0</v>
@@ -22448,7 +22448,7 @@
         <v>0</v>
       </c>
       <c r="D1249" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="E1249" t="b">
         <v>0</v>
@@ -22465,7 +22465,7 @@
         <v>0</v>
       </c>
       <c r="D1250" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="E1250" t="b">
         <v>0</v>
@@ -22482,7 +22482,7 @@
         <v>0</v>
       </c>
       <c r="D1251" t="n">
-        <v>0.6</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="E1251" t="b">
         <v>0</v>
@@ -22758,13 +22758,13 @@
         </is>
       </c>
       <c r="B1267" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C1267" t="n">
-        <v>-2</v>
+        <v>-1.714285714285714</v>
       </c>
       <c r="D1267" t="n">
-        <v>-0.4</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1267" t="b">
         <v>1</v>
@@ -22778,10 +22778,10 @@
       </c>
       <c r="B1268" t="inlineStr"/>
       <c r="C1268" t="n">
-        <v>-2.285714285714286</v>
+        <v>-1.714285714285714</v>
       </c>
       <c r="D1268" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E1268" t="b">
         <v>0</v>
@@ -22797,10 +22797,10 @@
         <v>0</v>
       </c>
       <c r="C1269" t="n">
-        <v>-2.285714285714286</v>
+        <v>-1.714285714285714</v>
       </c>
       <c r="D1269" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E1269" t="b">
         <v>1</v>
@@ -22814,10 +22814,10 @@
       </c>
       <c r="B1270" t="inlineStr"/>
       <c r="C1270" t="n">
-        <v>-1.857142857142857</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D1270" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E1270" t="b">
         <v>0</v>
@@ -22831,10 +22831,10 @@
       </c>
       <c r="B1271" t="inlineStr"/>
       <c r="C1271" t="n">
-        <v>-1.428571428571429</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1271" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E1271" t="b">
         <v>0</v>
@@ -22848,10 +22848,10 @@
       </c>
       <c r="B1272" t="inlineStr"/>
       <c r="C1272" t="n">
-        <v>-1</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1272" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E1272" t="b">
         <v>0</v>
@@ -22865,10 +22865,10 @@
       </c>
       <c r="B1273" t="inlineStr"/>
       <c r="C1273" t="n">
-        <v>-0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D1273" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E1273" t="b">
         <v>0</v>
@@ -22882,10 +22882,10 @@
       </c>
       <c r="B1274" t="inlineStr"/>
       <c r="C1274" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1274" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E1274" t="b">
         <v>0</v>
@@ -22904,7 +22904,7 @@
         <v>0</v>
       </c>
       <c r="D1275" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E1275" t="b">
         <v>1</v>
@@ -22923,7 +22923,7 @@
         <v>0</v>
       </c>
       <c r="D1276" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E1276" t="b">
         <v>1</v>
@@ -22942,7 +22942,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1277" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="E1277" t="b">
         <v>1</v>
@@ -22959,7 +22959,7 @@
         <v>-0.8571428571428571</v>
       </c>
       <c r="D1278" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.6</v>
       </c>
       <c r="E1278" t="b">
         <v>0</v>
@@ -22978,7 +22978,7 @@
         <v>-0.8571428571428571</v>
       </c>
       <c r="D1279" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.6</v>
       </c>
       <c r="E1279" t="b">
         <v>1</v>
@@ -22997,7 +22997,7 @@
         <v>-0.8571428571428571</v>
       </c>
       <c r="D1280" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.6</v>
       </c>
       <c r="E1280" t="b">
         <v>1</v>
@@ -23014,7 +23014,7 @@
         <v>-0.8571428571428571</v>
       </c>
       <c r="D1281" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.6</v>
       </c>
       <c r="E1281" t="b">
         <v>0</v>
@@ -23033,7 +23033,7 @@
         <v>-0.8571428571428571</v>
       </c>
       <c r="D1282" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.6</v>
       </c>
       <c r="E1282" t="b">
         <v>1</v>
@@ -23050,7 +23050,7 @@
         <v>-0.8571428571428571</v>
       </c>
       <c r="D1283" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.6</v>
       </c>
       <c r="E1283" t="b">
         <v>0</v>
@@ -23069,7 +23069,7 @@
         <v>-0.8571428571428571</v>
       </c>
       <c r="D1284" t="n">
-        <v>-0.8333333333333334</v>
+        <v>-0.7</v>
       </c>
       <c r="E1284" t="b">
         <v>1</v>
@@ -23088,7 +23088,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1285" t="n">
-        <v>-0.8333333333333334</v>
+        <v>-0.7</v>
       </c>
       <c r="E1285" t="b">
         <v>1</v>
@@ -23105,7 +23105,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1286" t="n">
-        <v>-0.8333333333333334</v>
+        <v>-0.7</v>
       </c>
       <c r="E1286" t="b">
         <v>0</v>
@@ -23124,7 +23124,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1287" t="n">
-        <v>-0.8333333333333334</v>
+        <v>-0.7</v>
       </c>
       <c r="E1287" t="b">
         <v>1</v>
@@ -23141,7 +23141,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1288" t="n">
-        <v>-0.8333333333333334</v>
+        <v>-0.7</v>
       </c>
       <c r="E1288" t="b">
         <v>0</v>
@@ -23158,7 +23158,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1289" t="n">
-        <v>-0.8333333333333334</v>
+        <v>-0.7</v>
       </c>
       <c r="E1289" t="b">
         <v>0</v>
@@ -23177,7 +23177,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1290" t="n">
-        <v>-0.8333333333333334</v>
+        <v>-0.7</v>
       </c>
       <c r="E1290" t="b">
         <v>1</v>
@@ -23196,7 +23196,7 @@
         <v>0</v>
       </c>
       <c r="D1291" t="n">
-        <v>-0.8333333333333334</v>
+        <v>-0.7</v>
       </c>
       <c r="E1291" t="b">
         <v>1</v>
@@ -23213,7 +23213,7 @@
         <v>0</v>
       </c>
       <c r="D1292" t="n">
-        <v>-0.8333333333333334</v>
+        <v>-0.7</v>
       </c>
       <c r="E1292" t="b">
         <v>0</v>
@@ -23232,7 +23232,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1293" t="n">
-        <v>-0.8333333333333334</v>
+        <v>-0.7</v>
       </c>
       <c r="E1293" t="b">
         <v>1</v>
@@ -23251,7 +23251,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1294" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.6</v>
       </c>
       <c r="E1294" t="b">
         <v>1</v>
@@ -23268,7 +23268,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1295" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="E1295" t="b">
         <v>0</v>
@@ -23287,7 +23287,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1296" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E1296" t="b">
         <v>1</v>
@@ -23306,7 +23306,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1297" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.4</v>
       </c>
       <c r="E1297" t="b">
         <v>1</v>
@@ -25069,13 +25069,13 @@
         </is>
       </c>
       <c r="B1398" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C1398" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1398" t="n">
-        <v>0.2</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1398" t="b">
         <v>1</v>
@@ -25089,10 +25089,10 @@
       </c>
       <c r="B1399" t="inlineStr"/>
       <c r="C1399" t="n">
-        <v>0</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1399" t="n">
-        <v>0.1333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E1399" t="b">
         <v>0</v>
@@ -25106,10 +25106,10 @@
       </c>
       <c r="B1400" t="inlineStr"/>
       <c r="C1400" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1400" t="n">
-        <v>0.06666666666666667</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1400" t="b">
         <v>0</v>
@@ -25125,10 +25125,10 @@
         <v>0</v>
       </c>
       <c r="C1401" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1401" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="E1401" t="b">
         <v>1</v>
@@ -25142,10 +25142,10 @@
       </c>
       <c r="B1402" t="inlineStr"/>
       <c r="C1402" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1402" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="E1402" t="b">
         <v>0</v>
@@ -25159,10 +25159,10 @@
       </c>
       <c r="B1403" t="inlineStr"/>
       <c r="C1403" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1403" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="E1403" t="b">
         <v>0</v>
@@ -25176,12 +25176,29 @@
       </c>
       <c r="B1404" t="inlineStr"/>
       <c r="C1404" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1404" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="E1404" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B1405" t="inlineStr"/>
+      <c r="C1405" t="n">
+        <v>-0.5714285714285714</v>
+      </c>
+      <c r="D1405" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E1405" t="b">
         <v>0</v>
       </c>
     </row>
@@ -25215,7 +25232,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-05-25 to 2026-03-27 | Publication days: 472</t>
+          <t>Coverage: 2022-05-25 to 2026-03-28 | Publication days: 472</t>
         </is>
       </c>
     </row>

--- a/data/AU.xlsx
+++ b/data/AU.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1405"/>
+  <dimension ref="A1:E1406"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21899,13 +21899,13 @@
         </is>
       </c>
       <c r="B1218" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C1218" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D1218" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.2</v>
       </c>
       <c r="E1218" t="b">
         <v>1</v>
@@ -21919,10 +21919,10 @@
       </c>
       <c r="B1219" t="inlineStr"/>
       <c r="C1219" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D1219" t="n">
-        <v>-0.2</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1219" t="b">
         <v>0</v>
@@ -21936,10 +21936,10 @@
       </c>
       <c r="B1220" t="inlineStr"/>
       <c r="C1220" t="n">
-        <v>0.1428571428571428</v>
+        <v>1</v>
       </c>
       <c r="D1220" t="n">
-        <v>-0.1333333333333333</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1220" t="b">
         <v>0</v>
@@ -21953,10 +21953,10 @@
       </c>
       <c r="B1221" t="inlineStr"/>
       <c r="C1221" t="n">
-        <v>0.4285714285714285</v>
+        <v>1.571428571428571</v>
       </c>
       <c r="D1221" t="n">
-        <v>-0.03333333333333333</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="E1221" t="b">
         <v>0</v>
@@ -21970,10 +21970,10 @@
       </c>
       <c r="B1222" t="inlineStr"/>
       <c r="C1222" t="n">
-        <v>0.4285714285714285</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="D1222" t="n">
-        <v>-0.03333333333333333</v>
+        <v>0.3</v>
       </c>
       <c r="E1222" t="b">
         <v>0</v>
@@ -21989,10 +21989,10 @@
         <v>2</v>
       </c>
       <c r="C1223" t="n">
-        <v>0.7142857142857143</v>
+        <v>2.142857142857143</v>
       </c>
       <c r="D1223" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.3666666666666666</v>
       </c>
       <c r="E1223" t="b">
         <v>1</v>
@@ -22006,10 +22006,10 @@
       </c>
       <c r="B1224" t="inlineStr"/>
       <c r="C1224" t="n">
-        <v>0.5714285714285714</v>
+        <v>2</v>
       </c>
       <c r="D1224" t="n">
-        <v>0.1</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="E1224" t="b">
         <v>0</v>
@@ -22023,10 +22023,10 @@
       </c>
       <c r="B1225" t="inlineStr"/>
       <c r="C1225" t="n">
-        <v>0.8571428571428571</v>
+        <v>2</v>
       </c>
       <c r="D1225" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="E1225" t="b">
         <v>0</v>
@@ -22040,10 +22040,10 @@
       </c>
       <c r="B1226" t="inlineStr"/>
       <c r="C1226" t="n">
-        <v>1.142857142857143</v>
+        <v>2</v>
       </c>
       <c r="D1226" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="E1226" t="b">
         <v>0</v>
@@ -22059,10 +22059,10 @@
         <v>0</v>
       </c>
       <c r="C1227" t="n">
-        <v>1.142857142857143</v>
+        <v>1.714285714285714</v>
       </c>
       <c r="D1227" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="E1227" t="b">
         <v>1</v>
@@ -22076,10 +22076,10 @@
       </c>
       <c r="B1228" t="inlineStr"/>
       <c r="C1228" t="n">
-        <v>1.142857142857143</v>
+        <v>1.428571428571429</v>
       </c>
       <c r="D1228" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="E1228" t="b">
         <v>0</v>
@@ -22096,7 +22096,7 @@
         <v>1.142857142857143</v>
       </c>
       <c r="D1229" t="n">
-        <v>0.3</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="E1229" t="b">
         <v>0</v>
@@ -22113,7 +22113,7 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="D1230" t="n">
-        <v>0.3</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="E1230" t="b">
         <v>0</v>
@@ -22130,7 +22130,7 @@
         <v>0.5714285714285714</v>
       </c>
       <c r="D1231" t="n">
-        <v>0.3</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="E1231" t="b">
         <v>0</v>
@@ -22147,7 +22147,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1232" t="n">
-        <v>0.3</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="E1232" t="b">
         <v>0</v>
@@ -22164,7 +22164,7 @@
         <v>0</v>
       </c>
       <c r="D1233" t="n">
-        <v>0.3</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="E1233" t="b">
         <v>0</v>
@@ -22181,7 +22181,7 @@
         <v>0</v>
       </c>
       <c r="D1234" t="n">
-        <v>0.3</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="E1234" t="b">
         <v>0</v>
@@ -22200,7 +22200,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1235" t="n">
-        <v>0.3666666666666666</v>
+        <v>0.7</v>
       </c>
       <c r="E1235" t="b">
         <v>1</v>
@@ -22217,7 +22217,7 @@
         <v>0.5714285714285714</v>
       </c>
       <c r="D1236" t="n">
-        <v>0.4333333333333333</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="E1236" t="b">
         <v>0</v>
@@ -22234,7 +22234,7 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="D1237" t="n">
-        <v>0.5</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E1237" t="b">
         <v>0</v>
@@ -22251,7 +22251,7 @@
         <v>1.142857142857143</v>
       </c>
       <c r="D1238" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.9</v>
       </c>
       <c r="E1238" t="b">
         <v>0</v>
@@ -22270,7 +22270,7 @@
         <v>1.142857142857143</v>
       </c>
       <c r="D1239" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.9</v>
       </c>
       <c r="E1239" t="b">
         <v>1</v>
@@ -22289,7 +22289,7 @@
         <v>1.142857142857143</v>
       </c>
       <c r="D1240" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.9</v>
       </c>
       <c r="E1240" t="b">
         <v>1</v>
@@ -22306,7 +22306,7 @@
         <v>1.142857142857143</v>
       </c>
       <c r="D1241" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.9</v>
       </c>
       <c r="E1241" t="b">
         <v>0</v>
@@ -22325,7 +22325,7 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="D1242" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.9</v>
       </c>
       <c r="E1242" t="b">
         <v>1</v>
@@ -22342,7 +22342,7 @@
         <v>0.5714285714285714</v>
       </c>
       <c r="D1243" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.9</v>
       </c>
       <c r="E1243" t="b">
         <v>0</v>
@@ -22359,7 +22359,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1244" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="E1244" t="b">
         <v>0</v>
@@ -22378,7 +22378,7 @@
         <v>0</v>
       </c>
       <c r="D1245" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="E1245" t="b">
         <v>1</v>
@@ -22397,7 +22397,7 @@
         <v>0</v>
       </c>
       <c r="D1246" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="E1246" t="b">
         <v>1</v>
@@ -22414,7 +22414,7 @@
         <v>0</v>
       </c>
       <c r="D1247" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="E1247" t="b">
         <v>0</v>
@@ -22431,7 +22431,7 @@
         <v>0</v>
       </c>
       <c r="D1248" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.8</v>
       </c>
       <c r="E1248" t="b">
         <v>0</v>
@@ -22448,7 +22448,7 @@
         <v>0</v>
       </c>
       <c r="D1249" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="E1249" t="b">
         <v>0</v>
@@ -22465,7 +22465,7 @@
         <v>0</v>
       </c>
       <c r="D1250" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E1250" t="b">
         <v>0</v>
@@ -22482,7 +22482,7 @@
         <v>0</v>
       </c>
       <c r="D1251" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.6</v>
       </c>
       <c r="E1251" t="b">
         <v>0</v>
@@ -22758,13 +22758,13 @@
         </is>
       </c>
       <c r="B1267" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C1267" t="n">
-        <v>-1.714285714285714</v>
+        <v>-2</v>
       </c>
       <c r="D1267" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E1267" t="b">
         <v>1</v>
@@ -22778,10 +22778,10 @@
       </c>
       <c r="B1268" t="inlineStr"/>
       <c r="C1268" t="n">
-        <v>-1.714285714285714</v>
+        <v>-2.285714285714286</v>
       </c>
       <c r="D1268" t="n">
-        <v>-0.4</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1268" t="b">
         <v>0</v>
@@ -22797,10 +22797,10 @@
         <v>0</v>
       </c>
       <c r="C1269" t="n">
-        <v>-1.714285714285714</v>
+        <v>-2.285714285714286</v>
       </c>
       <c r="D1269" t="n">
-        <v>-0.4</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1269" t="b">
         <v>1</v>
@@ -22814,10 +22814,10 @@
       </c>
       <c r="B1270" t="inlineStr"/>
       <c r="C1270" t="n">
-        <v>-1.285714285714286</v>
+        <v>-1.857142857142857</v>
       </c>
       <c r="D1270" t="n">
-        <v>-0.4</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1270" t="b">
         <v>0</v>
@@ -22831,10 +22831,10 @@
       </c>
       <c r="B1271" t="inlineStr"/>
       <c r="C1271" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-1.428571428571429</v>
       </c>
       <c r="D1271" t="n">
-        <v>-0.4</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1271" t="b">
         <v>0</v>
@@ -22848,10 +22848,10 @@
       </c>
       <c r="B1272" t="inlineStr"/>
       <c r="C1272" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-1</v>
       </c>
       <c r="D1272" t="n">
-        <v>-0.4</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1272" t="b">
         <v>0</v>
@@ -22865,10 +22865,10 @@
       </c>
       <c r="B1273" t="inlineStr"/>
       <c r="C1273" t="n">
-        <v>0</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1273" t="n">
-        <v>-0.4</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1273" t="b">
         <v>0</v>
@@ -22882,10 +22882,10 @@
       </c>
       <c r="B1274" t="inlineStr"/>
       <c r="C1274" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1274" t="n">
-        <v>-0.4</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1274" t="b">
         <v>0</v>
@@ -22904,7 +22904,7 @@
         <v>0</v>
       </c>
       <c r="D1275" t="n">
-        <v>-0.4</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1275" t="b">
         <v>1</v>
@@ -22923,7 +22923,7 @@
         <v>0</v>
       </c>
       <c r="D1276" t="n">
-        <v>-0.4</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1276" t="b">
         <v>1</v>
@@ -22942,7 +22942,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1277" t="n">
-        <v>-0.5</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E1277" t="b">
         <v>1</v>
@@ -22959,7 +22959,7 @@
         <v>-0.8571428571428571</v>
       </c>
       <c r="D1278" t="n">
-        <v>-0.6</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E1278" t="b">
         <v>0</v>
@@ -22978,7 +22978,7 @@
         <v>-0.8571428571428571</v>
       </c>
       <c r="D1279" t="n">
-        <v>-0.6</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E1279" t="b">
         <v>1</v>
@@ -22997,7 +22997,7 @@
         <v>-0.8571428571428571</v>
       </c>
       <c r="D1280" t="n">
-        <v>-0.6</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E1280" t="b">
         <v>1</v>
@@ -23014,7 +23014,7 @@
         <v>-0.8571428571428571</v>
       </c>
       <c r="D1281" t="n">
-        <v>-0.6</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E1281" t="b">
         <v>0</v>
@@ -23033,7 +23033,7 @@
         <v>-0.8571428571428571</v>
       </c>
       <c r="D1282" t="n">
-        <v>-0.6</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E1282" t="b">
         <v>1</v>
@@ -23050,7 +23050,7 @@
         <v>-0.8571428571428571</v>
       </c>
       <c r="D1283" t="n">
-        <v>-0.6</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E1283" t="b">
         <v>0</v>
@@ -23069,7 +23069,7 @@
         <v>-0.8571428571428571</v>
       </c>
       <c r="D1284" t="n">
-        <v>-0.7</v>
+        <v>-0.8333333333333334</v>
       </c>
       <c r="E1284" t="b">
         <v>1</v>
@@ -23088,7 +23088,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1285" t="n">
-        <v>-0.7</v>
+        <v>-0.8333333333333334</v>
       </c>
       <c r="E1285" t="b">
         <v>1</v>
@@ -23105,7 +23105,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1286" t="n">
-        <v>-0.7</v>
+        <v>-0.8333333333333334</v>
       </c>
       <c r="E1286" t="b">
         <v>0</v>
@@ -23124,7 +23124,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1287" t="n">
-        <v>-0.7</v>
+        <v>-0.8333333333333334</v>
       </c>
       <c r="E1287" t="b">
         <v>1</v>
@@ -23141,7 +23141,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1288" t="n">
-        <v>-0.7</v>
+        <v>-0.8333333333333334</v>
       </c>
       <c r="E1288" t="b">
         <v>0</v>
@@ -23158,7 +23158,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1289" t="n">
-        <v>-0.7</v>
+        <v>-0.8333333333333334</v>
       </c>
       <c r="E1289" t="b">
         <v>0</v>
@@ -23177,7 +23177,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1290" t="n">
-        <v>-0.7</v>
+        <v>-0.8333333333333334</v>
       </c>
       <c r="E1290" t="b">
         <v>1</v>
@@ -23196,7 +23196,7 @@
         <v>0</v>
       </c>
       <c r="D1291" t="n">
-        <v>-0.7</v>
+        <v>-0.8333333333333334</v>
       </c>
       <c r="E1291" t="b">
         <v>1</v>
@@ -23213,7 +23213,7 @@
         <v>0</v>
       </c>
       <c r="D1292" t="n">
-        <v>-0.7</v>
+        <v>-0.8333333333333334</v>
       </c>
       <c r="E1292" t="b">
         <v>0</v>
@@ -23232,7 +23232,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1293" t="n">
-        <v>-0.7</v>
+        <v>-0.8333333333333334</v>
       </c>
       <c r="E1293" t="b">
         <v>1</v>
@@ -23251,7 +23251,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1294" t="n">
-        <v>-0.6</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E1294" t="b">
         <v>1</v>
@@ -23268,7 +23268,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1295" t="n">
-        <v>-0.5</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E1295" t="b">
         <v>0</v>
@@ -23287,7 +23287,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1296" t="n">
-        <v>-0.4</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1296" t="b">
         <v>1</v>
@@ -23306,7 +23306,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1297" t="n">
-        <v>-0.4</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1297" t="b">
         <v>1</v>
@@ -25069,13 +25069,13 @@
         </is>
       </c>
       <c r="B1398" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="C1398" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1398" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="E1398" t="b">
         <v>1</v>
@@ -25089,10 +25089,10 @@
       </c>
       <c r="B1399" t="inlineStr"/>
       <c r="C1399" t="n">
-        <v>-0.5714285714285714</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D1399" t="n">
-        <v>0</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="E1399" t="b">
         <v>0</v>
@@ -25106,10 +25106,10 @@
       </c>
       <c r="B1400" t="inlineStr"/>
       <c r="C1400" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D1400" t="n">
-        <v>-0.1333333333333333</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="E1400" t="b">
         <v>0</v>
@@ -25125,10 +25125,10 @@
         <v>0</v>
       </c>
       <c r="C1401" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D1401" t="n">
-        <v>-0.2</v>
+        <v>0.2</v>
       </c>
       <c r="E1401" t="b">
         <v>1</v>
@@ -25142,10 +25142,10 @@
       </c>
       <c r="B1402" t="inlineStr"/>
       <c r="C1402" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D1402" t="n">
-        <v>-0.2</v>
+        <v>0.2</v>
       </c>
       <c r="E1402" t="b">
         <v>0</v>
@@ -25159,10 +25159,10 @@
       </c>
       <c r="B1403" t="inlineStr"/>
       <c r="C1403" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D1403" t="n">
-        <v>-0.2</v>
+        <v>0.2</v>
       </c>
       <c r="E1403" t="b">
         <v>0</v>
@@ -25176,10 +25176,10 @@
       </c>
       <c r="B1404" t="inlineStr"/>
       <c r="C1404" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D1404" t="n">
-        <v>-0.2</v>
+        <v>0.2</v>
       </c>
       <c r="E1404" t="b">
         <v>0</v>
@@ -25193,13 +25193,32 @@
       </c>
       <c r="B1405" t="inlineStr"/>
       <c r="C1405" t="n">
-        <v>-0.5714285714285714</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D1405" t="n">
-        <v>-0.2</v>
+        <v>0.2</v>
       </c>
       <c r="E1405" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B1406" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1406" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="D1406" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E1406" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -25232,7 +25251,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-05-25 to 2026-03-28 | Publication days: 472</t>
+          <t>Coverage: 2022-05-25 to 2026-03-29 | Publication days: 473</t>
         </is>
       </c>
     </row>

--- a/data/AU.xlsx
+++ b/data/AU.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1406"/>
+  <dimension ref="A1:E1407"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21825,13 +21825,13 @@
         </is>
       </c>
       <c r="B1214" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C1214" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1214" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E1214" t="b">
         <v>1</v>
@@ -21847,10 +21847,10 @@
         <v>0</v>
       </c>
       <c r="C1215" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1215" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.5</v>
       </c>
       <c r="E1215" t="b">
         <v>1</v>
@@ -21864,10 +21864,10 @@
       </c>
       <c r="B1216" t="inlineStr"/>
       <c r="C1216" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1216" t="n">
-        <v>-0.5</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1216" t="b">
         <v>0</v>
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="B1217" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C1217" t="n">
-        <v>0.1428571428571428</v>
+        <v>0</v>
       </c>
       <c r="D1217" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1217" t="b">
         <v>1</v>
@@ -21899,13 +21899,13 @@
         </is>
       </c>
       <c r="B1218" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C1218" t="n">
-        <v>0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D1218" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="E1218" t="b">
         <v>1</v>
@@ -21919,10 +21919,10 @@
       </c>
       <c r="B1219" t="inlineStr"/>
       <c r="C1219" t="n">
-        <v>0.7142857142857143</v>
+        <v>0</v>
       </c>
       <c r="D1219" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E1219" t="b">
         <v>0</v>
@@ -21936,10 +21936,10 @@
       </c>
       <c r="B1220" t="inlineStr"/>
       <c r="C1220" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D1220" t="n">
-        <v>0.06666666666666667</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1220" t="b">
         <v>0</v>
@@ -21953,10 +21953,10 @@
       </c>
       <c r="B1221" t="inlineStr"/>
       <c r="C1221" t="n">
-        <v>1.571428571428571</v>
+        <v>0</v>
       </c>
       <c r="D1221" t="n">
-        <v>0.2333333333333333</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1221" t="b">
         <v>0</v>
@@ -21970,10 +21970,10 @@
       </c>
       <c r="B1222" t="inlineStr"/>
       <c r="C1222" t="n">
-        <v>1.857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1222" t="n">
-        <v>0.3</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1222" t="b">
         <v>0</v>
@@ -21986,13 +21986,13 @@
         </is>
       </c>
       <c r="B1223" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C1223" t="n">
-        <v>2.142857142857143</v>
+        <v>0</v>
       </c>
       <c r="D1223" t="n">
-        <v>0.3666666666666666</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1223" t="b">
         <v>1</v>
@@ -22006,10 +22006,10 @@
       </c>
       <c r="B1224" t="inlineStr"/>
       <c r="C1224" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D1224" t="n">
-        <v>0.4333333333333333</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1224" t="b">
         <v>0</v>
@@ -22023,10 +22023,10 @@
       </c>
       <c r="B1225" t="inlineStr"/>
       <c r="C1225" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D1225" t="n">
-        <v>0.5</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1225" t="b">
         <v>0</v>
@@ -22040,10 +22040,10 @@
       </c>
       <c r="B1226" t="inlineStr"/>
       <c r="C1226" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D1226" t="n">
-        <v>0.5666666666666667</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1226" t="b">
         <v>0</v>
@@ -22059,10 +22059,10 @@
         <v>0</v>
       </c>
       <c r="C1227" t="n">
-        <v>1.714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D1227" t="n">
-        <v>0.5666666666666667</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1227" t="b">
         <v>1</v>
@@ -22076,10 +22076,10 @@
       </c>
       <c r="B1228" t="inlineStr"/>
       <c r="C1228" t="n">
-        <v>1.428571428571429</v>
+        <v>0</v>
       </c>
       <c r="D1228" t="n">
-        <v>0.5666666666666667</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1228" t="b">
         <v>0</v>
@@ -22093,10 +22093,10 @@
       </c>
       <c r="B1229" t="inlineStr"/>
       <c r="C1229" t="n">
-        <v>1.142857142857143</v>
+        <v>0</v>
       </c>
       <c r="D1229" t="n">
-        <v>0.6333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E1229" t="b">
         <v>0</v>
@@ -22110,10 +22110,10 @@
       </c>
       <c r="B1230" t="inlineStr"/>
       <c r="C1230" t="n">
-        <v>0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="D1230" t="n">
-        <v>0.6333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E1230" t="b">
         <v>0</v>
@@ -22127,10 +22127,10 @@
       </c>
       <c r="B1231" t="inlineStr"/>
       <c r="C1231" t="n">
-        <v>0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D1231" t="n">
-        <v>0.6333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E1231" t="b">
         <v>0</v>
@@ -22144,10 +22144,10 @@
       </c>
       <c r="B1232" t="inlineStr"/>
       <c r="C1232" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1232" t="n">
-        <v>0.6333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E1232" t="b">
         <v>0</v>
@@ -22164,7 +22164,7 @@
         <v>0</v>
       </c>
       <c r="D1233" t="n">
-        <v>0.6333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E1233" t="b">
         <v>0</v>
@@ -22181,7 +22181,7 @@
         <v>0</v>
       </c>
       <c r="D1234" t="n">
-        <v>0.6333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E1234" t="b">
         <v>0</v>
@@ -22194,13 +22194,13 @@
         </is>
       </c>
       <c r="B1235" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C1235" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1235" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="E1235" t="b">
         <v>1</v>
@@ -22214,10 +22214,10 @@
       </c>
       <c r="B1236" t="inlineStr"/>
       <c r="C1236" t="n">
-        <v>0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D1236" t="n">
-        <v>0.7666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1236" t="b">
         <v>0</v>
@@ -22231,10 +22231,10 @@
       </c>
       <c r="B1237" t="inlineStr"/>
       <c r="C1237" t="n">
-        <v>0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="D1237" t="n">
-        <v>0.8333333333333334</v>
+        <v>0</v>
       </c>
       <c r="E1237" t="b">
         <v>0</v>
@@ -22248,10 +22248,10 @@
       </c>
       <c r="B1238" t="inlineStr"/>
       <c r="C1238" t="n">
-        <v>1.142857142857143</v>
+        <v>0</v>
       </c>
       <c r="D1238" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="E1238" t="b">
         <v>0</v>
@@ -22267,10 +22267,10 @@
         <v>0</v>
       </c>
       <c r="C1239" t="n">
-        <v>1.142857142857143</v>
+        <v>0</v>
       </c>
       <c r="D1239" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="E1239" t="b">
         <v>1</v>
@@ -22286,10 +22286,10 @@
         <v>0</v>
       </c>
       <c r="C1240" t="n">
-        <v>1.142857142857143</v>
+        <v>0</v>
       </c>
       <c r="D1240" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="E1240" t="b">
         <v>1</v>
@@ -22303,10 +22303,10 @@
       </c>
       <c r="B1241" t="inlineStr"/>
       <c r="C1241" t="n">
-        <v>1.142857142857143</v>
+        <v>0</v>
       </c>
       <c r="D1241" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="E1241" t="b">
         <v>0</v>
@@ -22322,10 +22322,10 @@
         <v>0</v>
       </c>
       <c r="C1242" t="n">
-        <v>0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="D1242" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="E1242" t="b">
         <v>1</v>
@@ -22339,10 +22339,10 @@
       </c>
       <c r="B1243" t="inlineStr"/>
       <c r="C1243" t="n">
-        <v>0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D1243" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="E1243" t="b">
         <v>0</v>
@@ -22356,10 +22356,10 @@
       </c>
       <c r="B1244" t="inlineStr"/>
       <c r="C1244" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1244" t="n">
-        <v>0.9666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1244" t="b">
         <v>0</v>
@@ -22378,7 +22378,7 @@
         <v>0</v>
       </c>
       <c r="D1245" t="n">
-        <v>0.9666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1245" t="b">
         <v>1</v>
@@ -22397,7 +22397,7 @@
         <v>0</v>
       </c>
       <c r="D1246" t="n">
-        <v>0.9666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1246" t="b">
         <v>1</v>
@@ -22414,7 +22414,7 @@
         <v>0</v>
       </c>
       <c r="D1247" t="n">
-        <v>0.8666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1247" t="b">
         <v>0</v>
@@ -22431,7 +22431,7 @@
         <v>0</v>
       </c>
       <c r="D1248" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="E1248" t="b">
         <v>0</v>
@@ -22448,7 +22448,7 @@
         <v>0</v>
       </c>
       <c r="D1249" t="n">
-        <v>0.7333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E1249" t="b">
         <v>0</v>
@@ -22465,7 +22465,7 @@
         <v>0</v>
       </c>
       <c r="D1250" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="E1250" t="b">
         <v>0</v>
@@ -22482,7 +22482,7 @@
         <v>0</v>
       </c>
       <c r="D1251" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="E1251" t="b">
         <v>0</v>
@@ -22499,7 +22499,7 @@
         <v>0</v>
       </c>
       <c r="D1252" t="n">
-        <v>0.5333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E1252" t="b">
         <v>0</v>
@@ -22518,7 +22518,7 @@
         <v>0</v>
       </c>
       <c r="D1253" t="n">
-        <v>0.4666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1253" t="b">
         <v>1</v>
@@ -22535,7 +22535,7 @@
         <v>0</v>
       </c>
       <c r="D1254" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="E1254" t="b">
         <v>0</v>
@@ -22554,7 +22554,7 @@
         <v>0</v>
       </c>
       <c r="D1255" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E1255" t="b">
         <v>1</v>
@@ -22571,7 +22571,7 @@
         <v>0</v>
       </c>
       <c r="D1256" t="n">
-        <v>0.2666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1256" t="b">
         <v>0</v>
@@ -22588,7 +22588,7 @@
         <v>0</v>
       </c>
       <c r="D1257" t="n">
-        <v>0.2666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1257" t="b">
         <v>0</v>
@@ -22605,7 +22605,7 @@
         <v>0</v>
       </c>
       <c r="D1258" t="n">
-        <v>0.2666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1258" t="b">
         <v>0</v>
@@ -22622,7 +22622,7 @@
         <v>0</v>
       </c>
       <c r="D1259" t="n">
-        <v>0.2666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1259" t="b">
         <v>0</v>
@@ -22639,7 +22639,7 @@
         <v>0</v>
       </c>
       <c r="D1260" t="n">
-        <v>0.2666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1260" t="b">
         <v>0</v>
@@ -22656,7 +22656,7 @@
         <v>0</v>
       </c>
       <c r="D1261" t="n">
-        <v>0.2666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1261" t="b">
         <v>0</v>
@@ -22675,7 +22675,7 @@
         <v>0</v>
       </c>
       <c r="D1262" t="n">
-        <v>0.2666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1262" t="b">
         <v>1</v>
@@ -22688,13 +22688,13 @@
         </is>
       </c>
       <c r="B1263" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="C1263" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D1263" t="n">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1263" t="b">
         <v>1</v>
@@ -22708,10 +22708,10 @@
       </c>
       <c r="B1264" t="inlineStr"/>
       <c r="C1264" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="D1264" t="n">
-        <v>0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1264" t="b">
         <v>0</v>
@@ -22725,10 +22725,10 @@
       </c>
       <c r="B1265" t="inlineStr"/>
       <c r="C1265" t="n">
-        <v>-1.285714285714286</v>
+        <v>0</v>
       </c>
       <c r="D1265" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="E1265" t="b">
         <v>0</v>
@@ -22742,10 +22742,10 @@
       </c>
       <c r="B1266" t="inlineStr"/>
       <c r="C1266" t="n">
-        <v>-1.714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D1266" t="n">
-        <v>-0.2666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1266" t="b">
         <v>0</v>
@@ -22761,10 +22761,10 @@
         <v>-2</v>
       </c>
       <c r="C1267" t="n">
-        <v>-2</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1267" t="n">
-        <v>-0.4</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1267" t="b">
         <v>1</v>
@@ -22778,10 +22778,10 @@
       </c>
       <c r="B1268" t="inlineStr"/>
       <c r="C1268" t="n">
-        <v>-2.285714285714286</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1268" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1268" t="b">
         <v>0</v>
@@ -22797,10 +22797,10 @@
         <v>0</v>
       </c>
       <c r="C1269" t="n">
-        <v>-2.285714285714286</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1269" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1269" t="b">
         <v>1</v>
@@ -22814,10 +22814,10 @@
       </c>
       <c r="B1270" t="inlineStr"/>
       <c r="C1270" t="n">
-        <v>-1.857142857142857</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1270" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1270" t="b">
         <v>0</v>
@@ -22831,10 +22831,10 @@
       </c>
       <c r="B1271" t="inlineStr"/>
       <c r="C1271" t="n">
-        <v>-1.428571428571429</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1271" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1271" t="b">
         <v>0</v>
@@ -22848,10 +22848,10 @@
       </c>
       <c r="B1272" t="inlineStr"/>
       <c r="C1272" t="n">
-        <v>-1</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1272" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1272" t="b">
         <v>0</v>
@@ -22868,7 +22868,7 @@
         <v>-0.5714285714285714</v>
       </c>
       <c r="D1273" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1273" t="b">
         <v>0</v>
@@ -22885,7 +22885,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1274" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1274" t="b">
         <v>0</v>
@@ -22904,7 +22904,7 @@
         <v>0</v>
       </c>
       <c r="D1275" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1275" t="b">
         <v>1</v>
@@ -22923,7 +22923,7 @@
         <v>0</v>
       </c>
       <c r="D1276" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1276" t="b">
         <v>1</v>
@@ -22936,13 +22936,13 @@
         </is>
       </c>
       <c r="B1277" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="C1277" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D1277" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1277" t="b">
         <v>1</v>
@@ -22956,10 +22956,10 @@
       </c>
       <c r="B1278" t="inlineStr"/>
       <c r="C1278" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="D1278" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1278" t="b">
         <v>0</v>
@@ -22975,10 +22975,10 @@
         <v>0</v>
       </c>
       <c r="C1279" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="D1279" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1279" t="b">
         <v>1</v>
@@ -22994,10 +22994,10 @@
         <v>0</v>
       </c>
       <c r="C1280" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="D1280" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1280" t="b">
         <v>1</v>
@@ -23011,10 +23011,10 @@
       </c>
       <c r="B1281" t="inlineStr"/>
       <c r="C1281" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="D1281" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1281" t="b">
         <v>0</v>
@@ -23030,10 +23030,10 @@
         <v>0</v>
       </c>
       <c r="C1282" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="D1282" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1282" t="b">
         <v>1</v>
@@ -23047,10 +23047,10 @@
       </c>
       <c r="B1283" t="inlineStr"/>
       <c r="C1283" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="D1283" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1283" t="b">
         <v>0</v>
@@ -23063,13 +23063,13 @@
         </is>
       </c>
       <c r="B1284" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="C1284" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="D1284" t="n">
-        <v>-0.8333333333333334</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1284" t="b">
         <v>1</v>
@@ -23085,10 +23085,10 @@
         <v>0</v>
       </c>
       <c r="C1285" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D1285" t="n">
-        <v>-0.8333333333333334</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1285" t="b">
         <v>1</v>
@@ -23102,10 +23102,10 @@
       </c>
       <c r="B1286" t="inlineStr"/>
       <c r="C1286" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D1286" t="n">
-        <v>-0.8333333333333334</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1286" t="b">
         <v>0</v>
@@ -23121,10 +23121,10 @@
         <v>0</v>
       </c>
       <c r="C1287" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D1287" t="n">
-        <v>-0.8333333333333334</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1287" t="b">
         <v>1</v>
@@ -23138,10 +23138,10 @@
       </c>
       <c r="B1288" t="inlineStr"/>
       <c r="C1288" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D1288" t="n">
-        <v>-0.8333333333333334</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1288" t="b">
         <v>0</v>
@@ -23155,10 +23155,10 @@
       </c>
       <c r="B1289" t="inlineStr"/>
       <c r="C1289" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D1289" t="n">
-        <v>-0.8333333333333334</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1289" t="b">
         <v>0</v>
@@ -23174,10 +23174,10 @@
         <v>0</v>
       </c>
       <c r="C1290" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D1290" t="n">
-        <v>-0.8333333333333334</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1290" t="b">
         <v>1</v>
@@ -23196,7 +23196,7 @@
         <v>0</v>
       </c>
       <c r="D1291" t="n">
-        <v>-0.8333333333333334</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1291" t="b">
         <v>1</v>
@@ -23213,7 +23213,7 @@
         <v>0</v>
       </c>
       <c r="D1292" t="n">
-        <v>-0.8333333333333334</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1292" t="b">
         <v>0</v>
@@ -23232,7 +23232,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1293" t="n">
-        <v>-0.8333333333333334</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E1293" t="b">
         <v>1</v>
@@ -23251,7 +23251,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1294" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E1294" t="b">
         <v>1</v>
@@ -23268,7 +23268,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1295" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E1295" t="b">
         <v>0</v>
@@ -23287,7 +23287,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1296" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E1296" t="b">
         <v>1</v>
@@ -23306,7 +23306,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1297" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1297" t="b">
         <v>1</v>
@@ -23323,7 +23323,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1298" t="n">
-        <v>-0.4</v>
+        <v>-0.1</v>
       </c>
       <c r="E1298" t="b">
         <v>0</v>
@@ -23340,7 +23340,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1299" t="n">
-        <v>-0.4</v>
+        <v>-0.1</v>
       </c>
       <c r="E1299" t="b">
         <v>0</v>
@@ -23357,7 +23357,7 @@
         <v>0</v>
       </c>
       <c r="D1300" t="n">
-        <v>-0.4</v>
+        <v>-0.1</v>
       </c>
       <c r="E1300" t="b">
         <v>0</v>
@@ -23374,7 +23374,7 @@
         <v>0</v>
       </c>
       <c r="D1301" t="n">
-        <v>-0.4</v>
+        <v>-0.1</v>
       </c>
       <c r="E1301" t="b">
         <v>0</v>
@@ -23391,7 +23391,7 @@
         <v>0</v>
       </c>
       <c r="D1302" t="n">
-        <v>-0.4</v>
+        <v>-0.1</v>
       </c>
       <c r="E1302" t="b">
         <v>0</v>
@@ -23408,7 +23408,7 @@
         <v>0</v>
       </c>
       <c r="D1303" t="n">
-        <v>-0.4</v>
+        <v>-0.1</v>
       </c>
       <c r="E1303" t="b">
         <v>0</v>
@@ -23425,7 +23425,7 @@
         <v>0</v>
       </c>
       <c r="D1304" t="n">
-        <v>-0.4</v>
+        <v>-0.1</v>
       </c>
       <c r="E1304" t="b">
         <v>0</v>
@@ -23442,7 +23442,7 @@
         <v>0</v>
       </c>
       <c r="D1305" t="n">
-        <v>-0.4</v>
+        <v>-0.1</v>
       </c>
       <c r="E1305" t="b">
         <v>0</v>
@@ -23459,7 +23459,7 @@
         <v>0</v>
       </c>
       <c r="D1306" t="n">
-        <v>-0.4</v>
+        <v>-0.1</v>
       </c>
       <c r="E1306" t="b">
         <v>0</v>
@@ -23476,7 +23476,7 @@
         <v>0</v>
       </c>
       <c r="D1307" t="n">
-        <v>-0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="E1307" t="b">
         <v>0</v>
@@ -23493,7 +23493,7 @@
         <v>0</v>
       </c>
       <c r="D1308" t="n">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="E1308" t="b">
         <v>0</v>
@@ -23510,7 +23510,7 @@
         <v>0</v>
       </c>
       <c r="D1309" t="n">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="E1309" t="b">
         <v>0</v>
@@ -23527,7 +23527,7 @@
         <v>0</v>
       </c>
       <c r="D1310" t="n">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="E1310" t="b">
         <v>0</v>
@@ -23544,7 +23544,7 @@
         <v>0</v>
       </c>
       <c r="D1311" t="n">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="E1311" t="b">
         <v>0</v>
@@ -23561,7 +23561,7 @@
         <v>0</v>
       </c>
       <c r="D1312" t="n">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="E1312" t="b">
         <v>0</v>
@@ -23578,7 +23578,7 @@
         <v>0</v>
       </c>
       <c r="D1313" t="n">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="E1313" t="b">
         <v>0</v>
@@ -24054,13 +24054,13 @@
         </is>
       </c>
       <c r="B1341" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C1341" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1341" t="n">
-        <v>0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1341" t="b">
         <v>1</v>
@@ -24074,10 +24074,10 @@
       </c>
       <c r="B1342" t="inlineStr"/>
       <c r="C1342" t="n">
-        <v>0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D1342" t="n">
-        <v>0.1333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E1342" t="b">
         <v>0</v>
@@ -24093,10 +24093,10 @@
         <v>0</v>
       </c>
       <c r="C1343" t="n">
-        <v>0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D1343" t="n">
-        <v>0.1333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E1343" t="b">
         <v>1</v>
@@ -24110,10 +24110,10 @@
       </c>
       <c r="B1344" t="inlineStr"/>
       <c r="C1344" t="n">
-        <v>0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D1344" t="n">
-        <v>0.1333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E1344" t="b">
         <v>0</v>
@@ -24129,10 +24129,10 @@
         <v>0</v>
       </c>
       <c r="C1345" t="n">
-        <v>0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D1345" t="n">
-        <v>0.1333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E1345" t="b">
         <v>1</v>
@@ -24146,10 +24146,10 @@
       </c>
       <c r="B1346" t="inlineStr"/>
       <c r="C1346" t="n">
-        <v>0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D1346" t="n">
-        <v>0.1333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E1346" t="b">
         <v>0</v>
@@ -24165,10 +24165,10 @@
         <v>0</v>
       </c>
       <c r="C1347" t="n">
-        <v>0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D1347" t="n">
-        <v>0.1333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E1347" t="b">
         <v>1</v>
@@ -24182,10 +24182,10 @@
       </c>
       <c r="B1348" t="inlineStr"/>
       <c r="C1348" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1348" t="n">
-        <v>0.1333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E1348" t="b">
         <v>0</v>
@@ -24202,7 +24202,7 @@
         <v>0</v>
       </c>
       <c r="D1349" t="n">
-        <v>0.1333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E1349" t="b">
         <v>0</v>
@@ -24215,13 +24215,13 @@
         </is>
       </c>
       <c r="B1350" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C1350" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1350" t="n">
-        <v>0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1350" t="b">
         <v>1</v>
@@ -24235,7 +24235,7 @@
       </c>
       <c r="B1351" t="inlineStr"/>
       <c r="C1351" t="n">
-        <v>-0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D1351" t="n">
         <v>0</v>
@@ -24251,13 +24251,13 @@
         </is>
       </c>
       <c r="B1352" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="C1352" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D1352" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="E1352" t="b">
         <v>1</v>
@@ -24273,10 +24273,10 @@
         <v>0</v>
       </c>
       <c r="C1353" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D1353" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="E1353" t="b">
         <v>1</v>
@@ -24292,10 +24292,10 @@
         <v>0</v>
       </c>
       <c r="C1354" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D1354" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="E1354" t="b">
         <v>1</v>
@@ -24309,10 +24309,10 @@
       </c>
       <c r="B1355" t="inlineStr"/>
       <c r="C1355" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D1355" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="E1355" t="b">
         <v>0</v>
@@ -24325,13 +24325,13 @@
         </is>
       </c>
       <c r="B1356" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C1356" t="n">
-        <v>-0.7142857142857143</v>
+        <v>0</v>
       </c>
       <c r="D1356" t="n">
-        <v>-0.03333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E1356" t="b">
         <v>1</v>
@@ -24347,10 +24347,10 @@
         <v>0</v>
       </c>
       <c r="C1357" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D1357" t="n">
-        <v>-0.03333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E1357" t="b">
         <v>1</v>
@@ -24366,10 +24366,10 @@
         <v>0</v>
       </c>
       <c r="C1358" t="n">
-        <v>-0.1428571428571428</v>
+        <v>0</v>
       </c>
       <c r="D1358" t="n">
-        <v>-0.03333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E1358" t="b">
         <v>1</v>
@@ -24383,10 +24383,10 @@
       </c>
       <c r="B1359" t="inlineStr"/>
       <c r="C1359" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1359" t="n">
-        <v>-0.03333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E1359" t="b">
         <v>0</v>
@@ -24400,10 +24400,10 @@
       </c>
       <c r="B1360" t="inlineStr"/>
       <c r="C1360" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1360" t="n">
-        <v>-0.03333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E1360" t="b">
         <v>0</v>
@@ -24419,10 +24419,10 @@
         <v>0</v>
       </c>
       <c r="C1361" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1361" t="n">
-        <v>-0.03333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E1361" t="b">
         <v>1</v>
@@ -24436,10 +24436,10 @@
       </c>
       <c r="B1362" t="inlineStr"/>
       <c r="C1362" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1362" t="n">
-        <v>-0.03333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E1362" t="b">
         <v>0</v>
@@ -24456,7 +24456,7 @@
         <v>0</v>
       </c>
       <c r="D1363" t="n">
-        <v>-0.03333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E1363" t="b">
         <v>0</v>
@@ -24473,7 +24473,7 @@
         <v>0</v>
       </c>
       <c r="D1364" t="n">
-        <v>-0.03333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E1364" t="b">
         <v>0</v>
@@ -24490,7 +24490,7 @@
         <v>0</v>
       </c>
       <c r="D1365" t="n">
-        <v>-0.03333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E1365" t="b">
         <v>0</v>
@@ -24507,7 +24507,7 @@
         <v>0</v>
       </c>
       <c r="D1366" t="n">
-        <v>-0.03333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E1366" t="b">
         <v>0</v>
@@ -24526,7 +24526,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1367" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1367" t="b">
         <v>1</v>
@@ -24543,7 +24543,7 @@
         <v>0.5714285714285714</v>
       </c>
       <c r="D1368" t="n">
-        <v>0.1</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1368" t="b">
         <v>0</v>
@@ -24560,7 +24560,7 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="D1369" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2</v>
       </c>
       <c r="E1369" t="b">
         <v>0</v>
@@ -24577,7 +24577,7 @@
         <v>1.142857142857143</v>
       </c>
       <c r="D1370" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="E1370" t="b">
         <v>0</v>
@@ -24594,7 +24594,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="D1371" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E1371" t="b">
         <v>0</v>
@@ -24613,7 +24613,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="D1372" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E1372" t="b">
         <v>1</v>
@@ -24632,7 +24632,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="D1373" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E1373" t="b">
         <v>1</v>
@@ -24649,7 +24649,7 @@
         <v>1.142857142857143</v>
       </c>
       <c r="D1374" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E1374" t="b">
         <v>0</v>
@@ -24668,7 +24668,7 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="D1375" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E1375" t="b">
         <v>1</v>
@@ -24687,7 +24687,7 @@
         <v>0.5714285714285714</v>
       </c>
       <c r="D1376" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E1376" t="b">
         <v>1</v>
@@ -24706,7 +24706,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1377" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E1377" t="b">
         <v>1</v>
@@ -24723,7 +24723,7 @@
         <v>0</v>
       </c>
       <c r="D1378" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E1378" t="b">
         <v>0</v>
@@ -24742,7 +24742,7 @@
         <v>0</v>
       </c>
       <c r="D1379" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E1379" t="b">
         <v>1</v>
@@ -24759,7 +24759,7 @@
         <v>0</v>
       </c>
       <c r="D1380" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E1380" t="b">
         <v>0</v>
@@ -24776,7 +24776,7 @@
         <v>0</v>
       </c>
       <c r="D1381" t="n">
-        <v>0.3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E1381" t="b">
         <v>0</v>
@@ -24793,7 +24793,7 @@
         <v>0</v>
       </c>
       <c r="D1382" t="n">
-        <v>0.4</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E1382" t="b">
         <v>0</v>
@@ -24812,7 +24812,7 @@
         <v>0</v>
       </c>
       <c r="D1383" t="n">
-        <v>0.4</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E1383" t="b">
         <v>1</v>
@@ -24829,7 +24829,7 @@
         <v>0</v>
       </c>
       <c r="D1384" t="n">
-        <v>0.4</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E1384" t="b">
         <v>0</v>
@@ -24846,7 +24846,7 @@
         <v>0</v>
       </c>
       <c r="D1385" t="n">
-        <v>0.4</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E1385" t="b">
         <v>0</v>
@@ -25219,6 +25219,23 @@
       </c>
       <c r="E1406" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="A1407" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B1407" t="inlineStr"/>
+      <c r="C1407" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1407" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E1407" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -25251,7 +25268,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-05-25 to 2026-03-29 | Publication days: 473</t>
+          <t>Coverage: 2022-05-25 to 2026-03-30 | Publication days: 473</t>
         </is>
       </c>
     </row>

--- a/data/AU.xlsx
+++ b/data/AU.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1407"/>
+  <dimension ref="A1:E1408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -25235,6 +25235,23 @@
         <v>0.2</v>
       </c>
       <c r="E1407" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="A1408" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B1408" t="inlineStr"/>
+      <c r="C1408" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1408" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E1408" t="b">
         <v>0</v>
       </c>
     </row>
@@ -25268,7 +25285,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-05-25 to 2026-03-30 | Publication days: 473</t>
+          <t>Coverage: 2022-05-25 to 2026-03-31 | Publication days: 473</t>
         </is>
       </c>
     </row>

--- a/data/AU.xlsx
+++ b/data/AU.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1408"/>
+  <dimension ref="A1:E1409"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21825,13 +21825,13 @@
         </is>
       </c>
       <c r="B1214" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C1214" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1214" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E1214" t="b">
         <v>1</v>
@@ -21847,10 +21847,10 @@
         <v>0</v>
       </c>
       <c r="C1215" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1215" t="n">
-        <v>-0.5</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E1215" t="b">
         <v>1</v>
@@ -21864,10 +21864,10 @@
       </c>
       <c r="B1216" t="inlineStr"/>
       <c r="C1216" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1216" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="E1216" t="b">
         <v>0</v>
@@ -21883,10 +21883,10 @@
         <v>0</v>
       </c>
       <c r="C1217" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1217" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1217" t="b">
         <v>1</v>
@@ -21902,10 +21902,10 @@
         <v>0</v>
       </c>
       <c r="C1218" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1218" t="n">
-        <v>-0.3</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1218" t="b">
         <v>1</v>
@@ -21919,10 +21919,10 @@
       </c>
       <c r="B1219" t="inlineStr"/>
       <c r="C1219" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1219" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="E1219" t="b">
         <v>0</v>
@@ -21936,10 +21936,10 @@
       </c>
       <c r="B1220" t="inlineStr"/>
       <c r="C1220" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1220" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E1220" t="b">
         <v>0</v>
@@ -21956,7 +21956,7 @@
         <v>0</v>
       </c>
       <c r="D1221" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1221" t="b">
         <v>0</v>
@@ -21973,7 +21973,7 @@
         <v>0</v>
       </c>
       <c r="D1222" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1222" t="b">
         <v>0</v>
@@ -21992,7 +21992,7 @@
         <v>0</v>
       </c>
       <c r="D1223" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1223" t="b">
         <v>1</v>
@@ -22009,7 +22009,7 @@
         <v>0</v>
       </c>
       <c r="D1224" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1224" t="b">
         <v>0</v>
@@ -22026,7 +22026,7 @@
         <v>0</v>
       </c>
       <c r="D1225" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1225" t="b">
         <v>0</v>
@@ -22043,7 +22043,7 @@
         <v>0</v>
       </c>
       <c r="D1226" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1226" t="b">
         <v>0</v>
@@ -22062,7 +22062,7 @@
         <v>0</v>
       </c>
       <c r="D1227" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1227" t="b">
         <v>1</v>
@@ -22079,7 +22079,7 @@
         <v>0</v>
       </c>
       <c r="D1228" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1228" t="b">
         <v>0</v>
@@ -22096,7 +22096,7 @@
         <v>0</v>
       </c>
       <c r="D1229" t="n">
-        <v>0</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1229" t="b">
         <v>0</v>
@@ -22113,7 +22113,7 @@
         <v>0</v>
       </c>
       <c r="D1230" t="n">
-        <v>0</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1230" t="b">
         <v>0</v>
@@ -22130,7 +22130,7 @@
         <v>0</v>
       </c>
       <c r="D1231" t="n">
-        <v>0</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1231" t="b">
         <v>0</v>
@@ -22147,7 +22147,7 @@
         <v>0</v>
       </c>
       <c r="D1232" t="n">
-        <v>0</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1232" t="b">
         <v>0</v>
@@ -22164,7 +22164,7 @@
         <v>0</v>
       </c>
       <c r="D1233" t="n">
-        <v>0</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1233" t="b">
         <v>0</v>
@@ -22181,7 +22181,7 @@
         <v>0</v>
       </c>
       <c r="D1234" t="n">
-        <v>0</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1234" t="b">
         <v>0</v>
@@ -22200,7 +22200,7 @@
         <v>0</v>
       </c>
       <c r="D1235" t="n">
-        <v>0</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1235" t="b">
         <v>1</v>
@@ -22217,7 +22217,7 @@
         <v>0</v>
       </c>
       <c r="D1236" t="n">
-        <v>0</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1236" t="b">
         <v>0</v>
@@ -22234,7 +22234,7 @@
         <v>0</v>
       </c>
       <c r="D1237" t="n">
-        <v>0</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1237" t="b">
         <v>0</v>
@@ -22251,7 +22251,7 @@
         <v>0</v>
       </c>
       <c r="D1238" t="n">
-        <v>0</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1238" t="b">
         <v>0</v>
@@ -22270,7 +22270,7 @@
         <v>0</v>
       </c>
       <c r="D1239" t="n">
-        <v>0</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1239" t="b">
         <v>1</v>
@@ -22289,7 +22289,7 @@
         <v>0</v>
       </c>
       <c r="D1240" t="n">
-        <v>0</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1240" t="b">
         <v>1</v>
@@ -22306,7 +22306,7 @@
         <v>0</v>
       </c>
       <c r="D1241" t="n">
-        <v>0</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1241" t="b">
         <v>0</v>
@@ -22325,7 +22325,7 @@
         <v>0</v>
       </c>
       <c r="D1242" t="n">
-        <v>0</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1242" t="b">
         <v>1</v>
@@ -22342,7 +22342,7 @@
         <v>0</v>
       </c>
       <c r="D1243" t="n">
-        <v>0</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1243" t="b">
         <v>0</v>
@@ -22669,13 +22669,13 @@
         </is>
       </c>
       <c r="B1262" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C1262" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1262" t="n">
-        <v>0</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1262" t="b">
         <v>1</v>
@@ -22688,7 +22688,7 @@
         </is>
       </c>
       <c r="B1263" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C1263" t="n">
         <v>0</v>
@@ -22708,10 +22708,10 @@
       </c>
       <c r="B1264" t="inlineStr"/>
       <c r="C1264" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1264" t="n">
-        <v>0</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1264" t="b">
         <v>0</v>
@@ -22725,10 +22725,10 @@
       </c>
       <c r="B1265" t="inlineStr"/>
       <c r="C1265" t="n">
-        <v>0</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1265" t="n">
-        <v>0</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1265" t="b">
         <v>0</v>
@@ -22742,10 +22742,10 @@
       </c>
       <c r="B1266" t="inlineStr"/>
       <c r="C1266" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1266" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="E1266" t="b">
         <v>0</v>
@@ -22761,10 +22761,10 @@
         <v>-2</v>
       </c>
       <c r="C1267" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D1267" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1267" t="b">
         <v>1</v>
@@ -22778,10 +22778,10 @@
       </c>
       <c r="B1268" t="inlineStr"/>
       <c r="C1268" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-1.428571428571429</v>
       </c>
       <c r="D1268" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1268" t="b">
         <v>0</v>
@@ -22794,13 +22794,13 @@
         </is>
       </c>
       <c r="B1269" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C1269" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-1.428571428571429</v>
       </c>
       <c r="D1269" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1269" t="b">
         <v>1</v>
@@ -22814,10 +22814,10 @@
       </c>
       <c r="B1270" t="inlineStr"/>
       <c r="C1270" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1270" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E1270" t="b">
         <v>0</v>
@@ -22831,7 +22831,7 @@
       </c>
       <c r="B1271" t="inlineStr"/>
       <c r="C1271" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1271" t="n">
         <v>-0.1333333333333333</v>
@@ -22848,10 +22848,10 @@
       </c>
       <c r="B1272" t="inlineStr"/>
       <c r="C1272" t="n">
-        <v>-0.5714285714285714</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1272" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1272" t="b">
         <v>0</v>
@@ -22865,10 +22865,10 @@
       </c>
       <c r="B1273" t="inlineStr"/>
       <c r="C1273" t="n">
-        <v>-0.5714285714285714</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D1273" t="n">
-        <v>-0.1333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E1273" t="b">
         <v>0</v>
@@ -22882,10 +22882,10 @@
       </c>
       <c r="B1274" t="inlineStr"/>
       <c r="C1274" t="n">
-        <v>-0.2857142857142857</v>
+        <v>1.428571428571429</v>
       </c>
       <c r="D1274" t="n">
-        <v>-0.1333333333333333</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1274" t="b">
         <v>0</v>
@@ -22901,10 +22901,10 @@
         <v>0</v>
       </c>
       <c r="C1275" t="n">
-        <v>0</v>
+        <v>1.714285714285714</v>
       </c>
       <c r="D1275" t="n">
-        <v>-0.1333333333333333</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1275" t="b">
         <v>1</v>
@@ -22920,10 +22920,10 @@
         <v>0</v>
       </c>
       <c r="C1276" t="n">
-        <v>0</v>
+        <v>1.428571428571429</v>
       </c>
       <c r="D1276" t="n">
-        <v>-0.1333333333333333</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1276" t="b">
         <v>1</v>
@@ -22936,13 +22936,13 @@
         </is>
       </c>
       <c r="B1277" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C1277" t="n">
-        <v>0</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D1277" t="n">
-        <v>-0.1333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E1277" t="b">
         <v>1</v>
@@ -22956,10 +22956,10 @@
       </c>
       <c r="B1278" t="inlineStr"/>
       <c r="C1278" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1278" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1278" t="b">
         <v>0</v>
@@ -22978,7 +22978,7 @@
         <v>0</v>
       </c>
       <c r="D1279" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1279" t="b">
         <v>1</v>
@@ -22994,10 +22994,10 @@
         <v>0</v>
       </c>
       <c r="C1280" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1280" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1280" t="b">
         <v>1</v>
@@ -23011,10 +23011,10 @@
       </c>
       <c r="B1281" t="inlineStr"/>
       <c r="C1281" t="n">
-        <v>0</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1281" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1281" t="b">
         <v>0</v>
@@ -23030,10 +23030,10 @@
         <v>0</v>
       </c>
       <c r="C1282" t="n">
-        <v>0</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1282" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1282" t="b">
         <v>1</v>
@@ -23047,10 +23047,10 @@
       </c>
       <c r="B1283" t="inlineStr"/>
       <c r="C1283" t="n">
-        <v>0</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1283" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1283" t="b">
         <v>0</v>
@@ -23063,13 +23063,13 @@
         </is>
       </c>
       <c r="B1284" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="C1284" t="n">
-        <v>0</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D1284" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1284" t="b">
         <v>1</v>
@@ -23085,10 +23085,10 @@
         <v>0</v>
       </c>
       <c r="C1285" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1285" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1285" t="b">
         <v>1</v>
@@ -23102,10 +23102,10 @@
       </c>
       <c r="B1286" t="inlineStr"/>
       <c r="C1286" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1286" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1286" t="b">
         <v>0</v>
@@ -23121,10 +23121,10 @@
         <v>0</v>
       </c>
       <c r="C1287" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1287" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1287" t="b">
         <v>1</v>
@@ -23138,10 +23138,10 @@
       </c>
       <c r="B1288" t="inlineStr"/>
       <c r="C1288" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1288" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1288" t="b">
         <v>0</v>
@@ -23155,10 +23155,10 @@
       </c>
       <c r="B1289" t="inlineStr"/>
       <c r="C1289" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1289" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1289" t="b">
         <v>0</v>
@@ -23174,10 +23174,10 @@
         <v>0</v>
       </c>
       <c r="C1290" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1290" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1290" t="b">
         <v>1</v>
@@ -23196,7 +23196,7 @@
         <v>0</v>
       </c>
       <c r="D1291" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1291" t="b">
         <v>1</v>
@@ -23213,7 +23213,7 @@
         <v>0</v>
       </c>
       <c r="D1292" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E1292" t="b">
         <v>0</v>
@@ -23232,7 +23232,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1293" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1293" t="b">
         <v>1</v>
@@ -23251,7 +23251,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1294" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E1294" t="b">
         <v>1</v>
@@ -23268,7 +23268,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1295" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1295" t="b">
         <v>0</v>
@@ -23287,7 +23287,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1296" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1296" t="b">
         <v>1</v>
@@ -23306,7 +23306,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1297" t="n">
-        <v>-0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1297" t="b">
         <v>1</v>
@@ -23323,7 +23323,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1298" t="n">
-        <v>-0.1</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1298" t="b">
         <v>0</v>
@@ -23340,7 +23340,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1299" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="E1299" t="b">
         <v>0</v>
@@ -23357,7 +23357,7 @@
         <v>0</v>
       </c>
       <c r="D1300" t="n">
-        <v>-0.1</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1300" t="b">
         <v>0</v>
@@ -23374,7 +23374,7 @@
         <v>0</v>
       </c>
       <c r="D1301" t="n">
-        <v>-0.1</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1301" t="b">
         <v>0</v>
@@ -23391,7 +23391,7 @@
         <v>0</v>
       </c>
       <c r="D1302" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="E1302" t="b">
         <v>0</v>
@@ -23408,7 +23408,7 @@
         <v>0</v>
       </c>
       <c r="D1303" t="n">
-        <v>-0.1</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1303" t="b">
         <v>0</v>
@@ -23425,7 +23425,7 @@
         <v>0</v>
       </c>
       <c r="D1304" t="n">
-        <v>-0.1</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1304" t="b">
         <v>0</v>
@@ -23442,7 +23442,7 @@
         <v>0</v>
       </c>
       <c r="D1305" t="n">
-        <v>-0.1</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1305" t="b">
         <v>0</v>
@@ -23459,7 +23459,7 @@
         <v>0</v>
       </c>
       <c r="D1306" t="n">
-        <v>-0.1</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1306" t="b">
         <v>0</v>
@@ -23476,7 +23476,7 @@
         <v>0</v>
       </c>
       <c r="D1307" t="n">
-        <v>-0.1</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1307" t="b">
         <v>0</v>
@@ -23493,7 +23493,7 @@
         <v>0</v>
       </c>
       <c r="D1308" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="E1308" t="b">
         <v>0</v>
@@ -23510,7 +23510,7 @@
         <v>0</v>
       </c>
       <c r="D1309" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="E1309" t="b">
         <v>0</v>
@@ -23527,7 +23527,7 @@
         <v>0</v>
       </c>
       <c r="D1310" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="E1310" t="b">
         <v>0</v>
@@ -23544,7 +23544,7 @@
         <v>0</v>
       </c>
       <c r="D1311" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="E1311" t="b">
         <v>0</v>
@@ -23561,7 +23561,7 @@
         <v>0</v>
       </c>
       <c r="D1312" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="E1312" t="b">
         <v>0</v>
@@ -23578,7 +23578,7 @@
         <v>0</v>
       </c>
       <c r="D1313" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="E1313" t="b">
         <v>0</v>
@@ -24054,13 +24054,13 @@
         </is>
       </c>
       <c r="B1341" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C1341" t="n">
-        <v>0</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D1341" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E1341" t="b">
         <v>1</v>
@@ -24074,10 +24074,10 @@
       </c>
       <c r="B1342" t="inlineStr"/>
       <c r="C1342" t="n">
-        <v>0</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D1342" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E1342" t="b">
         <v>0</v>
@@ -24093,10 +24093,10 @@
         <v>0</v>
       </c>
       <c r="C1343" t="n">
-        <v>0</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D1343" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E1343" t="b">
         <v>1</v>
@@ -24110,10 +24110,10 @@
       </c>
       <c r="B1344" t="inlineStr"/>
       <c r="C1344" t="n">
-        <v>0</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D1344" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E1344" t="b">
         <v>0</v>
@@ -24129,10 +24129,10 @@
         <v>0</v>
       </c>
       <c r="C1345" t="n">
-        <v>0</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D1345" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E1345" t="b">
         <v>1</v>
@@ -24146,10 +24146,10 @@
       </c>
       <c r="B1346" t="inlineStr"/>
       <c r="C1346" t="n">
-        <v>0</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D1346" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E1346" t="b">
         <v>0</v>
@@ -24165,10 +24165,10 @@
         <v>0</v>
       </c>
       <c r="C1347" t="n">
-        <v>0</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D1347" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E1347" t="b">
         <v>1</v>
@@ -24182,10 +24182,10 @@
       </c>
       <c r="B1348" t="inlineStr"/>
       <c r="C1348" t="n">
-        <v>0</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D1348" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E1348" t="b">
         <v>0</v>
@@ -24202,7 +24202,7 @@
         <v>0</v>
       </c>
       <c r="D1349" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E1349" t="b">
         <v>0</v>
@@ -24215,13 +24215,13 @@
         </is>
       </c>
       <c r="B1350" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C1350" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1350" t="n">
-        <v>0</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1350" t="b">
         <v>1</v>
@@ -24235,10 +24235,10 @@
       </c>
       <c r="B1351" t="inlineStr"/>
       <c r="C1351" t="n">
-        <v>0</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1351" t="n">
-        <v>0</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1351" t="b">
         <v>0</v>
@@ -24251,13 +24251,13 @@
         </is>
       </c>
       <c r="B1352" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="C1352" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D1352" t="n">
-        <v>0</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E1352" t="b">
         <v>1</v>
@@ -24273,10 +24273,10 @@
         <v>0</v>
       </c>
       <c r="C1353" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D1353" t="n">
-        <v>0</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E1353" t="b">
         <v>1</v>
@@ -24292,10 +24292,10 @@
         <v>0</v>
       </c>
       <c r="C1354" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D1354" t="n">
-        <v>0</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E1354" t="b">
         <v>1</v>
@@ -24309,10 +24309,10 @@
       </c>
       <c r="B1355" t="inlineStr"/>
       <c r="C1355" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D1355" t="n">
-        <v>0</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E1355" t="b">
         <v>0</v>
@@ -24328,10 +24328,10 @@
         <v>0</v>
       </c>
       <c r="C1356" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D1356" t="n">
-        <v>0</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E1356" t="b">
         <v>1</v>
@@ -24347,10 +24347,10 @@
         <v>0</v>
       </c>
       <c r="C1357" t="n">
-        <v>0</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D1357" t="n">
-        <v>0</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E1357" t="b">
         <v>1</v>
@@ -24366,10 +24366,10 @@
         <v>0</v>
       </c>
       <c r="C1358" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1358" t="n">
-        <v>0</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E1358" t="b">
         <v>1</v>
@@ -24386,7 +24386,7 @@
         <v>0</v>
       </c>
       <c r="D1359" t="n">
-        <v>0</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E1359" t="b">
         <v>0</v>
@@ -24403,7 +24403,7 @@
         <v>0</v>
       </c>
       <c r="D1360" t="n">
-        <v>0</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E1360" t="b">
         <v>0</v>
@@ -24422,7 +24422,7 @@
         <v>0</v>
       </c>
       <c r="D1361" t="n">
-        <v>0</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E1361" t="b">
         <v>1</v>
@@ -24439,7 +24439,7 @@
         <v>0</v>
       </c>
       <c r="D1362" t="n">
-        <v>0</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E1362" t="b">
         <v>0</v>
@@ -24456,7 +24456,7 @@
         <v>0</v>
       </c>
       <c r="D1363" t="n">
-        <v>0</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E1363" t="b">
         <v>0</v>
@@ -24473,7 +24473,7 @@
         <v>0</v>
       </c>
       <c r="D1364" t="n">
-        <v>0</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E1364" t="b">
         <v>0</v>
@@ -24490,7 +24490,7 @@
         <v>0</v>
       </c>
       <c r="D1365" t="n">
-        <v>0</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E1365" t="b">
         <v>0</v>
@@ -24507,7 +24507,7 @@
         <v>0</v>
       </c>
       <c r="D1366" t="n">
-        <v>0</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E1366" t="b">
         <v>0</v>
@@ -24526,7 +24526,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1367" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1367" t="b">
         <v>1</v>
@@ -24543,7 +24543,7 @@
         <v>0.5714285714285714</v>
       </c>
       <c r="D1368" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="E1368" t="b">
         <v>0</v>
@@ -24560,7 +24560,7 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="D1369" t="n">
-        <v>0.2</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E1369" t="b">
         <v>0</v>
@@ -24577,7 +24577,7 @@
         <v>1.142857142857143</v>
       </c>
       <c r="D1370" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="E1370" t="b">
         <v>0</v>
@@ -24594,7 +24594,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="D1371" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2</v>
       </c>
       <c r="E1371" t="b">
         <v>0</v>
@@ -24613,7 +24613,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="D1372" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="E1372" t="b">
         <v>1</v>
@@ -24632,7 +24632,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="D1373" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="E1373" t="b">
         <v>1</v>
@@ -24649,7 +24649,7 @@
         <v>1.142857142857143</v>
       </c>
       <c r="D1374" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="E1374" t="b">
         <v>0</v>
@@ -24668,7 +24668,7 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="D1375" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="E1375" t="b">
         <v>1</v>
@@ -24687,7 +24687,7 @@
         <v>0.5714285714285714</v>
       </c>
       <c r="D1376" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="E1376" t="b">
         <v>1</v>
@@ -24700,13 +24700,13 @@
         </is>
       </c>
       <c r="B1377" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="C1377" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="D1377" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E1377" t="b">
         <v>1</v>
@@ -24720,10 +24720,10 @@
       </c>
       <c r="B1378" t="inlineStr"/>
       <c r="C1378" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1378" t="n">
-        <v>0.3333333333333333</v>
+        <v>-0.1</v>
       </c>
       <c r="E1378" t="b">
         <v>0</v>
@@ -24739,10 +24739,10 @@
         <v>0</v>
       </c>
       <c r="C1379" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1379" t="n">
-        <v>0.3333333333333333</v>
+        <v>-0.1</v>
       </c>
       <c r="E1379" t="b">
         <v>1</v>
@@ -24756,10 +24756,10 @@
       </c>
       <c r="B1380" t="inlineStr"/>
       <c r="C1380" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1380" t="n">
-        <v>0.3333333333333333</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E1380" t="b">
         <v>0</v>
@@ -24773,10 +24773,10 @@
       </c>
       <c r="B1381" t="inlineStr"/>
       <c r="C1381" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1381" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1381" t="b">
         <v>0</v>
@@ -24790,10 +24790,10 @@
       </c>
       <c r="B1382" t="inlineStr"/>
       <c r="C1382" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1382" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1382" t="b">
         <v>0</v>
@@ -24809,10 +24809,10 @@
         <v>0</v>
       </c>
       <c r="C1383" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1383" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1383" t="b">
         <v>1</v>
@@ -24826,10 +24826,10 @@
       </c>
       <c r="B1384" t="inlineStr"/>
       <c r="C1384" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1384" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1384" t="b">
         <v>0</v>
@@ -24846,7 +24846,7 @@
         <v>0</v>
       </c>
       <c r="D1385" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1385" t="b">
         <v>0</v>
@@ -24863,7 +24863,7 @@
         <v>0</v>
       </c>
       <c r="D1386" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1386" t="b">
         <v>0</v>
@@ -24882,7 +24882,7 @@
         <v>0</v>
       </c>
       <c r="D1387" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1387" t="b">
         <v>1</v>
@@ -24901,7 +24901,7 @@
         <v>0</v>
       </c>
       <c r="D1388" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1388" t="b">
         <v>1</v>
@@ -24918,7 +24918,7 @@
         <v>0</v>
       </c>
       <c r="D1389" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1389" t="b">
         <v>0</v>
@@ -24935,7 +24935,7 @@
         <v>0</v>
       </c>
       <c r="D1390" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1390" t="b">
         <v>0</v>
@@ -24952,7 +24952,7 @@
         <v>0</v>
       </c>
       <c r="D1391" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1391" t="b">
         <v>0</v>
@@ -24969,7 +24969,7 @@
         <v>0</v>
       </c>
       <c r="D1392" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1392" t="b">
         <v>0</v>
@@ -24986,7 +24986,7 @@
         <v>0</v>
       </c>
       <c r="D1393" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1393" t="b">
         <v>0</v>
@@ -24999,13 +24999,13 @@
         </is>
       </c>
       <c r="B1394" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C1394" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1394" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1394" t="b">
         <v>1</v>
@@ -25019,10 +25019,10 @@
       </c>
       <c r="B1395" t="inlineStr"/>
       <c r="C1395" t="n">
-        <v>0</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1395" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E1395" t="b">
         <v>0</v>
@@ -25036,10 +25036,10 @@
       </c>
       <c r="B1396" t="inlineStr"/>
       <c r="C1396" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1396" t="n">
-        <v>0.3333333333333333</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1396" t="b">
         <v>0</v>
@@ -25053,10 +25053,10 @@
       </c>
       <c r="B1397" t="inlineStr"/>
       <c r="C1397" t="n">
-        <v>0</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D1397" t="n">
-        <v>0.2666666666666667</v>
+        <v>-0.2</v>
       </c>
       <c r="E1397" t="b">
         <v>0</v>
@@ -25072,10 +25072,10 @@
         <v>2</v>
       </c>
       <c r="C1398" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1398" t="n">
-        <v>0.2666666666666667</v>
+        <v>-0.2</v>
       </c>
       <c r="E1398" t="b">
         <v>1</v>
@@ -25089,10 +25089,10 @@
       </c>
       <c r="B1399" t="inlineStr"/>
       <c r="C1399" t="n">
-        <v>0.5714285714285714</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1399" t="n">
-        <v>0.2666666666666667</v>
+        <v>-0.2</v>
       </c>
       <c r="E1399" t="b">
         <v>0</v>
@@ -25106,10 +25106,10 @@
       </c>
       <c r="B1400" t="inlineStr"/>
       <c r="C1400" t="n">
-        <v>0.8571428571428571</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1400" t="n">
-        <v>0.2666666666666667</v>
+        <v>-0.2</v>
       </c>
       <c r="E1400" t="b">
         <v>0</v>
@@ -25125,10 +25125,10 @@
         <v>0</v>
       </c>
       <c r="C1401" t="n">
-        <v>0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="D1401" t="n">
-        <v>0.2</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1401" t="b">
         <v>1</v>
@@ -25142,10 +25142,10 @@
       </c>
       <c r="B1402" t="inlineStr"/>
       <c r="C1402" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1402" t="n">
-        <v>0.2</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1402" t="b">
         <v>0</v>
@@ -25159,10 +25159,10 @@
       </c>
       <c r="B1403" t="inlineStr"/>
       <c r="C1403" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D1403" t="n">
-        <v>0.2</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1403" t="b">
         <v>0</v>
@@ -25179,7 +25179,7 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="D1404" t="n">
-        <v>0.2</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1404" t="b">
         <v>0</v>
@@ -25196,7 +25196,7 @@
         <v>0.5714285714285714</v>
       </c>
       <c r="D1405" t="n">
-        <v>0.2</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1405" t="b">
         <v>0</v>
@@ -25215,7 +25215,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1406" t="n">
-        <v>0.2</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1406" t="b">
         <v>1</v>
@@ -25232,7 +25232,7 @@
         <v>0</v>
       </c>
       <c r="D1407" t="n">
-        <v>0.2</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1407" t="b">
         <v>0</v>
@@ -25244,15 +25244,36 @@
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="B1408" t="inlineStr"/>
+      <c r="B1408" t="n">
+        <v>0</v>
+      </c>
       <c r="C1408" t="n">
         <v>0</v>
       </c>
       <c r="D1408" t="n">
-        <v>0.2</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1408" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="A1409" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B1409" t="n">
+        <v>-2</v>
+      </c>
+      <c r="C1409" t="n">
+        <v>-0.2857142857142857</v>
+      </c>
+      <c r="D1409" t="n">
+        <v>-0.1333333333333333</v>
+      </c>
+      <c r="E1409" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -25285,7 +25306,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-05-25 to 2026-03-31 | Publication days: 473</t>
+          <t>Coverage: 2022-05-25 to 2026-04-01 | Publication days: 475</t>
         </is>
       </c>
     </row>

--- a/data/AU.xlsx
+++ b/data/AU.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1409"/>
+  <dimension ref="A1:E1410"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -25274,6 +25274,23 @@
       </c>
       <c r="E1409" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="A1410" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B1410" t="inlineStr"/>
+      <c r="C1410" t="n">
+        <v>-0.5714285714285714</v>
+      </c>
+      <c r="D1410" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E1410" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -25306,7 +25323,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-05-25 to 2026-04-01 | Publication days: 475</t>
+          <t>Coverage: 2022-05-25 to 2026-04-02 | Publication days: 475</t>
         </is>
       </c>
     </row>

--- a/data/AU.xlsx
+++ b/data/AU.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1410"/>
+  <dimension ref="A1:E1411"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21825,13 +21825,13 @@
         </is>
       </c>
       <c r="B1214" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="C1214" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1214" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E1214" t="b">
         <v>1</v>
@@ -21847,10 +21847,10 @@
         <v>0</v>
       </c>
       <c r="C1215" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1215" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.6</v>
       </c>
       <c r="E1215" t="b">
         <v>1</v>
@@ -21864,10 +21864,10 @@
       </c>
       <c r="B1216" t="inlineStr"/>
       <c r="C1216" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1216" t="n">
-        <v>-0.5</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1216" t="b">
         <v>0</v>
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="B1217" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C1217" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1217" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1217" t="b">
         <v>1</v>
@@ -21899,13 +21899,13 @@
         </is>
       </c>
       <c r="B1218" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C1218" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D1218" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.2</v>
       </c>
       <c r="E1218" t="b">
         <v>1</v>
@@ -21919,10 +21919,10 @@
       </c>
       <c r="B1219" t="inlineStr"/>
       <c r="C1219" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D1219" t="n">
-        <v>-0.3</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E1219" t="b">
         <v>0</v>
@@ -21936,10 +21936,10 @@
       </c>
       <c r="B1220" t="inlineStr"/>
       <c r="C1220" t="n">
-        <v>-0.2857142857142857</v>
+        <v>1.285714285714286</v>
       </c>
       <c r="D1220" t="n">
-        <v>-0.2333333333333333</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1220" t="b">
         <v>0</v>
@@ -21953,10 +21953,10 @@
       </c>
       <c r="B1221" t="inlineStr"/>
       <c r="C1221" t="n">
-        <v>0</v>
+        <v>2.142857142857143</v>
       </c>
       <c r="D1221" t="n">
-        <v>-0.1333333333333333</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E1221" t="b">
         <v>0</v>
@@ -21970,10 +21970,10 @@
       </c>
       <c r="B1222" t="inlineStr"/>
       <c r="C1222" t="n">
-        <v>0</v>
+        <v>2.571428571428572</v>
       </c>
       <c r="D1222" t="n">
-        <v>-0.1333333333333333</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="E1222" t="b">
         <v>0</v>
@@ -21986,13 +21986,13 @@
         </is>
       </c>
       <c r="B1223" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C1223" t="n">
-        <v>0</v>
+        <v>2.857142857142857</v>
       </c>
       <c r="D1223" t="n">
-        <v>-0.1333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="E1223" t="b">
         <v>1</v>
@@ -22006,10 +22006,10 @@
       </c>
       <c r="B1224" t="inlineStr"/>
       <c r="C1224" t="n">
-        <v>0</v>
+        <v>2.714285714285714</v>
       </c>
       <c r="D1224" t="n">
-        <v>-0.1333333333333333</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="E1224" t="b">
         <v>0</v>
@@ -22023,10 +22023,10 @@
       </c>
       <c r="B1225" t="inlineStr"/>
       <c r="C1225" t="n">
-        <v>0</v>
+        <v>2.571428571428572</v>
       </c>
       <c r="D1225" t="n">
-        <v>-0.1333333333333333</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="E1225" t="b">
         <v>0</v>
@@ -22040,10 +22040,10 @@
       </c>
       <c r="B1226" t="inlineStr"/>
       <c r="C1226" t="n">
-        <v>0</v>
+        <v>2.428571428571428</v>
       </c>
       <c r="D1226" t="n">
-        <v>-0.1333333333333333</v>
+        <v>0.7</v>
       </c>
       <c r="E1226" t="b">
         <v>0</v>
@@ -22059,10 +22059,10 @@
         <v>0</v>
       </c>
       <c r="C1227" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D1227" t="n">
-        <v>-0.1333333333333333</v>
+        <v>0.7</v>
       </c>
       <c r="E1227" t="b">
         <v>1</v>
@@ -22076,10 +22076,10 @@
       </c>
       <c r="B1228" t="inlineStr"/>
       <c r="C1228" t="n">
-        <v>0</v>
+        <v>1.571428571428571</v>
       </c>
       <c r="D1228" t="n">
-        <v>-0.1333333333333333</v>
+        <v>0.7</v>
       </c>
       <c r="E1228" t="b">
         <v>0</v>
@@ -22093,10 +22093,10 @@
       </c>
       <c r="B1229" t="inlineStr"/>
       <c r="C1229" t="n">
-        <v>0</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="D1229" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="E1229" t="b">
         <v>0</v>
@@ -22110,10 +22110,10 @@
       </c>
       <c r="B1230" t="inlineStr"/>
       <c r="C1230" t="n">
-        <v>0</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D1230" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="E1230" t="b">
         <v>0</v>
@@ -22127,10 +22127,10 @@
       </c>
       <c r="B1231" t="inlineStr"/>
       <c r="C1231" t="n">
-        <v>0</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D1231" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="E1231" t="b">
         <v>0</v>
@@ -22144,10 +22144,10 @@
       </c>
       <c r="B1232" t="inlineStr"/>
       <c r="C1232" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1232" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="E1232" t="b">
         <v>0</v>
@@ -22164,7 +22164,7 @@
         <v>0</v>
       </c>
       <c r="D1233" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="E1233" t="b">
         <v>0</v>
@@ -22181,7 +22181,7 @@
         <v>0</v>
       </c>
       <c r="D1234" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="E1234" t="b">
         <v>0</v>
@@ -22200,7 +22200,7 @@
         <v>0</v>
       </c>
       <c r="D1235" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="E1235" t="b">
         <v>1</v>
@@ -22217,7 +22217,7 @@
         <v>0</v>
       </c>
       <c r="D1236" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="E1236" t="b">
         <v>0</v>
@@ -22234,7 +22234,7 @@
         <v>0</v>
       </c>
       <c r="D1237" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="E1237" t="b">
         <v>0</v>
@@ -22251,7 +22251,7 @@
         <v>0</v>
       </c>
       <c r="D1238" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="E1238" t="b">
         <v>0</v>
@@ -22270,7 +22270,7 @@
         <v>0</v>
       </c>
       <c r="D1239" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="E1239" t="b">
         <v>1</v>
@@ -22289,7 +22289,7 @@
         <v>0</v>
       </c>
       <c r="D1240" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="E1240" t="b">
         <v>1</v>
@@ -22306,7 +22306,7 @@
         <v>0</v>
       </c>
       <c r="D1241" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="E1241" t="b">
         <v>0</v>
@@ -22325,7 +22325,7 @@
         <v>0</v>
       </c>
       <c r="D1242" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="E1242" t="b">
         <v>1</v>
@@ -22342,7 +22342,7 @@
         <v>0</v>
       </c>
       <c r="D1243" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="E1243" t="b">
         <v>0</v>
@@ -22359,7 +22359,7 @@
         <v>0</v>
       </c>
       <c r="D1244" t="n">
-        <v>0</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="E1244" t="b">
         <v>0</v>
@@ -22378,7 +22378,7 @@
         <v>0</v>
       </c>
       <c r="D1245" t="n">
-        <v>0</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="E1245" t="b">
         <v>1</v>
@@ -22397,7 +22397,7 @@
         <v>0</v>
       </c>
       <c r="D1246" t="n">
-        <v>0</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="E1246" t="b">
         <v>1</v>
@@ -22414,7 +22414,7 @@
         <v>0</v>
       </c>
       <c r="D1247" t="n">
-        <v>0</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="E1247" t="b">
         <v>0</v>
@@ -22431,7 +22431,7 @@
         <v>0</v>
       </c>
       <c r="D1248" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E1248" t="b">
         <v>0</v>
@@ -22448,7 +22448,7 @@
         <v>0</v>
       </c>
       <c r="D1249" t="n">
-        <v>0</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="E1249" t="b">
         <v>0</v>
@@ -22465,7 +22465,7 @@
         <v>0</v>
       </c>
       <c r="D1250" t="n">
-        <v>0</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="E1250" t="b">
         <v>0</v>
@@ -22482,7 +22482,7 @@
         <v>0</v>
       </c>
       <c r="D1251" t="n">
-        <v>0</v>
+        <v>0.3666666666666666</v>
       </c>
       <c r="E1251" t="b">
         <v>0</v>
@@ -22499,7 +22499,7 @@
         <v>0</v>
       </c>
       <c r="D1252" t="n">
-        <v>0</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="E1252" t="b">
         <v>0</v>
@@ -22518,7 +22518,7 @@
         <v>0</v>
       </c>
       <c r="D1253" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E1253" t="b">
         <v>1</v>
@@ -22535,7 +22535,7 @@
         <v>0</v>
       </c>
       <c r="D1254" t="n">
-        <v>0</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1254" t="b">
         <v>0</v>
@@ -22554,7 +22554,7 @@
         <v>0</v>
       </c>
       <c r="D1255" t="n">
-        <v>0</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1255" t="b">
         <v>1</v>
@@ -22669,13 +22669,13 @@
         </is>
       </c>
       <c r="B1262" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="C1262" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1262" t="n">
-        <v>0.06666666666666667</v>
+        <v>-0.1</v>
       </c>
       <c r="E1262" t="b">
         <v>1</v>
@@ -22688,13 +22688,13 @@
         </is>
       </c>
       <c r="B1263" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="C1263" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1263" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="E1263" t="b">
         <v>1</v>
@@ -22708,10 +22708,10 @@
       </c>
       <c r="B1264" t="inlineStr"/>
       <c r="C1264" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D1264" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.3</v>
       </c>
       <c r="E1264" t="b">
         <v>0</v>
@@ -22725,10 +22725,10 @@
       </c>
       <c r="B1265" t="inlineStr"/>
       <c r="C1265" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-1.714285714285714</v>
       </c>
       <c r="D1265" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E1265" t="b">
         <v>0</v>
@@ -22742,10 +22742,10 @@
       </c>
       <c r="B1266" t="inlineStr"/>
       <c r="C1266" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-2.142857142857143</v>
       </c>
       <c r="D1266" t="n">
-        <v>-0.2</v>
+        <v>-0.5</v>
       </c>
       <c r="E1266" t="b">
         <v>0</v>
@@ -22758,13 +22758,13 @@
         </is>
       </c>
       <c r="B1267" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="C1267" t="n">
-        <v>-1.142857142857143</v>
+        <v>-2.571428571428572</v>
       </c>
       <c r="D1267" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.6</v>
       </c>
       <c r="E1267" t="b">
         <v>1</v>
@@ -22778,10 +22778,10 @@
       </c>
       <c r="B1268" t="inlineStr"/>
       <c r="C1268" t="n">
-        <v>-1.428571428571429</v>
+        <v>-3</v>
       </c>
       <c r="D1268" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.7</v>
       </c>
       <c r="E1268" t="b">
         <v>0</v>
@@ -22794,13 +22794,13 @@
         </is>
       </c>
       <c r="B1269" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C1269" t="n">
-        <v>-1.428571428571429</v>
+        <v>-2.571428571428572</v>
       </c>
       <c r="D1269" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.7</v>
       </c>
       <c r="E1269" t="b">
         <v>1</v>
@@ -22814,10 +22814,10 @@
       </c>
       <c r="B1270" t="inlineStr"/>
       <c r="C1270" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-2.142857142857143</v>
       </c>
       <c r="D1270" t="n">
-        <v>-0.2</v>
+        <v>-0.7</v>
       </c>
       <c r="E1270" t="b">
         <v>0</v>
@@ -22831,10 +22831,10 @@
       </c>
       <c r="B1271" t="inlineStr"/>
       <c r="C1271" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-1.714285714285714</v>
       </c>
       <c r="D1271" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.7</v>
       </c>
       <c r="E1271" t="b">
         <v>0</v>
@@ -22848,10 +22848,10 @@
       </c>
       <c r="B1272" t="inlineStr"/>
       <c r="C1272" t="n">
-        <v>0.2857142857142857</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D1272" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.7</v>
       </c>
       <c r="E1272" t="b">
         <v>0</v>
@@ -22865,10 +22865,10 @@
       </c>
       <c r="B1273" t="inlineStr"/>
       <c r="C1273" t="n">
-        <v>0.8571428571428571</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1273" t="n">
-        <v>0</v>
+        <v>-0.7</v>
       </c>
       <c r="E1273" t="b">
         <v>0</v>
@@ -22882,10 +22882,10 @@
       </c>
       <c r="B1274" t="inlineStr"/>
       <c r="C1274" t="n">
-        <v>1.428571428571429</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1274" t="n">
-        <v>0.06666666666666667</v>
+        <v>-0.7</v>
       </c>
       <c r="E1274" t="b">
         <v>0</v>
@@ -22901,10 +22901,10 @@
         <v>0</v>
       </c>
       <c r="C1275" t="n">
-        <v>1.714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D1275" t="n">
-        <v>0.06666666666666667</v>
+        <v>-0.7</v>
       </c>
       <c r="E1275" t="b">
         <v>1</v>
@@ -22920,10 +22920,10 @@
         <v>0</v>
       </c>
       <c r="C1276" t="n">
-        <v>1.428571428571429</v>
+        <v>0</v>
       </c>
       <c r="D1276" t="n">
-        <v>0.06666666666666667</v>
+        <v>-0.7</v>
       </c>
       <c r="E1276" t="b">
         <v>1</v>
@@ -22939,10 +22939,10 @@
         <v>-2</v>
       </c>
       <c r="C1277" t="n">
-        <v>0.8571428571428571</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1277" t="n">
-        <v>0</v>
+        <v>-0.7666666666666667</v>
       </c>
       <c r="E1277" t="b">
         <v>1</v>
@@ -22956,10 +22956,10 @@
       </c>
       <c r="B1278" t="inlineStr"/>
       <c r="C1278" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1278" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.8333333333333334</v>
       </c>
       <c r="E1278" t="b">
         <v>0</v>
@@ -22975,10 +22975,10 @@
         <v>0</v>
       </c>
       <c r="C1279" t="n">
-        <v>0</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1279" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.8333333333333334</v>
       </c>
       <c r="E1279" t="b">
         <v>1</v>
@@ -22994,10 +22994,10 @@
         <v>0</v>
       </c>
       <c r="C1280" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1280" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.8333333333333334</v>
       </c>
       <c r="E1280" t="b">
         <v>1</v>
@@ -23014,7 +23014,7 @@
         <v>-0.5714285714285714</v>
       </c>
       <c r="D1281" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.8333333333333334</v>
       </c>
       <c r="E1281" t="b">
         <v>0</v>
@@ -23033,7 +23033,7 @@
         <v>-0.5714285714285714</v>
       </c>
       <c r="D1282" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.8333333333333334</v>
       </c>
       <c r="E1282" t="b">
         <v>1</v>
@@ -23050,7 +23050,7 @@
         <v>-0.5714285714285714</v>
       </c>
       <c r="D1283" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.8333333333333334</v>
       </c>
       <c r="E1283" t="b">
         <v>0</v>
@@ -23069,7 +23069,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D1284" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.9333333333333333</v>
       </c>
       <c r="E1284" t="b">
         <v>1</v>
@@ -23088,7 +23088,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1285" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.9333333333333333</v>
       </c>
       <c r="E1285" t="b">
         <v>1</v>
@@ -23105,7 +23105,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1286" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.9333333333333333</v>
       </c>
       <c r="E1286" t="b">
         <v>0</v>
@@ -23124,7 +23124,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1287" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.9333333333333333</v>
       </c>
       <c r="E1287" t="b">
         <v>1</v>
@@ -23141,7 +23141,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1288" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.9333333333333333</v>
       </c>
       <c r="E1288" t="b">
         <v>0</v>
@@ -23158,7 +23158,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1289" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.9333333333333333</v>
       </c>
       <c r="E1289" t="b">
         <v>0</v>
@@ -23177,7 +23177,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1290" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.9333333333333333</v>
       </c>
       <c r="E1290" t="b">
         <v>1</v>
@@ -23196,7 +23196,7 @@
         <v>0</v>
       </c>
       <c r="D1291" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.9333333333333333</v>
       </c>
       <c r="E1291" t="b">
         <v>1</v>
@@ -23213,7 +23213,7 @@
         <v>0</v>
       </c>
       <c r="D1292" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.8333333333333334</v>
       </c>
       <c r="E1292" t="b">
         <v>0</v>
@@ -23232,7 +23232,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1293" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.8333333333333334</v>
       </c>
       <c r="E1293" t="b">
         <v>1</v>
@@ -23251,7 +23251,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1294" t="n">
-        <v>-0.2</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E1294" t="b">
         <v>1</v>
@@ -23268,7 +23268,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1295" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E1295" t="b">
         <v>0</v>
@@ -23287,7 +23287,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1296" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1296" t="b">
         <v>1</v>
@@ -23306,7 +23306,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1297" t="n">
-        <v>0</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1297" t="b">
         <v>1</v>
@@ -23323,7 +23323,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1298" t="n">
-        <v>0.06666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1298" t="b">
         <v>0</v>
@@ -23340,7 +23340,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1299" t="n">
-        <v>0</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1299" t="b">
         <v>0</v>
@@ -23357,7 +23357,7 @@
         <v>0</v>
       </c>
       <c r="D1300" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1300" t="b">
         <v>0</v>
@@ -23374,7 +23374,7 @@
         <v>0</v>
       </c>
       <c r="D1301" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1301" t="b">
         <v>0</v>
@@ -23391,7 +23391,7 @@
         <v>0</v>
       </c>
       <c r="D1302" t="n">
-        <v>-0.2</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1302" t="b">
         <v>0</v>
@@ -23408,7 +23408,7 @@
         <v>0</v>
       </c>
       <c r="D1303" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1303" t="b">
         <v>0</v>
@@ -24054,13 +24054,13 @@
         </is>
       </c>
       <c r="B1341" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="C1341" t="n">
-        <v>0.4285714285714285</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1341" t="n">
-        <v>0.1</v>
+        <v>-0.1</v>
       </c>
       <c r="E1341" t="b">
         <v>1</v>
@@ -24074,10 +24074,10 @@
       </c>
       <c r="B1342" t="inlineStr"/>
       <c r="C1342" t="n">
-        <v>0.8571428571428571</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1342" t="n">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="E1342" t="b">
         <v>0</v>
@@ -24093,10 +24093,10 @@
         <v>0</v>
       </c>
       <c r="C1343" t="n">
-        <v>0.8571428571428571</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1343" t="n">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="E1343" t="b">
         <v>1</v>
@@ -24110,10 +24110,10 @@
       </c>
       <c r="B1344" t="inlineStr"/>
       <c r="C1344" t="n">
-        <v>0.8571428571428571</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1344" t="n">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="E1344" t="b">
         <v>0</v>
@@ -24129,10 +24129,10 @@
         <v>0</v>
       </c>
       <c r="C1345" t="n">
-        <v>0.8571428571428571</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1345" t="n">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="E1345" t="b">
         <v>1</v>
@@ -24146,10 +24146,10 @@
       </c>
       <c r="B1346" t="inlineStr"/>
       <c r="C1346" t="n">
-        <v>0.8571428571428571</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1346" t="n">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="E1346" t="b">
         <v>0</v>
@@ -24165,10 +24165,10 @@
         <v>0</v>
       </c>
       <c r="C1347" t="n">
-        <v>0.8571428571428571</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1347" t="n">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="E1347" t="b">
         <v>1</v>
@@ -24182,10 +24182,10 @@
       </c>
       <c r="B1348" t="inlineStr"/>
       <c r="C1348" t="n">
-        <v>0.4285714285714285</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1348" t="n">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="E1348" t="b">
         <v>0</v>
@@ -24202,7 +24202,7 @@
         <v>0</v>
       </c>
       <c r="D1349" t="n">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="E1349" t="b">
         <v>0</v>
@@ -24215,13 +24215,13 @@
         </is>
       </c>
       <c r="B1350" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="C1350" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1350" t="n">
-        <v>0.1333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="E1350" t="b">
         <v>1</v>
@@ -24235,10 +24235,10 @@
       </c>
       <c r="B1351" t="inlineStr"/>
       <c r="C1351" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1351" t="n">
-        <v>0.06666666666666667</v>
+        <v>-0.4</v>
       </c>
       <c r="E1351" t="b">
         <v>0</v>
@@ -24254,10 +24254,10 @@
         <v>-3</v>
       </c>
       <c r="C1352" t="n">
-        <v>-1</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D1352" t="n">
-        <v>-0.03333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="E1352" t="b">
         <v>1</v>
@@ -24273,10 +24273,10 @@
         <v>0</v>
       </c>
       <c r="C1353" t="n">
-        <v>-1</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D1353" t="n">
-        <v>-0.03333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="E1353" t="b">
         <v>1</v>
@@ -24292,10 +24292,10 @@
         <v>0</v>
       </c>
       <c r="C1354" t="n">
-        <v>-1</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D1354" t="n">
-        <v>-0.03333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="E1354" t="b">
         <v>1</v>
@@ -24309,10 +24309,10 @@
       </c>
       <c r="B1355" t="inlineStr"/>
       <c r="C1355" t="n">
-        <v>-1</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D1355" t="n">
-        <v>-0.03333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="E1355" t="b">
         <v>0</v>
@@ -24328,10 +24328,10 @@
         <v>0</v>
       </c>
       <c r="C1356" t="n">
-        <v>-1</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D1356" t="n">
-        <v>-0.03333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="E1356" t="b">
         <v>1</v>
@@ -24347,10 +24347,10 @@
         <v>0</v>
       </c>
       <c r="C1357" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1357" t="n">
-        <v>-0.03333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="E1357" t="b">
         <v>1</v>
@@ -24369,7 +24369,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1358" t="n">
-        <v>-0.03333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="E1358" t="b">
         <v>1</v>
@@ -24386,7 +24386,7 @@
         <v>0</v>
       </c>
       <c r="D1359" t="n">
-        <v>-0.03333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="E1359" t="b">
         <v>0</v>
@@ -24403,7 +24403,7 @@
         <v>0</v>
       </c>
       <c r="D1360" t="n">
-        <v>-0.03333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="E1360" t="b">
         <v>0</v>
@@ -24422,7 +24422,7 @@
         <v>0</v>
       </c>
       <c r="D1361" t="n">
-        <v>-0.03333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="E1361" t="b">
         <v>1</v>
@@ -24439,7 +24439,7 @@
         <v>0</v>
       </c>
       <c r="D1362" t="n">
-        <v>-0.03333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="E1362" t="b">
         <v>0</v>
@@ -24456,7 +24456,7 @@
         <v>0</v>
       </c>
       <c r="D1363" t="n">
-        <v>-0.03333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="E1363" t="b">
         <v>0</v>
@@ -24473,7 +24473,7 @@
         <v>0</v>
       </c>
       <c r="D1364" t="n">
-        <v>-0.03333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="E1364" t="b">
         <v>0</v>
@@ -24490,7 +24490,7 @@
         <v>0</v>
       </c>
       <c r="D1365" t="n">
-        <v>-0.03333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="E1365" t="b">
         <v>0</v>
@@ -24507,7 +24507,7 @@
         <v>0</v>
       </c>
       <c r="D1366" t="n">
-        <v>-0.03333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="E1366" t="b">
         <v>0</v>
@@ -24520,13 +24520,13 @@
         </is>
       </c>
       <c r="B1367" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="C1367" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1367" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.6</v>
       </c>
       <c r="E1367" t="b">
         <v>1</v>
@@ -24540,10 +24540,10 @@
       </c>
       <c r="B1368" t="inlineStr"/>
       <c r="C1368" t="n">
-        <v>0.5714285714285714</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1368" t="n">
-        <v>0.1</v>
+        <v>-0.7</v>
       </c>
       <c r="E1368" t="b">
         <v>0</v>
@@ -24557,10 +24557,10 @@
       </c>
       <c r="B1369" t="inlineStr"/>
       <c r="C1369" t="n">
-        <v>0.8571428571428571</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D1369" t="n">
-        <v>0.1666666666666667</v>
+        <v>-0.8</v>
       </c>
       <c r="E1369" t="b">
         <v>0</v>
@@ -24574,10 +24574,10 @@
       </c>
       <c r="B1370" t="inlineStr"/>
       <c r="C1370" t="n">
-        <v>1.142857142857143</v>
+        <v>-1.714285714285714</v>
       </c>
       <c r="D1370" t="n">
-        <v>0.2333333333333333</v>
+        <v>-0.9</v>
       </c>
       <c r="E1370" t="b">
         <v>0</v>
@@ -24591,10 +24591,10 @@
       </c>
       <c r="B1371" t="inlineStr"/>
       <c r="C1371" t="n">
-        <v>1.428571428571429</v>
+        <v>-2.142857142857143</v>
       </c>
       <c r="D1371" t="n">
-        <v>0.2</v>
+        <v>-0.9</v>
       </c>
       <c r="E1371" t="b">
         <v>0</v>
@@ -24610,10 +24610,10 @@
         <v>0</v>
       </c>
       <c r="C1372" t="n">
-        <v>1.428571428571429</v>
+        <v>-2.142857142857143</v>
       </c>
       <c r="D1372" t="n">
-        <v>0.1</v>
+        <v>-0.8</v>
       </c>
       <c r="E1372" t="b">
         <v>1</v>
@@ -24626,13 +24626,13 @@
         </is>
       </c>
       <c r="B1373" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="C1373" t="n">
-        <v>1.428571428571429</v>
+        <v>-2.571428571428572</v>
       </c>
       <c r="D1373" t="n">
-        <v>0.1</v>
+        <v>-0.9</v>
       </c>
       <c r="E1373" t="b">
         <v>1</v>
@@ -24646,10 +24646,10 @@
       </c>
       <c r="B1374" t="inlineStr"/>
       <c r="C1374" t="n">
-        <v>1.142857142857143</v>
+        <v>-2.571428571428572</v>
       </c>
       <c r="D1374" t="n">
-        <v>0.1</v>
+        <v>-1</v>
       </c>
       <c r="E1374" t="b">
         <v>0</v>
@@ -24665,10 +24665,10 @@
         <v>0</v>
       </c>
       <c r="C1375" t="n">
-        <v>0.8571428571428571</v>
+        <v>-2.142857142857143</v>
       </c>
       <c r="D1375" t="n">
-        <v>0.1</v>
+        <v>-1</v>
       </c>
       <c r="E1375" t="b">
         <v>1</v>
@@ -24684,10 +24684,10 @@
         <v>0</v>
       </c>
       <c r="C1376" t="n">
-        <v>0.5714285714285714</v>
+        <v>-1.714285714285714</v>
       </c>
       <c r="D1376" t="n">
-        <v>0.1</v>
+        <v>-1</v>
       </c>
       <c r="E1376" t="b">
         <v>1</v>
@@ -24700,13 +24700,13 @@
         </is>
       </c>
       <c r="B1377" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="C1377" t="n">
-        <v>-0.1428571428571428</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D1377" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E1377" t="b">
         <v>1</v>
@@ -24723,7 +24723,7 @@
         <v>-0.8571428571428571</v>
       </c>
       <c r="D1378" t="n">
-        <v>-0.1</v>
+        <v>-1</v>
       </c>
       <c r="E1378" t="b">
         <v>0</v>
@@ -24742,7 +24742,7 @@
         <v>-0.8571428571428571</v>
       </c>
       <c r="D1379" t="n">
-        <v>-0.1</v>
+        <v>-1</v>
       </c>
       <c r="E1379" t="b">
         <v>1</v>
@@ -24756,10 +24756,10 @@
       </c>
       <c r="B1380" t="inlineStr"/>
       <c r="C1380" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1380" t="n">
-        <v>-0.03333333333333333</v>
+        <v>-0.9</v>
       </c>
       <c r="E1380" t="b">
         <v>0</v>
@@ -24773,10 +24773,10 @@
       </c>
       <c r="B1381" t="inlineStr"/>
       <c r="C1381" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="D1381" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.8</v>
       </c>
       <c r="E1381" t="b">
         <v>0</v>
@@ -24790,10 +24790,10 @@
       </c>
       <c r="B1382" t="inlineStr"/>
       <c r="C1382" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="D1382" t="n">
-        <v>0.1333333333333333</v>
+        <v>-0.7</v>
       </c>
       <c r="E1382" t="b">
         <v>0</v>
@@ -24809,10 +24809,10 @@
         <v>0</v>
       </c>
       <c r="C1383" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="D1383" t="n">
-        <v>0.1333333333333333</v>
+        <v>-0.7</v>
       </c>
       <c r="E1383" t="b">
         <v>1</v>
@@ -24826,10 +24826,10 @@
       </c>
       <c r="B1384" t="inlineStr"/>
       <c r="C1384" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D1384" t="n">
-        <v>0.1333333333333333</v>
+        <v>-0.7</v>
       </c>
       <c r="E1384" t="b">
         <v>0</v>
@@ -24846,7 +24846,7 @@
         <v>0</v>
       </c>
       <c r="D1385" t="n">
-        <v>0.1333333333333333</v>
+        <v>-0.7</v>
       </c>
       <c r="E1385" t="b">
         <v>0</v>
@@ -24863,7 +24863,7 @@
         <v>0</v>
       </c>
       <c r="D1386" t="n">
-        <v>0.1333333333333333</v>
+        <v>-0.7</v>
       </c>
       <c r="E1386" t="b">
         <v>0</v>
@@ -24882,7 +24882,7 @@
         <v>0</v>
       </c>
       <c r="D1387" t="n">
-        <v>0.1333333333333333</v>
+        <v>-0.7</v>
       </c>
       <c r="E1387" t="b">
         <v>1</v>
@@ -24901,7 +24901,7 @@
         <v>0</v>
       </c>
       <c r="D1388" t="n">
-        <v>0.1333333333333333</v>
+        <v>-0.7</v>
       </c>
       <c r="E1388" t="b">
         <v>1</v>
@@ -24918,7 +24918,7 @@
         <v>0</v>
       </c>
       <c r="D1389" t="n">
-        <v>0.1333333333333333</v>
+        <v>-0.7</v>
       </c>
       <c r="E1389" t="b">
         <v>0</v>
@@ -24935,7 +24935,7 @@
         <v>0</v>
       </c>
       <c r="D1390" t="n">
-        <v>0.1333333333333333</v>
+        <v>-0.7</v>
       </c>
       <c r="E1390" t="b">
         <v>0</v>
@@ -24952,7 +24952,7 @@
         <v>0</v>
       </c>
       <c r="D1391" t="n">
-        <v>0.1333333333333333</v>
+        <v>-0.7</v>
       </c>
       <c r="E1391" t="b">
         <v>0</v>
@@ -24969,7 +24969,7 @@
         <v>0</v>
       </c>
       <c r="D1392" t="n">
-        <v>0.1333333333333333</v>
+        <v>-0.7</v>
       </c>
       <c r="E1392" t="b">
         <v>0</v>
@@ -24986,7 +24986,7 @@
         <v>0</v>
       </c>
       <c r="D1393" t="n">
-        <v>0.1333333333333333</v>
+        <v>-0.7</v>
       </c>
       <c r="E1393" t="b">
         <v>0</v>
@@ -24999,13 +24999,13 @@
         </is>
       </c>
       <c r="B1394" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C1394" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1394" t="n">
-        <v>0.06666666666666667</v>
+        <v>-0.7</v>
       </c>
       <c r="E1394" t="b">
         <v>1</v>
@@ -25019,10 +25019,10 @@
       </c>
       <c r="B1395" t="inlineStr"/>
       <c r="C1395" t="n">
-        <v>-0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D1395" t="n">
-        <v>0</v>
+        <v>-0.7</v>
       </c>
       <c r="E1395" t="b">
         <v>0</v>
@@ -25036,10 +25036,10 @@
       </c>
       <c r="B1396" t="inlineStr"/>
       <c r="C1396" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="D1396" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.7</v>
       </c>
       <c r="E1396" t="b">
         <v>0</v>
@@ -25053,10 +25053,10 @@
       </c>
       <c r="B1397" t="inlineStr"/>
       <c r="C1397" t="n">
-        <v>-1.142857142857143</v>
+        <v>0</v>
       </c>
       <c r="D1397" t="n">
-        <v>-0.2</v>
+        <v>-0.6</v>
       </c>
       <c r="E1397" t="b">
         <v>0</v>
@@ -25072,10 +25072,10 @@
         <v>2</v>
       </c>
       <c r="C1398" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1398" t="n">
-        <v>-0.2</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1398" t="b">
         <v>1</v>
@@ -25089,10 +25089,10 @@
       </c>
       <c r="B1399" t="inlineStr"/>
       <c r="C1399" t="n">
-        <v>-0.5714285714285714</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D1399" t="n">
-        <v>-0.2</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1399" t="b">
         <v>0</v>
@@ -25106,10 +25106,10 @@
       </c>
       <c r="B1400" t="inlineStr"/>
       <c r="C1400" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D1400" t="n">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="E1400" t="b">
         <v>0</v>
@@ -25125,10 +25125,10 @@
         <v>0</v>
       </c>
       <c r="C1401" t="n">
-        <v>0</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D1401" t="n">
-        <v>-0.2666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1401" t="b">
         <v>1</v>
@@ -25142,10 +25142,10 @@
       </c>
       <c r="B1402" t="inlineStr"/>
       <c r="C1402" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D1402" t="n">
-        <v>-0.2666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1402" t="b">
         <v>0</v>
@@ -25159,10 +25159,10 @@
       </c>
       <c r="B1403" t="inlineStr"/>
       <c r="C1403" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D1403" t="n">
-        <v>-0.2666666666666667</v>
+        <v>0.1</v>
       </c>
       <c r="E1403" t="b">
         <v>0</v>
@@ -25179,7 +25179,7 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="D1404" t="n">
-        <v>-0.2666666666666667</v>
+        <v>0.2</v>
       </c>
       <c r="E1404" t="b">
         <v>0</v>
@@ -25196,7 +25196,7 @@
         <v>0.5714285714285714</v>
       </c>
       <c r="D1405" t="n">
-        <v>-0.2666666666666667</v>
+        <v>0.2</v>
       </c>
       <c r="E1405" t="b">
         <v>0</v>
@@ -25215,7 +25215,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1406" t="n">
-        <v>-0.2666666666666667</v>
+        <v>0.2</v>
       </c>
       <c r="E1406" t="b">
         <v>1</v>
@@ -25232,7 +25232,7 @@
         <v>0</v>
       </c>
       <c r="D1407" t="n">
-        <v>-0.1666666666666667</v>
+        <v>0.2</v>
       </c>
       <c r="E1407" t="b">
         <v>0</v>
@@ -25251,7 +25251,7 @@
         <v>0</v>
       </c>
       <c r="D1408" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0.2</v>
       </c>
       <c r="E1408" t="b">
         <v>1</v>
@@ -25264,13 +25264,13 @@
         </is>
       </c>
       <c r="B1409" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C1409" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1409" t="n">
-        <v>-0.1333333333333333</v>
+        <v>0.2</v>
       </c>
       <c r="E1409" t="b">
         <v>1</v>
@@ -25284,13 +25284,32 @@
       </c>
       <c r="B1410" t="inlineStr"/>
       <c r="C1410" t="n">
-        <v>-0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D1410" t="n">
-        <v>-0.2</v>
+        <v>0.2</v>
       </c>
       <c r="E1410" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="A1411" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B1411" t="n">
+        <v>-2</v>
+      </c>
+      <c r="C1411" t="n">
+        <v>-0.2857142857142857</v>
+      </c>
+      <c r="D1411" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="E1411" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -25323,7 +25342,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-05-25 to 2026-04-02 | Publication days: 475</t>
+          <t>Coverage: 2022-05-25 to 2026-04-03 | Publication days: 476</t>
         </is>
       </c>
     </row>

--- a/data/AU.xlsx
+++ b/data/AU.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1411"/>
+  <dimension ref="A1:E1412"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21825,13 +21825,13 @@
         </is>
       </c>
       <c r="B1214" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="C1214" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1214" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E1214" t="b">
         <v>1</v>
@@ -21847,10 +21847,10 @@
         <v>0</v>
       </c>
       <c r="C1215" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1215" t="n">
-        <v>-0.6</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E1215" t="b">
         <v>1</v>
@@ -21864,10 +21864,10 @@
       </c>
       <c r="B1216" t="inlineStr"/>
       <c r="C1216" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1216" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="E1216" t="b">
         <v>0</v>
@@ -21883,10 +21883,10 @@
         <v>3</v>
       </c>
       <c r="C1217" t="n">
-        <v>0</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D1217" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1217" t="b">
         <v>1</v>
@@ -21899,7 +21899,7 @@
         </is>
       </c>
       <c r="B1218" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C1218" t="n">
         <v>0.4285714285714285</v>
@@ -21919,10 +21919,10 @@
       </c>
       <c r="B1219" t="inlineStr"/>
       <c r="C1219" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D1219" t="n">
-        <v>-0.03333333333333333</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1219" t="b">
         <v>0</v>
@@ -21936,10 +21936,10 @@
       </c>
       <c r="B1220" t="inlineStr"/>
       <c r="C1220" t="n">
-        <v>1.285714285714286</v>
+        <v>1</v>
       </c>
       <c r="D1220" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1220" t="b">
         <v>0</v>
@@ -21953,10 +21953,10 @@
       </c>
       <c r="B1221" t="inlineStr"/>
       <c r="C1221" t="n">
-        <v>2.142857142857143</v>
+        <v>1.571428571428571</v>
       </c>
       <c r="D1221" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="E1221" t="b">
         <v>0</v>
@@ -21970,10 +21970,10 @@
       </c>
       <c r="B1222" t="inlineStr"/>
       <c r="C1222" t="n">
-        <v>2.571428571428572</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="D1222" t="n">
-        <v>0.4333333333333333</v>
+        <v>0.3</v>
       </c>
       <c r="E1222" t="b">
         <v>0</v>
@@ -21989,10 +21989,10 @@
         <v>2</v>
       </c>
       <c r="C1223" t="n">
-        <v>2.857142857142857</v>
+        <v>2.142857142857143</v>
       </c>
       <c r="D1223" t="n">
-        <v>0.5</v>
+        <v>0.3666666666666666</v>
       </c>
       <c r="E1223" t="b">
         <v>1</v>
@@ -22006,10 +22006,10 @@
       </c>
       <c r="B1224" t="inlineStr"/>
       <c r="C1224" t="n">
-        <v>2.714285714285714</v>
+        <v>2</v>
       </c>
       <c r="D1224" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="E1224" t="b">
         <v>0</v>
@@ -22023,10 +22023,10 @@
       </c>
       <c r="B1225" t="inlineStr"/>
       <c r="C1225" t="n">
-        <v>2.571428571428572</v>
+        <v>2</v>
       </c>
       <c r="D1225" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="E1225" t="b">
         <v>0</v>
@@ -22040,10 +22040,10 @@
       </c>
       <c r="B1226" t="inlineStr"/>
       <c r="C1226" t="n">
-        <v>2.428571428571428</v>
+        <v>2</v>
       </c>
       <c r="D1226" t="n">
-        <v>0.7</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="E1226" t="b">
         <v>0</v>
@@ -22059,10 +22059,10 @@
         <v>0</v>
       </c>
       <c r="C1227" t="n">
-        <v>2</v>
+        <v>1.714285714285714</v>
       </c>
       <c r="D1227" t="n">
-        <v>0.7</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="E1227" t="b">
         <v>1</v>
@@ -22076,10 +22076,10 @@
       </c>
       <c r="B1228" t="inlineStr"/>
       <c r="C1228" t="n">
-        <v>1.571428571428571</v>
+        <v>1.428571428571429</v>
       </c>
       <c r="D1228" t="n">
-        <v>0.7</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="E1228" t="b">
         <v>0</v>
@@ -22096,7 +22096,7 @@
         <v>1.142857142857143</v>
       </c>
       <c r="D1229" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="E1229" t="b">
         <v>0</v>
@@ -22113,7 +22113,7 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="D1230" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="E1230" t="b">
         <v>0</v>
@@ -22130,7 +22130,7 @@
         <v>0.5714285714285714</v>
       </c>
       <c r="D1231" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="E1231" t="b">
         <v>0</v>
@@ -22147,7 +22147,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D1232" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="E1232" t="b">
         <v>0</v>
@@ -22164,7 +22164,7 @@
         <v>0</v>
       </c>
       <c r="D1233" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="E1233" t="b">
         <v>0</v>
@@ -22181,7 +22181,7 @@
         <v>0</v>
       </c>
       <c r="D1234" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="E1234" t="b">
         <v>0</v>
@@ -22200,7 +22200,7 @@
         <v>0</v>
       </c>
       <c r="D1235" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="E1235" t="b">
         <v>1</v>
@@ -22217,7 +22217,7 @@
         <v>0</v>
       </c>
       <c r="D1236" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="E1236" t="b">
         <v>0</v>
@@ -22234,7 +22234,7 @@
         <v>0</v>
       </c>
       <c r="D1237" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="E1237" t="b">
         <v>0</v>
@@ -22251,7 +22251,7 @@
         <v>0</v>
       </c>
       <c r="D1238" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="E1238" t="b">
         <v>0</v>
@@ -22270,7 +22270,7 @@
         <v>0</v>
       </c>
       <c r="D1239" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="E1239" t="b">
         <v>1</v>
@@ -22289,7 +22289,7 @@
         <v>0</v>
       </c>
       <c r="D1240" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="E1240" t="b">
         <v>1</v>
@@ -22306,7 +22306,7 @@
         <v>0</v>
       </c>
       <c r="D1241" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="E1241" t="b">
         <v>0</v>
@@ -22325,7 +22325,7 @@
         <v>0</v>
       </c>
       <c r="D1242" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="E1242" t="b">
         <v>1</v>
@@ -22342,7 +22342,7 @@
         <v>0</v>
       </c>
       <c r="D1243" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="E1243" t="b">
         <v>0</v>
@@ -22359,7 +22359,7 @@
         <v>0</v>
       </c>
       <c r="D1244" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.7</v>
       </c>
       <c r="E1244" t="b">
         <v>0</v>
@@ -22378,7 +22378,7 @@
         <v>0</v>
       </c>
       <c r="D1245" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.7</v>
       </c>
       <c r="E1245" t="b">
         <v>1</v>
@@ -22397,7 +22397,7 @@
         <v>0</v>
       </c>
       <c r="D1246" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.7</v>
       </c>
       <c r="E1246" t="b">
         <v>1</v>
@@ -22414,7 +22414,7 @@
         <v>0</v>
       </c>
       <c r="D1247" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.6</v>
       </c>
       <c r="E1247" t="b">
         <v>0</v>
@@ -22431,7 +22431,7 @@
         <v>0</v>
       </c>
       <c r="D1248" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="E1248" t="b">
         <v>0</v>
@@ -22448,7 +22448,7 @@
         <v>0</v>
       </c>
       <c r="D1249" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="E1249" t="b">
         <v>0</v>
@@ -22465,7 +22465,7 @@
         <v>0</v>
       </c>
       <c r="D1250" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="E1250" t="b">
         <v>0</v>
@@ -22482,7 +22482,7 @@
         <v>0</v>
       </c>
       <c r="D1251" t="n">
-        <v>0.3666666666666666</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E1251" t="b">
         <v>0</v>
@@ -22669,13 +22669,13 @@
         </is>
       </c>
       <c r="B1262" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="C1262" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D1262" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="E1262" t="b">
         <v>1</v>
@@ -22688,13 +22688,13 @@
         </is>
       </c>
       <c r="B1263" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="C1263" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1263" t="n">
-        <v>-0.2</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1263" t="b">
         <v>1</v>
@@ -22708,10 +22708,10 @@
       </c>
       <c r="B1264" t="inlineStr"/>
       <c r="C1264" t="n">
-        <v>-1.285714285714286</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1264" t="n">
-        <v>-0.3</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1264" t="b">
         <v>0</v>
@@ -22725,10 +22725,10 @@
       </c>
       <c r="B1265" t="inlineStr"/>
       <c r="C1265" t="n">
-        <v>-1.714285714285714</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1265" t="n">
-        <v>-0.4</v>
+        <v>-0.2</v>
       </c>
       <c r="E1265" t="b">
         <v>0</v>
@@ -22742,10 +22742,10 @@
       </c>
       <c r="B1266" t="inlineStr"/>
       <c r="C1266" t="n">
-        <v>-2.142857142857143</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D1266" t="n">
-        <v>-0.5</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1266" t="b">
         <v>0</v>
@@ -22761,10 +22761,10 @@
         <v>-3</v>
       </c>
       <c r="C1267" t="n">
-        <v>-2.571428571428572</v>
+        <v>-1.571428571428571</v>
       </c>
       <c r="D1267" t="n">
-        <v>-0.6</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1267" t="b">
         <v>1</v>
@@ -22778,10 +22778,10 @@
       </c>
       <c r="B1268" t="inlineStr"/>
       <c r="C1268" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="D1268" t="n">
-        <v>-0.7</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1268" t="b">
         <v>0</v>
@@ -22794,13 +22794,13 @@
         </is>
       </c>
       <c r="B1269" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C1269" t="n">
-        <v>-2.571428571428572</v>
+        <v>-1.571428571428571</v>
       </c>
       <c r="D1269" t="n">
-        <v>-0.7</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1269" t="b">
         <v>1</v>
@@ -22814,10 +22814,10 @@
       </c>
       <c r="B1270" t="inlineStr"/>
       <c r="C1270" t="n">
-        <v>-2.142857142857143</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1270" t="n">
-        <v>-0.7</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1270" t="b">
         <v>0</v>
@@ -22831,10 +22831,10 @@
       </c>
       <c r="B1271" t="inlineStr"/>
       <c r="C1271" t="n">
-        <v>-1.714285714285714</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="D1271" t="n">
-        <v>-0.7</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1271" t="b">
         <v>0</v>
@@ -22848,10 +22848,10 @@
       </c>
       <c r="B1272" t="inlineStr"/>
       <c r="C1272" t="n">
-        <v>-1.285714285714286</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D1272" t="n">
-        <v>-0.7</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1272" t="b">
         <v>0</v>
@@ -22865,10 +22865,10 @@
       </c>
       <c r="B1273" t="inlineStr"/>
       <c r="C1273" t="n">
-        <v>-0.8571428571428571</v>
+        <v>1.285714285714286</v>
       </c>
       <c r="D1273" t="n">
-        <v>-0.7</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1273" t="b">
         <v>0</v>
@@ -22882,10 +22882,10 @@
       </c>
       <c r="B1274" t="inlineStr"/>
       <c r="C1274" t="n">
-        <v>-0.4285714285714285</v>
+        <v>2.142857142857143</v>
       </c>
       <c r="D1274" t="n">
-        <v>-0.7</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1274" t="b">
         <v>0</v>
@@ -22901,10 +22901,10 @@
         <v>0</v>
       </c>
       <c r="C1275" t="n">
-        <v>0</v>
+        <v>2.571428571428572</v>
       </c>
       <c r="D1275" t="n">
-        <v>-0.7</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1275" t="b">
         <v>1</v>
@@ -22920,10 +22920,10 @@
         <v>0</v>
       </c>
       <c r="C1276" t="n">
-        <v>0</v>
+        <v>2.142857142857143</v>
       </c>
       <c r="D1276" t="n">
-        <v>-0.7</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1276" t="b">
         <v>1</v>
@@ -22939,10 +22939,10 @@
         <v>-2</v>
       </c>
       <c r="C1277" t="n">
-        <v>-0.2857142857142857</v>
+        <v>1.428571428571429</v>
       </c>
       <c r="D1277" t="n">
-        <v>-0.7666666666666667</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1277" t="b">
         <v>1</v>
@@ -22956,10 +22956,10 @@
       </c>
       <c r="B1278" t="inlineStr"/>
       <c r="C1278" t="n">
-        <v>-0.5714285714285714</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D1278" t="n">
-        <v>-0.8333333333333334</v>
+        <v>0</v>
       </c>
       <c r="E1278" t="b">
         <v>0</v>
@@ -22975,10 +22975,10 @@
         <v>0</v>
       </c>
       <c r="C1279" t="n">
-        <v>-0.5714285714285714</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1279" t="n">
-        <v>-0.8333333333333334</v>
+        <v>0</v>
       </c>
       <c r="E1279" t="b">
         <v>1</v>
@@ -22994,10 +22994,10 @@
         <v>0</v>
       </c>
       <c r="C1280" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="D1280" t="n">
-        <v>-0.8333333333333334</v>
+        <v>0</v>
       </c>
       <c r="E1280" t="b">
         <v>1</v>
@@ -23014,7 +23014,7 @@
         <v>-0.5714285714285714</v>
       </c>
       <c r="D1281" t="n">
-        <v>-0.8333333333333334</v>
+        <v>0</v>
       </c>
       <c r="E1281" t="b">
         <v>0</v>
@@ -23033,7 +23033,7 @@
         <v>-0.5714285714285714</v>
       </c>
       <c r="D1282" t="n">
-        <v>-0.8333333333333334</v>
+        <v>0</v>
       </c>
       <c r="E1282" t="b">
         <v>1</v>
@@ -23050,7 +23050,7 @@
         <v>-0.5714285714285714</v>
       </c>
       <c r="D1283" t="n">
-        <v>-0.8333333333333334</v>
+        <v>0</v>
       </c>
       <c r="E1283" t="b">
         <v>0</v>
@@ -23069,7 +23069,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D1284" t="n">
-        <v>-0.9333333333333333</v>
+        <v>-0.1</v>
       </c>
       <c r="E1284" t="b">
         <v>1</v>
@@ -23088,7 +23088,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1285" t="n">
-        <v>-0.9333333333333333</v>
+        <v>-0.1</v>
       </c>
       <c r="E1285" t="b">
         <v>1</v>
@@ -23105,7 +23105,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1286" t="n">
-        <v>-0.9333333333333333</v>
+        <v>-0.1</v>
       </c>
       <c r="E1286" t="b">
         <v>0</v>
@@ -23124,7 +23124,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1287" t="n">
-        <v>-0.9333333333333333</v>
+        <v>-0.1</v>
       </c>
       <c r="E1287" t="b">
         <v>1</v>
@@ -23141,7 +23141,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1288" t="n">
-        <v>-0.9333333333333333</v>
+        <v>-0.1</v>
       </c>
       <c r="E1288" t="b">
         <v>0</v>
@@ -23158,7 +23158,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1289" t="n">
-        <v>-0.9333333333333333</v>
+        <v>-0.1</v>
       </c>
       <c r="E1289" t="b">
         <v>0</v>
@@ -23177,7 +23177,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1290" t="n">
-        <v>-0.9333333333333333</v>
+        <v>-0.1</v>
       </c>
       <c r="E1290" t="b">
         <v>1</v>
@@ -23196,7 +23196,7 @@
         <v>0</v>
       </c>
       <c r="D1291" t="n">
-        <v>-0.9333333333333333</v>
+        <v>-0.1</v>
       </c>
       <c r="E1291" t="b">
         <v>1</v>
@@ -23213,7 +23213,7 @@
         <v>0</v>
       </c>
       <c r="D1292" t="n">
-        <v>-0.8333333333333334</v>
+        <v>-0.1</v>
       </c>
       <c r="E1292" t="b">
         <v>0</v>
@@ -23232,7 +23232,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1293" t="n">
-        <v>-0.8333333333333334</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1293" t="b">
         <v>1</v>
@@ -23251,7 +23251,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1294" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1294" t="b">
         <v>1</v>
@@ -23268,7 +23268,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1295" t="n">
-        <v>-0.6333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E1295" t="b">
         <v>0</v>
@@ -23287,7 +23287,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1296" t="n">
-        <v>-0.5333333333333333</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1296" t="b">
         <v>1</v>
@@ -23306,7 +23306,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1297" t="n">
-        <v>-0.4333333333333333</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E1297" t="b">
         <v>1</v>
@@ -23323,7 +23323,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1298" t="n">
-        <v>-0.3333333333333333</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="E1298" t="b">
         <v>0</v>
@@ -23340,7 +23340,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1299" t="n">
-        <v>-0.3333333333333333</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E1299" t="b">
         <v>0</v>
@@ -23357,7 +23357,7 @@
         <v>0</v>
       </c>
       <c r="D1300" t="n">
-        <v>-0.3333333333333333</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1300" t="b">
         <v>0</v>
@@ -23374,7 +23374,7 @@
         <v>0</v>
       </c>
       <c r="D1301" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E1301" t="b">
         <v>0</v>
@@ -23391,7 +23391,7 @@
         <v>0</v>
       </c>
       <c r="D1302" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1302" t="b">
         <v>0</v>
@@ -23408,7 +23408,7 @@
         <v>0</v>
       </c>
       <c r="D1303" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E1303" t="b">
         <v>0</v>
@@ -24054,13 +24054,13 @@
         </is>
       </c>
       <c r="B1341" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
       <c r="C1341" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1341" t="n">
-        <v>-0.1</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1341" t="b">
         <v>1</v>
@@ -24074,10 +24074,10 @@
       </c>
       <c r="B1342" t="inlineStr"/>
       <c r="C1342" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D1342" t="n">
-        <v>-0.2</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1342" t="b">
         <v>0</v>
@@ -24093,10 +24093,10 @@
         <v>0</v>
       </c>
       <c r="C1343" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D1343" t="n">
-        <v>-0.2</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1343" t="b">
         <v>1</v>
@@ -24110,10 +24110,10 @@
       </c>
       <c r="B1344" t="inlineStr"/>
       <c r="C1344" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D1344" t="n">
-        <v>-0.2</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1344" t="b">
         <v>0</v>
@@ -24129,10 +24129,10 @@
         <v>0</v>
       </c>
       <c r="C1345" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D1345" t="n">
-        <v>-0.2</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1345" t="b">
         <v>1</v>
@@ -24146,10 +24146,10 @@
       </c>
       <c r="B1346" t="inlineStr"/>
       <c r="C1346" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D1346" t="n">
-        <v>-0.2</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1346" t="b">
         <v>0</v>
@@ -24165,10 +24165,10 @@
         <v>0</v>
       </c>
       <c r="C1347" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D1347" t="n">
-        <v>-0.2</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1347" t="b">
         <v>1</v>
@@ -24182,10 +24182,10 @@
       </c>
       <c r="B1348" t="inlineStr"/>
       <c r="C1348" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1348" t="n">
-        <v>-0.2</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1348" t="b">
         <v>0</v>
@@ -24202,7 +24202,7 @@
         <v>0</v>
       </c>
       <c r="D1349" t="n">
-        <v>-0.2</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1349" t="b">
         <v>0</v>
@@ -24215,13 +24215,13 @@
         </is>
       </c>
       <c r="B1350" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="C1350" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1350" t="n">
-        <v>-0.3</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1350" t="b">
         <v>1</v>
@@ -24235,10 +24235,10 @@
       </c>
       <c r="B1351" t="inlineStr"/>
       <c r="C1351" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1351" t="n">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
       <c r="E1351" t="b">
         <v>0</v>
@@ -24254,10 +24254,10 @@
         <v>-3</v>
       </c>
       <c r="C1352" t="n">
-        <v>-1.285714285714286</v>
+        <v>-1</v>
       </c>
       <c r="D1352" t="n">
-        <v>-0.5</v>
+        <v>-0.1</v>
       </c>
       <c r="E1352" t="b">
         <v>1</v>
@@ -24273,10 +24273,10 @@
         <v>0</v>
       </c>
       <c r="C1353" t="n">
-        <v>-1.285714285714286</v>
+        <v>-1</v>
       </c>
       <c r="D1353" t="n">
-        <v>-0.5</v>
+        <v>-0.1</v>
       </c>
       <c r="E1353" t="b">
         <v>1</v>
@@ -24292,10 +24292,10 @@
         <v>0</v>
       </c>
       <c r="C1354" t="n">
-        <v>-1.285714285714286</v>
+        <v>-1</v>
       </c>
       <c r="D1354" t="n">
-        <v>-0.5</v>
+        <v>-0.1</v>
       </c>
       <c r="E1354" t="b">
         <v>1</v>
@@ -24309,10 +24309,10 @@
       </c>
       <c r="B1355" t="inlineStr"/>
       <c r="C1355" t="n">
-        <v>-1.285714285714286</v>
+        <v>-1</v>
       </c>
       <c r="D1355" t="n">
-        <v>-0.5</v>
+        <v>-0.1</v>
       </c>
       <c r="E1355" t="b">
         <v>0</v>
@@ -24328,10 +24328,10 @@
         <v>0</v>
       </c>
       <c r="C1356" t="n">
-        <v>-1.285714285714286</v>
+        <v>-1</v>
       </c>
       <c r="D1356" t="n">
-        <v>-0.5</v>
+        <v>-0.1</v>
       </c>
       <c r="E1356" t="b">
         <v>1</v>
@@ -24347,10 +24347,10 @@
         <v>0</v>
       </c>
       <c r="C1357" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D1357" t="n">
-        <v>-0.5</v>
+        <v>-0.1</v>
       </c>
       <c r="E1357" t="b">
         <v>1</v>
@@ -24369,7 +24369,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1358" t="n">
-        <v>-0.5</v>
+        <v>-0.1</v>
       </c>
       <c r="E1358" t="b">
         <v>1</v>
@@ -24386,7 +24386,7 @@
         <v>0</v>
       </c>
       <c r="D1359" t="n">
-        <v>-0.5</v>
+        <v>-0.1</v>
       </c>
       <c r="E1359" t="b">
         <v>0</v>
@@ -24403,7 +24403,7 @@
         <v>0</v>
       </c>
       <c r="D1360" t="n">
-        <v>-0.5</v>
+        <v>-0.1</v>
       </c>
       <c r="E1360" t="b">
         <v>0</v>
@@ -24422,7 +24422,7 @@
         <v>0</v>
       </c>
       <c r="D1361" t="n">
-        <v>-0.5</v>
+        <v>-0.1</v>
       </c>
       <c r="E1361" t="b">
         <v>1</v>
@@ -24439,7 +24439,7 @@
         <v>0</v>
       </c>
       <c r="D1362" t="n">
-        <v>-0.5</v>
+        <v>-0.1</v>
       </c>
       <c r="E1362" t="b">
         <v>0</v>
@@ -24456,7 +24456,7 @@
         <v>0</v>
       </c>
       <c r="D1363" t="n">
-        <v>-0.5</v>
+        <v>-0.1</v>
       </c>
       <c r="E1363" t="b">
         <v>0</v>
@@ -24473,7 +24473,7 @@
         <v>0</v>
       </c>
       <c r="D1364" t="n">
-        <v>-0.5</v>
+        <v>-0.1</v>
       </c>
       <c r="E1364" t="b">
         <v>0</v>
@@ -24490,7 +24490,7 @@
         <v>0</v>
       </c>
       <c r="D1365" t="n">
-        <v>-0.5</v>
+        <v>-0.1</v>
       </c>
       <c r="E1365" t="b">
         <v>0</v>
@@ -24507,7 +24507,7 @@
         <v>0</v>
       </c>
       <c r="D1366" t="n">
-        <v>-0.5</v>
+        <v>-0.1</v>
       </c>
       <c r="E1366" t="b">
         <v>0</v>
@@ -24520,13 +24520,13 @@
         </is>
       </c>
       <c r="B1367" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
       <c r="C1367" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1367" t="n">
-        <v>-0.6</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E1367" t="b">
         <v>1</v>
@@ -24540,10 +24540,10 @@
       </c>
       <c r="B1368" t="inlineStr"/>
       <c r="C1368" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D1368" t="n">
-        <v>-0.7</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1368" t="b">
         <v>0</v>
@@ -24557,10 +24557,10 @@
       </c>
       <c r="B1369" t="inlineStr"/>
       <c r="C1369" t="n">
-        <v>-1.285714285714286</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D1369" t="n">
-        <v>-0.8</v>
+        <v>0.1</v>
       </c>
       <c r="E1369" t="b">
         <v>0</v>
@@ -24574,10 +24574,10 @@
       </c>
       <c r="B1370" t="inlineStr"/>
       <c r="C1370" t="n">
-        <v>-1.714285714285714</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="D1370" t="n">
-        <v>-0.9</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E1370" t="b">
         <v>0</v>
@@ -24591,10 +24591,10 @@
       </c>
       <c r="B1371" t="inlineStr"/>
       <c r="C1371" t="n">
-        <v>-2.142857142857143</v>
+        <v>1.428571428571429</v>
       </c>
       <c r="D1371" t="n">
-        <v>-0.9</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E1371" t="b">
         <v>0</v>
@@ -24610,10 +24610,10 @@
         <v>0</v>
       </c>
       <c r="C1372" t="n">
-        <v>-2.142857142857143</v>
+        <v>1.428571428571429</v>
       </c>
       <c r="D1372" t="n">
-        <v>-0.8</v>
+        <v>0.1</v>
       </c>
       <c r="E1372" t="b">
         <v>1</v>
@@ -24626,13 +24626,13 @@
         </is>
       </c>
       <c r="B1373" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="C1373" t="n">
-        <v>-2.571428571428572</v>
+        <v>1.428571428571429</v>
       </c>
       <c r="D1373" t="n">
-        <v>-0.9</v>
+        <v>0.1</v>
       </c>
       <c r="E1373" t="b">
         <v>1</v>
@@ -24646,10 +24646,10 @@
       </c>
       <c r="B1374" t="inlineStr"/>
       <c r="C1374" t="n">
-        <v>-2.571428571428572</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="D1374" t="n">
-        <v>-1</v>
+        <v>0.1</v>
       </c>
       <c r="E1374" t="b">
         <v>0</v>
@@ -24665,10 +24665,10 @@
         <v>0</v>
       </c>
       <c r="C1375" t="n">
-        <v>-2.142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D1375" t="n">
-        <v>-1</v>
+        <v>0.1</v>
       </c>
       <c r="E1375" t="b">
         <v>1</v>
@@ -24684,10 +24684,10 @@
         <v>0</v>
       </c>
       <c r="C1376" t="n">
-        <v>-1.714285714285714</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D1376" t="n">
-        <v>-1</v>
+        <v>0.1</v>
       </c>
       <c r="E1376" t="b">
         <v>1</v>
@@ -24703,10 +24703,10 @@
         <v>0</v>
       </c>
       <c r="C1377" t="n">
-        <v>-1.285714285714286</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1377" t="n">
-        <v>-1</v>
+        <v>0.1</v>
       </c>
       <c r="E1377" t="b">
         <v>1</v>
@@ -24720,10 +24720,10 @@
       </c>
       <c r="B1378" t="inlineStr"/>
       <c r="C1378" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="D1378" t="n">
-        <v>-1</v>
+        <v>0.1</v>
       </c>
       <c r="E1378" t="b">
         <v>0</v>
@@ -24739,10 +24739,10 @@
         <v>0</v>
       </c>
       <c r="C1379" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="D1379" t="n">
-        <v>-1</v>
+        <v>0.1</v>
       </c>
       <c r="E1379" t="b">
         <v>1</v>
@@ -24756,10 +24756,10 @@
       </c>
       <c r="B1380" t="inlineStr"/>
       <c r="C1380" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D1380" t="n">
-        <v>-0.9</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E1380" t="b">
         <v>0</v>
@@ -24776,7 +24776,7 @@
         <v>0</v>
       </c>
       <c r="D1381" t="n">
-        <v>-0.8</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="E1381" t="b">
         <v>0</v>
@@ -24793,7 +24793,7 @@
         <v>0</v>
       </c>
       <c r="D1382" t="n">
-        <v>-0.7</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E1382" t="b">
         <v>0</v>
@@ -24812,7 +24812,7 @@
         <v>0</v>
       </c>
       <c r="D1383" t="n">
-        <v>-0.7</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E1383" t="b">
         <v>1</v>
@@ -24829,7 +24829,7 @@
         <v>0</v>
       </c>
       <c r="D1384" t="n">
-        <v>-0.7</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E1384" t="b">
         <v>0</v>
@@ -24846,7 +24846,7 @@
         <v>0</v>
       </c>
       <c r="D1385" t="n">
-        <v>-0.7</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E1385" t="b">
         <v>0</v>
@@ -24863,7 +24863,7 @@
         <v>0</v>
       </c>
       <c r="D1386" t="n">
-        <v>-0.7</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E1386" t="b">
         <v>0</v>
@@ -24876,13 +24876,13 @@
         </is>
       </c>
       <c r="B1387" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C1387" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1387" t="n">
-        <v>-0.7</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="E1387" t="b">
         <v>1</v>
@@ -24898,10 +24898,10 @@
         <v>0</v>
       </c>
       <c r="C1388" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1388" t="n">
-        <v>-0.7</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="E1388" t="b">
         <v>1</v>
@@ -24915,10 +24915,10 @@
       </c>
       <c r="B1389" t="inlineStr"/>
       <c r="C1389" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1389" t="n">
-        <v>-0.7</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="E1389" t="b">
         <v>0</v>
@@ -24932,10 +24932,10 @@
       </c>
       <c r="B1390" t="inlineStr"/>
       <c r="C1390" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1390" t="n">
-        <v>-0.7</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="E1390" t="b">
         <v>0</v>
@@ -24949,10 +24949,10 @@
       </c>
       <c r="B1391" t="inlineStr"/>
       <c r="C1391" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1391" t="n">
-        <v>-0.7</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="E1391" t="b">
         <v>0</v>
@@ -24966,10 +24966,10 @@
       </c>
       <c r="B1392" t="inlineStr"/>
       <c r="C1392" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1392" t="n">
-        <v>-0.7</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="E1392" t="b">
         <v>0</v>
@@ -24983,10 +24983,10 @@
       </c>
       <c r="B1393" t="inlineStr"/>
       <c r="C1393" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1393" t="n">
-        <v>-0.7</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="E1393" t="b">
         <v>0</v>
@@ -25005,7 +25005,7 @@
         <v>0</v>
       </c>
       <c r="D1394" t="n">
-        <v>-0.7</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="E1394" t="b">
         <v>1</v>
@@ -25022,7 +25022,7 @@
         <v>0</v>
       </c>
       <c r="D1395" t="n">
-        <v>-0.7</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="E1395" t="b">
         <v>0</v>
@@ -25039,7 +25039,7 @@
         <v>0</v>
       </c>
       <c r="D1396" t="n">
-        <v>-0.7</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="E1396" t="b">
         <v>0</v>
@@ -25056,7 +25056,7 @@
         <v>0</v>
       </c>
       <c r="D1397" t="n">
-        <v>-0.6</v>
+        <v>0.2</v>
       </c>
       <c r="E1397" t="b">
         <v>0</v>
@@ -25069,13 +25069,13 @@
         </is>
       </c>
       <c r="B1398" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="C1398" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1398" t="n">
-        <v>-0.4333333333333333</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1398" t="b">
         <v>1</v>
@@ -25089,10 +25089,10 @@
       </c>
       <c r="B1399" t="inlineStr"/>
       <c r="C1399" t="n">
-        <v>0.5714285714285714</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1399" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1399" t="b">
         <v>0</v>
@@ -25106,10 +25106,10 @@
       </c>
       <c r="B1400" t="inlineStr"/>
       <c r="C1400" t="n">
-        <v>0.8571428571428571</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1400" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="E1400" t="b">
         <v>0</v>
@@ -25125,10 +25125,10 @@
         <v>0</v>
       </c>
       <c r="C1401" t="n">
-        <v>0.8571428571428571</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1401" t="n">
-        <v>0</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1401" t="b">
         <v>1</v>
@@ -25142,10 +25142,10 @@
       </c>
       <c r="B1402" t="inlineStr"/>
       <c r="C1402" t="n">
-        <v>0.8571428571428571</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1402" t="n">
-        <v>0</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1402" t="b">
         <v>0</v>
@@ -25159,10 +25159,10 @@
       </c>
       <c r="B1403" t="inlineStr"/>
       <c r="C1403" t="n">
-        <v>0.8571428571428571</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1403" t="n">
-        <v>0.1</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1403" t="b">
         <v>0</v>
@@ -25176,10 +25176,10 @@
       </c>
       <c r="B1404" t="inlineStr"/>
       <c r="C1404" t="n">
-        <v>0.8571428571428571</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1404" t="n">
-        <v>0.2</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1404" t="b">
         <v>0</v>
@@ -25193,10 +25193,10 @@
       </c>
       <c r="B1405" t="inlineStr"/>
       <c r="C1405" t="n">
-        <v>0.5714285714285714</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1405" t="n">
-        <v>0.2</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1405" t="b">
         <v>0</v>
@@ -25212,10 +25212,10 @@
         <v>0</v>
       </c>
       <c r="C1406" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1406" t="n">
-        <v>0.2</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1406" t="b">
         <v>1</v>
@@ -25232,7 +25232,7 @@
         <v>0</v>
       </c>
       <c r="D1407" t="n">
-        <v>0.2</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1407" t="b">
         <v>0</v>
@@ -25251,7 +25251,7 @@
         <v>0</v>
       </c>
       <c r="D1408" t="n">
-        <v>0.2</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1408" t="b">
         <v>1</v>
@@ -25270,7 +25270,7 @@
         <v>0</v>
       </c>
       <c r="D1409" t="n">
-        <v>0.2</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1409" t="b">
         <v>1</v>
@@ -25287,7 +25287,7 @@
         <v>0</v>
       </c>
       <c r="D1410" t="n">
-        <v>0.2</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1410" t="b">
         <v>0</v>
@@ -25300,16 +25300,33 @@
         </is>
       </c>
       <c r="B1411" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C1411" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1411" t="n">
-        <v>0.1333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1411" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="A1412" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B1412" t="inlineStr"/>
+      <c r="C1412" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1412" t="n">
+        <v>-0.2666666666666667</v>
+      </c>
+      <c r="E1412" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -25342,7 +25359,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-05-25 to 2026-04-03 | Publication days: 476</t>
+          <t>Coverage: 2022-05-25 to 2026-04-04 | Publication days: 476</t>
         </is>
       </c>
     </row>

--- a/data/AU.xlsx
+++ b/data/AU.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1412"/>
+  <dimension ref="A1:E1413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -25069,13 +25069,13 @@
         </is>
       </c>
       <c r="B1398" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C1398" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1398" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1398" t="b">
         <v>1</v>
@@ -25089,10 +25089,10 @@
       </c>
       <c r="B1399" t="inlineStr"/>
       <c r="C1399" t="n">
-        <v>-0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D1399" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1399" t="b">
         <v>0</v>
@@ -25106,10 +25106,10 @@
       </c>
       <c r="B1400" t="inlineStr"/>
       <c r="C1400" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="D1400" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="E1400" t="b">
         <v>0</v>
@@ -25125,10 +25125,10 @@
         <v>0</v>
       </c>
       <c r="C1401" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="D1401" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1401" t="b">
         <v>1</v>
@@ -25142,10 +25142,10 @@
       </c>
       <c r="B1402" t="inlineStr"/>
       <c r="C1402" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="D1402" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1402" t="b">
         <v>0</v>
@@ -25159,10 +25159,10 @@
       </c>
       <c r="B1403" t="inlineStr"/>
       <c r="C1403" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="D1403" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1403" t="b">
         <v>0</v>
@@ -25176,10 +25176,10 @@
       </c>
       <c r="B1404" t="inlineStr"/>
       <c r="C1404" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="D1404" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1404" t="b">
         <v>0</v>
@@ -25193,10 +25193,10 @@
       </c>
       <c r="B1405" t="inlineStr"/>
       <c r="C1405" t="n">
-        <v>-0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D1405" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1405" t="b">
         <v>0</v>
@@ -25212,10 +25212,10 @@
         <v>0</v>
       </c>
       <c r="C1406" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1406" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1406" t="b">
         <v>1</v>
@@ -25232,7 +25232,7 @@
         <v>0</v>
       </c>
       <c r="D1407" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1407" t="b">
         <v>0</v>
@@ -25251,7 +25251,7 @@
         <v>0</v>
       </c>
       <c r="D1408" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1408" t="b">
         <v>1</v>
@@ -25270,7 +25270,7 @@
         <v>0</v>
       </c>
       <c r="D1409" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1409" t="b">
         <v>1</v>
@@ -25287,7 +25287,7 @@
         <v>0</v>
       </c>
       <c r="D1410" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1410" t="b">
         <v>0</v>
@@ -25306,7 +25306,7 @@
         <v>0</v>
       </c>
       <c r="D1411" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1411" t="b">
         <v>1</v>
@@ -25323,10 +25323,29 @@
         <v>0</v>
       </c>
       <c r="D1412" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1412" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="A1413" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B1413" t="n">
+        <v>-2</v>
+      </c>
+      <c r="C1413" t="n">
+        <v>-0.2857142857142857</v>
+      </c>
+      <c r="D1413" t="n">
+        <v>-0.1333333333333333</v>
+      </c>
+      <c r="E1413" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -25359,7 +25378,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-05-25 to 2026-04-04 | Publication days: 476</t>
+          <t>Coverage: 2022-05-25 to 2026-04-05 | Publication days: 477</t>
         </is>
       </c>
     </row>

--- a/data/AU.xlsx
+++ b/data/AU.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1413"/>
+  <dimension ref="A1:E1414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -25346,6 +25346,23 @@
       </c>
       <c r="E1413" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B1414" t="inlineStr"/>
+      <c r="C1414" t="n">
+        <v>-0.5714285714285714</v>
+      </c>
+      <c r="D1414" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E1414" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -25378,7 +25395,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-05-25 to 2026-04-05 | Publication days: 477</t>
+          <t>Coverage: 2022-05-25 to 2026-04-06 | Publication days: 477</t>
         </is>
       </c>
     </row>

--- a/data/AU.xlsx
+++ b/data/AU.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1414"/>
+  <dimension ref="A1:E1415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -25362,6 +25362,23 @@
         <v>-0.2</v>
       </c>
       <c r="E1414" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="A1415" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B1415" t="inlineStr"/>
+      <c r="C1415" t="n">
+        <v>-0.8571428571428571</v>
+      </c>
+      <c r="D1415" t="n">
+        <v>-0.2666666666666667</v>
+      </c>
+      <c r="E1415" t="b">
         <v>0</v>
       </c>
     </row>
@@ -25395,7 +25412,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-05-25 to 2026-04-06 | Publication days: 477</t>
+          <t>Coverage: 2022-05-25 to 2026-04-07 | Publication days: 477</t>
         </is>
       </c>
     </row>

--- a/data/AU.xlsx
+++ b/data/AU.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1415"/>
+  <dimension ref="A1:E1416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -24700,13 +24700,13 @@
         </is>
       </c>
       <c r="B1377" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="C1377" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="D1377" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E1377" t="b">
         <v>1</v>
@@ -24720,10 +24720,10 @@
       </c>
       <c r="B1378" t="inlineStr"/>
       <c r="C1378" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1378" t="n">
-        <v>0.1</v>
+        <v>-0.1</v>
       </c>
       <c r="E1378" t="b">
         <v>0</v>
@@ -24739,10 +24739,10 @@
         <v>0</v>
       </c>
       <c r="C1379" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1379" t="n">
-        <v>0.1</v>
+        <v>-0.1</v>
       </c>
       <c r="E1379" t="b">
         <v>1</v>
@@ -24756,10 +24756,10 @@
       </c>
       <c r="B1380" t="inlineStr"/>
       <c r="C1380" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1380" t="n">
-        <v>0.1666666666666667</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E1380" t="b">
         <v>0</v>
@@ -24773,10 +24773,10 @@
       </c>
       <c r="B1381" t="inlineStr"/>
       <c r="C1381" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1381" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1381" t="b">
         <v>0</v>
@@ -24790,10 +24790,10 @@
       </c>
       <c r="B1382" t="inlineStr"/>
       <c r="C1382" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1382" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1382" t="b">
         <v>0</v>
@@ -24809,10 +24809,10 @@
         <v>0</v>
       </c>
       <c r="C1383" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1383" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1383" t="b">
         <v>1</v>
@@ -24826,10 +24826,10 @@
       </c>
       <c r="B1384" t="inlineStr"/>
       <c r="C1384" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1384" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1384" t="b">
         <v>0</v>
@@ -24846,7 +24846,7 @@
         <v>0</v>
       </c>
       <c r="D1385" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1385" t="b">
         <v>0</v>
@@ -24863,7 +24863,7 @@
         <v>0</v>
       </c>
       <c r="D1386" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1386" t="b">
         <v>0</v>
@@ -24882,7 +24882,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1387" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1387" t="b">
         <v>1</v>
@@ -24901,7 +24901,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1388" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1388" t="b">
         <v>1</v>
@@ -24918,7 +24918,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1389" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1389" t="b">
         <v>0</v>
@@ -24935,7 +24935,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1390" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1390" t="b">
         <v>0</v>
@@ -24952,7 +24952,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1391" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1391" t="b">
         <v>0</v>
@@ -24969,7 +24969,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1392" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1392" t="b">
         <v>0</v>
@@ -24986,7 +24986,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1393" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1393" t="b">
         <v>0</v>
@@ -24999,13 +24999,13 @@
         </is>
       </c>
       <c r="B1394" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C1394" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1394" t="n">
-        <v>0.2666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1394" t="b">
         <v>1</v>
@@ -25019,10 +25019,10 @@
       </c>
       <c r="B1395" t="inlineStr"/>
       <c r="C1395" t="n">
-        <v>0</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1395" t="n">
-        <v>0.2666666666666667</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1395" t="b">
         <v>0</v>
@@ -25036,10 +25036,10 @@
       </c>
       <c r="B1396" t="inlineStr"/>
       <c r="C1396" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1396" t="n">
-        <v>0.2666666666666667</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1396" t="b">
         <v>0</v>
@@ -25053,10 +25053,10 @@
       </c>
       <c r="B1397" t="inlineStr"/>
       <c r="C1397" t="n">
-        <v>0</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D1397" t="n">
-        <v>0.2</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1397" t="b">
         <v>0</v>
@@ -25072,10 +25072,10 @@
         <v>0</v>
       </c>
       <c r="C1398" t="n">
-        <v>0</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D1398" t="n">
-        <v>0.1333333333333333</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1398" t="b">
         <v>1</v>
@@ -25089,10 +25089,10 @@
       </c>
       <c r="B1399" t="inlineStr"/>
       <c r="C1399" t="n">
-        <v>0</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D1399" t="n">
-        <v>0.06666666666666667</v>
+        <v>-0.4</v>
       </c>
       <c r="E1399" t="b">
         <v>0</v>
@@ -25106,10 +25106,10 @@
       </c>
       <c r="B1400" t="inlineStr"/>
       <c r="C1400" t="n">
-        <v>0</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D1400" t="n">
-        <v>0</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1400" t="b">
         <v>0</v>
@@ -25125,10 +25125,10 @@
         <v>0</v>
       </c>
       <c r="C1401" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1401" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1401" t="b">
         <v>1</v>
@@ -25142,10 +25142,10 @@
       </c>
       <c r="B1402" t="inlineStr"/>
       <c r="C1402" t="n">
-        <v>0</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1402" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1402" t="b">
         <v>0</v>
@@ -25159,10 +25159,10 @@
       </c>
       <c r="B1403" t="inlineStr"/>
       <c r="C1403" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1403" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1403" t="b">
         <v>0</v>
@@ -25179,7 +25179,7 @@
         <v>0</v>
       </c>
       <c r="D1404" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1404" t="b">
         <v>0</v>
@@ -25196,7 +25196,7 @@
         <v>0</v>
       </c>
       <c r="D1405" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1405" t="b">
         <v>0</v>
@@ -25215,7 +25215,7 @@
         <v>0</v>
       </c>
       <c r="D1406" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1406" t="b">
         <v>1</v>
@@ -25232,7 +25232,7 @@
         <v>0</v>
       </c>
       <c r="D1407" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1407" t="b">
         <v>0</v>
@@ -25251,7 +25251,7 @@
         <v>0</v>
       </c>
       <c r="D1408" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1408" t="b">
         <v>1</v>
@@ -25264,13 +25264,13 @@
         </is>
       </c>
       <c r="B1409" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C1409" t="n">
-        <v>0</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D1409" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E1409" t="b">
         <v>1</v>
@@ -25284,10 +25284,10 @@
       </c>
       <c r="B1410" t="inlineStr"/>
       <c r="C1410" t="n">
-        <v>0</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D1410" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1410" t="b">
         <v>0</v>
@@ -25303,10 +25303,10 @@
         <v>0</v>
       </c>
       <c r="C1411" t="n">
-        <v>0</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D1411" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1411" t="b">
         <v>1</v>
@@ -25320,10 +25320,10 @@
       </c>
       <c r="B1412" t="inlineStr"/>
       <c r="C1412" t="n">
-        <v>0</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D1412" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1412" t="b">
         <v>0</v>
@@ -25339,10 +25339,10 @@
         <v>-2</v>
       </c>
       <c r="C1413" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D1413" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E1413" t="b">
         <v>1</v>
@@ -25356,10 +25356,10 @@
       </c>
       <c r="B1414" t="inlineStr"/>
       <c r="C1414" t="n">
-        <v>-0.5714285714285714</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1414" t="n">
-        <v>-0.2</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E1414" t="b">
         <v>0</v>
@@ -25373,13 +25373,32 @@
       </c>
       <c r="B1415" t="inlineStr"/>
       <c r="C1415" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="D1415" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1415" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B1416" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1416" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1416" t="n">
+        <v>-0.2333333333333333</v>
+      </c>
+      <c r="E1416" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -25412,7 +25431,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-05-25 to 2026-04-07 | Publication days: 477</t>
+          <t>Coverage: 2022-05-25 to 2026-04-08 | Publication days: 478</t>
         </is>
       </c>
     </row>

--- a/data/AU.xlsx
+++ b/data/AU.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1416"/>
+  <dimension ref="A1:E1417"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -25399,6 +25399,23 @@
       </c>
       <c r="E1416" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="A1417" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B1417" t="inlineStr"/>
+      <c r="C1417" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1417" t="n">
+        <v>-0.06666666666666667</v>
+      </c>
+      <c r="E1417" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -25431,7 +25448,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-05-25 to 2026-04-08 | Publication days: 478</t>
+          <t>Coverage: 2022-05-25 to 2026-04-09 | Publication days: 478</t>
         </is>
       </c>
     </row>

--- a/data/AU.xlsx
+++ b/data/AU.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1417"/>
+  <dimension ref="A1:E1418"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22669,13 +22669,13 @@
         </is>
       </c>
       <c r="B1262" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="C1262" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1262" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="E1262" t="b">
         <v>1</v>
@@ -22691,10 +22691,10 @@
         <v>-2</v>
       </c>
       <c r="C1263" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D1263" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E1263" t="b">
         <v>1</v>
@@ -22708,10 +22708,10 @@
       </c>
       <c r="B1264" t="inlineStr"/>
       <c r="C1264" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-1</v>
       </c>
       <c r="D1264" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E1264" t="b">
         <v>0</v>
@@ -22725,10 +22725,10 @@
       </c>
       <c r="B1265" t="inlineStr"/>
       <c r="C1265" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D1265" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="E1265" t="b">
         <v>0</v>
@@ -22742,10 +22742,10 @@
       </c>
       <c r="B1266" t="inlineStr"/>
       <c r="C1266" t="n">
-        <v>-1.142857142857143</v>
+        <v>-1.571428571428571</v>
       </c>
       <c r="D1266" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E1266" t="b">
         <v>0</v>
@@ -22761,10 +22761,10 @@
         <v>-3</v>
       </c>
       <c r="C1267" t="n">
-        <v>-1.571428571428571</v>
+        <v>-2</v>
       </c>
       <c r="D1267" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1267" t="b">
         <v>1</v>
@@ -22778,10 +22778,10 @@
       </c>
       <c r="B1268" t="inlineStr"/>
       <c r="C1268" t="n">
-        <v>-2</v>
+        <v>-2.428571428571428</v>
       </c>
       <c r="D1268" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E1268" t="b">
         <v>0</v>
@@ -22794,13 +22794,13 @@
         </is>
       </c>
       <c r="B1269" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C1269" t="n">
-        <v>-1.571428571428571</v>
+        <v>-2</v>
       </c>
       <c r="D1269" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E1269" t="b">
         <v>1</v>
@@ -22814,10 +22814,10 @@
       </c>
       <c r="B1270" t="inlineStr"/>
       <c r="C1270" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-1.714285714285714</v>
       </c>
       <c r="D1270" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E1270" t="b">
         <v>0</v>
@@ -22831,10 +22831,10 @@
       </c>
       <c r="B1271" t="inlineStr"/>
       <c r="C1271" t="n">
-        <v>-0.1428571428571428</v>
+        <v>-1.428571428571429</v>
       </c>
       <c r="D1271" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E1271" t="b">
         <v>0</v>
@@ -22848,10 +22848,10 @@
       </c>
       <c r="B1272" t="inlineStr"/>
       <c r="C1272" t="n">
-        <v>0.5714285714285714</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D1272" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E1272" t="b">
         <v>0</v>
@@ -22865,10 +22865,10 @@
       </c>
       <c r="B1273" t="inlineStr"/>
       <c r="C1273" t="n">
-        <v>1.285714285714286</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1273" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E1273" t="b">
         <v>0</v>
@@ -22882,10 +22882,10 @@
       </c>
       <c r="B1274" t="inlineStr"/>
       <c r="C1274" t="n">
-        <v>2.142857142857143</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1274" t="n">
-        <v>0.1333333333333333</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E1274" t="b">
         <v>0</v>
@@ -22901,10 +22901,10 @@
         <v>0</v>
       </c>
       <c r="C1275" t="n">
-        <v>2.571428571428572</v>
+        <v>0</v>
       </c>
       <c r="D1275" t="n">
-        <v>0.1333333333333333</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E1275" t="b">
         <v>1</v>
@@ -22920,10 +22920,10 @@
         <v>0</v>
       </c>
       <c r="C1276" t="n">
-        <v>2.142857142857143</v>
+        <v>0</v>
       </c>
       <c r="D1276" t="n">
-        <v>0.1333333333333333</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E1276" t="b">
         <v>1</v>
@@ -22939,10 +22939,10 @@
         <v>-2</v>
       </c>
       <c r="C1277" t="n">
-        <v>1.428571428571429</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1277" t="n">
-        <v>0.06666666666666667</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E1277" t="b">
         <v>1</v>
@@ -22956,10 +22956,10 @@
       </c>
       <c r="B1278" t="inlineStr"/>
       <c r="C1278" t="n">
-        <v>0.7142857142857143</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1278" t="n">
-        <v>0</v>
+        <v>-0.7</v>
       </c>
       <c r="E1278" t="b">
         <v>0</v>
@@ -22975,10 +22975,10 @@
         <v>0</v>
       </c>
       <c r="C1279" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1279" t="n">
-        <v>0</v>
+        <v>-0.7</v>
       </c>
       <c r="E1279" t="b">
         <v>1</v>
@@ -22994,10 +22994,10 @@
         <v>0</v>
       </c>
       <c r="C1280" t="n">
-        <v>-0.1428571428571428</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1280" t="n">
-        <v>0</v>
+        <v>-0.7</v>
       </c>
       <c r="E1280" t="b">
         <v>1</v>
@@ -23014,7 +23014,7 @@
         <v>-0.5714285714285714</v>
       </c>
       <c r="D1281" t="n">
-        <v>0</v>
+        <v>-0.7</v>
       </c>
       <c r="E1281" t="b">
         <v>0</v>
@@ -23033,7 +23033,7 @@
         <v>-0.5714285714285714</v>
       </c>
       <c r="D1282" t="n">
-        <v>0</v>
+        <v>-0.7</v>
       </c>
       <c r="E1282" t="b">
         <v>1</v>
@@ -23050,7 +23050,7 @@
         <v>-0.5714285714285714</v>
       </c>
       <c r="D1283" t="n">
-        <v>0</v>
+        <v>-0.7</v>
       </c>
       <c r="E1283" t="b">
         <v>0</v>
@@ -23069,7 +23069,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D1284" t="n">
-        <v>-0.1</v>
+        <v>-0.8</v>
       </c>
       <c r="E1284" t="b">
         <v>1</v>
@@ -23088,7 +23088,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1285" t="n">
-        <v>-0.1</v>
+        <v>-0.8</v>
       </c>
       <c r="E1285" t="b">
         <v>1</v>
@@ -23105,7 +23105,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1286" t="n">
-        <v>-0.1</v>
+        <v>-0.8</v>
       </c>
       <c r="E1286" t="b">
         <v>0</v>
@@ -23124,7 +23124,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1287" t="n">
-        <v>-0.1</v>
+        <v>-0.8</v>
       </c>
       <c r="E1287" t="b">
         <v>1</v>
@@ -23141,7 +23141,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1288" t="n">
-        <v>-0.1</v>
+        <v>-0.8</v>
       </c>
       <c r="E1288" t="b">
         <v>0</v>
@@ -23158,7 +23158,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1289" t="n">
-        <v>-0.1</v>
+        <v>-0.8</v>
       </c>
       <c r="E1289" t="b">
         <v>0</v>
@@ -23177,7 +23177,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1290" t="n">
-        <v>-0.1</v>
+        <v>-0.8</v>
       </c>
       <c r="E1290" t="b">
         <v>1</v>
@@ -23196,7 +23196,7 @@
         <v>0</v>
       </c>
       <c r="D1291" t="n">
-        <v>-0.1</v>
+        <v>-0.8</v>
       </c>
       <c r="E1291" t="b">
         <v>1</v>
@@ -23213,7 +23213,7 @@
         <v>0</v>
       </c>
       <c r="D1292" t="n">
-        <v>-0.1</v>
+        <v>-0.7</v>
       </c>
       <c r="E1292" t="b">
         <v>0</v>
@@ -23232,7 +23232,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1293" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E1293" t="b">
         <v>1</v>
@@ -23251,7 +23251,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1294" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E1294" t="b">
         <v>1</v>
@@ -23268,7 +23268,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1295" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="E1295" t="b">
         <v>0</v>
@@ -23287,7 +23287,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1296" t="n">
-        <v>0.06666666666666667</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1296" t="b">
         <v>1</v>
@@ -23306,7 +23306,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1297" t="n">
-        <v>0.1666666666666667</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E1297" t="b">
         <v>1</v>
@@ -23323,7 +23323,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1298" t="n">
-        <v>0.2666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1298" t="b">
         <v>0</v>
@@ -23340,7 +23340,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1299" t="n">
-        <v>0.1666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1299" t="b">
         <v>0</v>
@@ -23357,7 +23357,7 @@
         <v>0</v>
       </c>
       <c r="D1300" t="n">
-        <v>0.06666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1300" t="b">
         <v>0</v>
@@ -23374,7 +23374,7 @@
         <v>0</v>
       </c>
       <c r="D1301" t="n">
-        <v>-0.03333333333333333</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1301" t="b">
         <v>0</v>
@@ -23391,7 +23391,7 @@
         <v>0</v>
       </c>
       <c r="D1302" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1302" t="b">
         <v>0</v>
@@ -23408,7 +23408,7 @@
         <v>0</v>
       </c>
       <c r="D1303" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E1303" t="b">
         <v>0</v>
@@ -24054,13 +24054,13 @@
         </is>
       </c>
       <c r="B1341" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C1341" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D1341" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.1</v>
       </c>
       <c r="E1341" t="b">
         <v>1</v>
@@ -24074,10 +24074,10 @@
       </c>
       <c r="B1342" t="inlineStr"/>
       <c r="C1342" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D1342" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.2</v>
       </c>
       <c r="E1342" t="b">
         <v>0</v>
@@ -24093,10 +24093,10 @@
         <v>0</v>
       </c>
       <c r="C1343" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D1343" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.2</v>
       </c>
       <c r="E1343" t="b">
         <v>1</v>
@@ -24110,10 +24110,10 @@
       </c>
       <c r="B1344" t="inlineStr"/>
       <c r="C1344" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D1344" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.2</v>
       </c>
       <c r="E1344" t="b">
         <v>0</v>
@@ -24129,10 +24129,10 @@
         <v>0</v>
       </c>
       <c r="C1345" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D1345" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.2</v>
       </c>
       <c r="E1345" t="b">
         <v>1</v>
@@ -24146,10 +24146,10 @@
       </c>
       <c r="B1346" t="inlineStr"/>
       <c r="C1346" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D1346" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.2</v>
       </c>
       <c r="E1346" t="b">
         <v>0</v>
@@ -24165,10 +24165,10 @@
         <v>0</v>
       </c>
       <c r="C1347" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D1347" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.2</v>
       </c>
       <c r="E1347" t="b">
         <v>1</v>
@@ -24182,10 +24182,10 @@
       </c>
       <c r="B1348" t="inlineStr"/>
       <c r="C1348" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D1348" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.2</v>
       </c>
       <c r="E1348" t="b">
         <v>0</v>
@@ -24202,7 +24202,7 @@
         <v>0</v>
       </c>
       <c r="D1349" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.2</v>
       </c>
       <c r="E1349" t="b">
         <v>0</v>
@@ -24215,13 +24215,13 @@
         </is>
       </c>
       <c r="B1350" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="C1350" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1350" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.1</v>
       </c>
       <c r="E1350" t="b">
         <v>1</v>
@@ -24235,7 +24235,7 @@
       </c>
       <c r="B1351" t="inlineStr"/>
       <c r="C1351" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1351" t="n">
         <v>0</v>
@@ -24254,7 +24254,7 @@
         <v>-3</v>
       </c>
       <c r="C1352" t="n">
-        <v>-1</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D1352" t="n">
         <v>-0.1</v>
@@ -24273,7 +24273,7 @@
         <v>0</v>
       </c>
       <c r="C1353" t="n">
-        <v>-1</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D1353" t="n">
         <v>-0.1</v>
@@ -24292,7 +24292,7 @@
         <v>0</v>
       </c>
       <c r="C1354" t="n">
-        <v>-1</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D1354" t="n">
         <v>-0.1</v>
@@ -24309,7 +24309,7 @@
       </c>
       <c r="B1355" t="inlineStr"/>
       <c r="C1355" t="n">
-        <v>-1</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D1355" t="n">
         <v>-0.1</v>
@@ -24328,7 +24328,7 @@
         <v>0</v>
       </c>
       <c r="C1356" t="n">
-        <v>-1</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D1356" t="n">
         <v>-0.1</v>
@@ -24347,7 +24347,7 @@
         <v>0</v>
       </c>
       <c r="C1357" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1357" t="n">
         <v>-0.1</v>
@@ -24520,13 +24520,13 @@
         </is>
       </c>
       <c r="B1367" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="C1367" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1367" t="n">
-        <v>-0.03333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E1367" t="b">
         <v>1</v>
@@ -24540,10 +24540,10 @@
       </c>
       <c r="B1368" t="inlineStr"/>
       <c r="C1368" t="n">
-        <v>0.5714285714285714</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1368" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="E1368" t="b">
         <v>0</v>
@@ -24557,10 +24557,10 @@
       </c>
       <c r="B1369" t="inlineStr"/>
       <c r="C1369" t="n">
-        <v>0.8571428571428571</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D1369" t="n">
-        <v>0.1</v>
+        <v>-0.4</v>
       </c>
       <c r="E1369" t="b">
         <v>0</v>
@@ -24574,10 +24574,10 @@
       </c>
       <c r="B1370" t="inlineStr"/>
       <c r="C1370" t="n">
-        <v>1.142857142857143</v>
+        <v>-1.714285714285714</v>
       </c>
       <c r="D1370" t="n">
-        <v>0.1666666666666667</v>
+        <v>-0.5</v>
       </c>
       <c r="E1370" t="b">
         <v>0</v>
@@ -24591,10 +24591,10 @@
       </c>
       <c r="B1371" t="inlineStr"/>
       <c r="C1371" t="n">
-        <v>1.428571428571429</v>
+        <v>-2.142857142857143</v>
       </c>
       <c r="D1371" t="n">
-        <v>0.1666666666666667</v>
+        <v>-0.7</v>
       </c>
       <c r="E1371" t="b">
         <v>0</v>
@@ -24610,10 +24610,10 @@
         <v>0</v>
       </c>
       <c r="C1372" t="n">
-        <v>1.428571428571429</v>
+        <v>-2.142857142857143</v>
       </c>
       <c r="D1372" t="n">
-        <v>0.1</v>
+        <v>-0.8</v>
       </c>
       <c r="E1372" t="b">
         <v>1</v>
@@ -24626,13 +24626,13 @@
         </is>
       </c>
       <c r="B1373" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="C1373" t="n">
-        <v>1.428571428571429</v>
+        <v>-2.571428571428572</v>
       </c>
       <c r="D1373" t="n">
-        <v>0.1</v>
+        <v>-0.9</v>
       </c>
       <c r="E1373" t="b">
         <v>1</v>
@@ -24646,10 +24646,10 @@
       </c>
       <c r="B1374" t="inlineStr"/>
       <c r="C1374" t="n">
-        <v>1.142857142857143</v>
+        <v>-2.571428571428572</v>
       </c>
       <c r="D1374" t="n">
-        <v>0.1</v>
+        <v>-1</v>
       </c>
       <c r="E1374" t="b">
         <v>0</v>
@@ -24665,10 +24665,10 @@
         <v>0</v>
       </c>
       <c r="C1375" t="n">
-        <v>0.8571428571428571</v>
+        <v>-2.142857142857143</v>
       </c>
       <c r="D1375" t="n">
-        <v>0.1</v>
+        <v>-1</v>
       </c>
       <c r="E1375" t="b">
         <v>1</v>
@@ -24684,10 +24684,10 @@
         <v>0</v>
       </c>
       <c r="C1376" t="n">
-        <v>0.5714285714285714</v>
+        <v>-1.714285714285714</v>
       </c>
       <c r="D1376" t="n">
-        <v>0.1</v>
+        <v>-1</v>
       </c>
       <c r="E1376" t="b">
         <v>1</v>
@@ -24700,13 +24700,13 @@
         </is>
       </c>
       <c r="B1377" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="C1377" t="n">
-        <v>-0.1428571428571428</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D1377" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E1377" t="b">
         <v>1</v>
@@ -24723,7 +24723,7 @@
         <v>-0.8571428571428571</v>
       </c>
       <c r="D1378" t="n">
-        <v>-0.1</v>
+        <v>-1</v>
       </c>
       <c r="E1378" t="b">
         <v>0</v>
@@ -24742,7 +24742,7 @@
         <v>-0.8571428571428571</v>
       </c>
       <c r="D1379" t="n">
-        <v>-0.1</v>
+        <v>-1</v>
       </c>
       <c r="E1379" t="b">
         <v>1</v>
@@ -24756,10 +24756,10 @@
       </c>
       <c r="B1380" t="inlineStr"/>
       <c r="C1380" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1380" t="n">
-        <v>-0.03333333333333333</v>
+        <v>-0.9</v>
       </c>
       <c r="E1380" t="b">
         <v>0</v>
@@ -24773,10 +24773,10 @@
       </c>
       <c r="B1381" t="inlineStr"/>
       <c r="C1381" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="D1381" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.8</v>
       </c>
       <c r="E1381" t="b">
         <v>0</v>
@@ -24790,10 +24790,10 @@
       </c>
       <c r="B1382" t="inlineStr"/>
       <c r="C1382" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="D1382" t="n">
-        <v>0.1333333333333333</v>
+        <v>-0.7</v>
       </c>
       <c r="E1382" t="b">
         <v>0</v>
@@ -24809,10 +24809,10 @@
         <v>0</v>
       </c>
       <c r="C1383" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="D1383" t="n">
-        <v>0.1333333333333333</v>
+        <v>-0.7</v>
       </c>
       <c r="E1383" t="b">
         <v>1</v>
@@ -24826,10 +24826,10 @@
       </c>
       <c r="B1384" t="inlineStr"/>
       <c r="C1384" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D1384" t="n">
-        <v>0.1333333333333333</v>
+        <v>-0.7</v>
       </c>
       <c r="E1384" t="b">
         <v>0</v>
@@ -24846,7 +24846,7 @@
         <v>0</v>
       </c>
       <c r="D1385" t="n">
-        <v>0.1333333333333333</v>
+        <v>-0.7</v>
       </c>
       <c r="E1385" t="b">
         <v>0</v>
@@ -24863,7 +24863,7 @@
         <v>0</v>
       </c>
       <c r="D1386" t="n">
-        <v>0.1333333333333333</v>
+        <v>-0.7</v>
       </c>
       <c r="E1386" t="b">
         <v>0</v>
@@ -24876,13 +24876,13 @@
         </is>
       </c>
       <c r="B1387" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="C1387" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D1387" t="n">
-        <v>0.06666666666666667</v>
+        <v>-0.6</v>
       </c>
       <c r="E1387" t="b">
         <v>1</v>
@@ -24898,10 +24898,10 @@
         <v>0</v>
       </c>
       <c r="C1388" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D1388" t="n">
-        <v>0.06666666666666667</v>
+        <v>-0.6</v>
       </c>
       <c r="E1388" t="b">
         <v>1</v>
@@ -24915,10 +24915,10 @@
       </c>
       <c r="B1389" t="inlineStr"/>
       <c r="C1389" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D1389" t="n">
-        <v>0.06666666666666667</v>
+        <v>-0.6</v>
       </c>
       <c r="E1389" t="b">
         <v>0</v>
@@ -24932,10 +24932,10 @@
       </c>
       <c r="B1390" t="inlineStr"/>
       <c r="C1390" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D1390" t="n">
-        <v>0.06666666666666667</v>
+        <v>-0.6</v>
       </c>
       <c r="E1390" t="b">
         <v>0</v>
@@ -24949,10 +24949,10 @@
       </c>
       <c r="B1391" t="inlineStr"/>
       <c r="C1391" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D1391" t="n">
-        <v>0.06666666666666667</v>
+        <v>-0.6</v>
       </c>
       <c r="E1391" t="b">
         <v>0</v>
@@ -24966,10 +24966,10 @@
       </c>
       <c r="B1392" t="inlineStr"/>
       <c r="C1392" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D1392" t="n">
-        <v>0.06666666666666667</v>
+        <v>-0.6</v>
       </c>
       <c r="E1392" t="b">
         <v>0</v>
@@ -24983,10 +24983,10 @@
       </c>
       <c r="B1393" t="inlineStr"/>
       <c r="C1393" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D1393" t="n">
-        <v>0.06666666666666667</v>
+        <v>-0.6</v>
       </c>
       <c r="E1393" t="b">
         <v>0</v>
@@ -24999,13 +24999,13 @@
         </is>
       </c>
       <c r="B1394" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C1394" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1394" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="E1394" t="b">
         <v>1</v>
@@ -25019,10 +25019,10 @@
       </c>
       <c r="B1395" t="inlineStr"/>
       <c r="C1395" t="n">
-        <v>-0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D1395" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.6</v>
       </c>
       <c r="E1395" t="b">
         <v>0</v>
@@ -25036,10 +25036,10 @@
       </c>
       <c r="B1396" t="inlineStr"/>
       <c r="C1396" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="D1396" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.6</v>
       </c>
       <c r="E1396" t="b">
         <v>0</v>
@@ -25053,10 +25053,10 @@
       </c>
       <c r="B1397" t="inlineStr"/>
       <c r="C1397" t="n">
-        <v>-1.142857142857143</v>
+        <v>0</v>
       </c>
       <c r="D1397" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.5</v>
       </c>
       <c r="E1397" t="b">
         <v>0</v>
@@ -25072,10 +25072,10 @@
         <v>0</v>
       </c>
       <c r="C1398" t="n">
-        <v>-1.142857142857143</v>
+        <v>0</v>
       </c>
       <c r="D1398" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E1398" t="b">
         <v>1</v>
@@ -25089,10 +25089,10 @@
       </c>
       <c r="B1399" t="inlineStr"/>
       <c r="C1399" t="n">
-        <v>-1.142857142857143</v>
+        <v>0</v>
       </c>
       <c r="D1399" t="n">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="E1399" t="b">
         <v>0</v>
@@ -25106,10 +25106,10 @@
       </c>
       <c r="B1400" t="inlineStr"/>
       <c r="C1400" t="n">
-        <v>-1.142857142857143</v>
+        <v>0</v>
       </c>
       <c r="D1400" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.2</v>
       </c>
       <c r="E1400" t="b">
         <v>0</v>
@@ -25125,10 +25125,10 @@
         <v>0</v>
       </c>
       <c r="C1401" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="D1401" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.1</v>
       </c>
       <c r="E1401" t="b">
         <v>1</v>
@@ -25142,10 +25142,10 @@
       </c>
       <c r="B1402" t="inlineStr"/>
       <c r="C1402" t="n">
-        <v>-0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D1402" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.1</v>
       </c>
       <c r="E1402" t="b">
         <v>0</v>
@@ -25159,10 +25159,10 @@
       </c>
       <c r="B1403" t="inlineStr"/>
       <c r="C1403" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D1403" t="n">
-        <v>-0.5333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E1403" t="b">
         <v>0</v>
@@ -25179,7 +25179,7 @@
         <v>0</v>
       </c>
       <c r="D1404" t="n">
-        <v>-0.5333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="E1404" t="b">
         <v>0</v>
@@ -25196,7 +25196,7 @@
         <v>0</v>
       </c>
       <c r="D1405" t="n">
-        <v>-0.5333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="E1405" t="b">
         <v>0</v>
@@ -25215,7 +25215,7 @@
         <v>0</v>
       </c>
       <c r="D1406" t="n">
-        <v>-0.5333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="E1406" t="b">
         <v>1</v>
@@ -25232,7 +25232,7 @@
         <v>0</v>
       </c>
       <c r="D1407" t="n">
-        <v>-0.4333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="E1407" t="b">
         <v>0</v>
@@ -25251,7 +25251,7 @@
         <v>0</v>
       </c>
       <c r="D1408" t="n">
-        <v>-0.3333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="E1408" t="b">
         <v>1</v>
@@ -25264,13 +25264,13 @@
         </is>
       </c>
       <c r="B1409" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C1409" t="n">
-        <v>0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D1409" t="n">
-        <v>-0.2333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="E1409" t="b">
         <v>1</v>
@@ -25284,10 +25284,10 @@
       </c>
       <c r="B1410" t="inlineStr"/>
       <c r="C1410" t="n">
-        <v>0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="D1410" t="n">
-        <v>-0.1333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="E1410" t="b">
         <v>0</v>
@@ -25303,10 +25303,10 @@
         <v>0</v>
       </c>
       <c r="C1411" t="n">
-        <v>0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="D1411" t="n">
-        <v>-0.1333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="E1411" t="b">
         <v>1</v>
@@ -25320,10 +25320,10 @@
       </c>
       <c r="B1412" t="inlineStr"/>
       <c r="C1412" t="n">
-        <v>0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="D1412" t="n">
-        <v>-0.1333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="E1412" t="b">
         <v>0</v>
@@ -25339,10 +25339,10 @@
         <v>-2</v>
       </c>
       <c r="C1413" t="n">
-        <v>0.5714285714285714</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1413" t="n">
-        <v>-0.2</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1413" t="b">
         <v>1</v>
@@ -25356,10 +25356,10 @@
       </c>
       <c r="B1414" t="inlineStr"/>
       <c r="C1414" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1414" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E1414" t="b">
         <v>0</v>
@@ -25373,10 +25373,10 @@
       </c>
       <c r="B1415" t="inlineStr"/>
       <c r="C1415" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1415" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.1</v>
       </c>
       <c r="E1415" t="b">
         <v>0</v>
@@ -25392,10 +25392,10 @@
         <v>3</v>
       </c>
       <c r="C1416" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D1416" t="n">
-        <v>-0.2333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E1416" t="b">
         <v>1</v>
@@ -25407,14 +25407,33 @@
           <t>2026-04-09</t>
         </is>
       </c>
-      <c r="B1417" t="inlineStr"/>
+      <c r="B1417" t="n">
+        <v>3</v>
+      </c>
       <c r="C1417" t="n">
         <v>0</v>
       </c>
       <c r="D1417" t="n">
-        <v>-0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1417" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B1418" t="inlineStr"/>
+      <c r="C1418" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="D1418" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E1418" t="b">
         <v>0</v>
       </c>
     </row>
@@ -25448,7 +25467,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-05-25 to 2026-04-09 | Publication days: 478</t>
+          <t>Coverage: 2022-05-25 to 2026-04-10 | Publication days: 479</t>
         </is>
       </c>
     </row>

--- a/data/AU.xlsx
+++ b/data/AU.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1418"/>
+  <dimension ref="A1:E1419"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22669,13 +22669,13 @@
         </is>
       </c>
       <c r="B1262" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
       <c r="C1262" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1262" t="n">
-        <v>-0.1</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1262" t="b">
         <v>1</v>
@@ -22691,10 +22691,10 @@
         <v>-2</v>
       </c>
       <c r="C1263" t="n">
-        <v>-0.7142857142857143</v>
+        <v>0</v>
       </c>
       <c r="D1263" t="n">
-        <v>-0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E1263" t="b">
         <v>1</v>
@@ -22708,10 +22708,10 @@
       </c>
       <c r="B1264" t="inlineStr"/>
       <c r="C1264" t="n">
-        <v>-1</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1264" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1264" t="b">
         <v>0</v>
@@ -22725,10 +22725,10 @@
       </c>
       <c r="B1265" t="inlineStr"/>
       <c r="C1265" t="n">
-        <v>-1.285714285714286</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1265" t="n">
-        <v>-0.3</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1265" t="b">
         <v>0</v>
@@ -22742,10 +22742,10 @@
       </c>
       <c r="B1266" t="inlineStr"/>
       <c r="C1266" t="n">
-        <v>-1.571428571428571</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D1266" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.2</v>
       </c>
       <c r="E1266" t="b">
         <v>0</v>
@@ -22761,10 +22761,10 @@
         <v>-3</v>
       </c>
       <c r="C1267" t="n">
-        <v>-2</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D1267" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.3</v>
       </c>
       <c r="E1267" t="b">
         <v>1</v>
@@ -22778,10 +22778,10 @@
       </c>
       <c r="B1268" t="inlineStr"/>
       <c r="C1268" t="n">
-        <v>-2.428571428571428</v>
+        <v>-1.714285714285714</v>
       </c>
       <c r="D1268" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.4</v>
       </c>
       <c r="E1268" t="b">
         <v>0</v>
@@ -22800,7 +22800,7 @@
         <v>-2</v>
       </c>
       <c r="D1269" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.4</v>
       </c>
       <c r="E1269" t="b">
         <v>1</v>
@@ -22817,7 +22817,7 @@
         <v>-1.714285714285714</v>
       </c>
       <c r="D1270" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.4</v>
       </c>
       <c r="E1270" t="b">
         <v>0</v>
@@ -22834,7 +22834,7 @@
         <v>-1.428571428571429</v>
       </c>
       <c r="D1271" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.4</v>
       </c>
       <c r="E1271" t="b">
         <v>0</v>
@@ -22851,7 +22851,7 @@
         <v>-1.142857142857143</v>
       </c>
       <c r="D1272" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.4</v>
       </c>
       <c r="E1272" t="b">
         <v>0</v>
@@ -22868,7 +22868,7 @@
         <v>-0.8571428571428571</v>
       </c>
       <c r="D1273" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.4</v>
       </c>
       <c r="E1273" t="b">
         <v>0</v>
@@ -22885,7 +22885,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1274" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.4</v>
       </c>
       <c r="E1274" t="b">
         <v>0</v>
@@ -22904,7 +22904,7 @@
         <v>0</v>
       </c>
       <c r="D1275" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.4</v>
       </c>
       <c r="E1275" t="b">
         <v>1</v>
@@ -22923,7 +22923,7 @@
         <v>0</v>
       </c>
       <c r="D1276" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.4</v>
       </c>
       <c r="E1276" t="b">
         <v>1</v>
@@ -22942,7 +22942,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1277" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E1277" t="b">
         <v>1</v>
@@ -22959,7 +22959,7 @@
         <v>-0.5714285714285714</v>
       </c>
       <c r="D1278" t="n">
-        <v>-0.7</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1278" t="b">
         <v>0</v>
@@ -22978,7 +22978,7 @@
         <v>-0.5714285714285714</v>
       </c>
       <c r="D1279" t="n">
-        <v>-0.7</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1279" t="b">
         <v>1</v>
@@ -22997,7 +22997,7 @@
         <v>-0.5714285714285714</v>
       </c>
       <c r="D1280" t="n">
-        <v>-0.7</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1280" t="b">
         <v>1</v>
@@ -23014,7 +23014,7 @@
         <v>-0.5714285714285714</v>
       </c>
       <c r="D1281" t="n">
-        <v>-0.7</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1281" t="b">
         <v>0</v>
@@ -23033,7 +23033,7 @@
         <v>-0.5714285714285714</v>
       </c>
       <c r="D1282" t="n">
-        <v>-0.7</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1282" t="b">
         <v>1</v>
@@ -23050,7 +23050,7 @@
         <v>-0.5714285714285714</v>
       </c>
       <c r="D1283" t="n">
-        <v>-0.7</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E1283" t="b">
         <v>0</v>
@@ -23069,7 +23069,7 @@
         <v>-0.7142857142857143</v>
       </c>
       <c r="D1284" t="n">
-        <v>-0.8</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E1284" t="b">
         <v>1</v>
@@ -23088,7 +23088,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1285" t="n">
-        <v>-0.8</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E1285" t="b">
         <v>1</v>
@@ -23105,7 +23105,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1286" t="n">
-        <v>-0.8</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E1286" t="b">
         <v>0</v>
@@ -23124,7 +23124,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1287" t="n">
-        <v>-0.8</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E1287" t="b">
         <v>1</v>
@@ -23141,7 +23141,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1288" t="n">
-        <v>-0.8</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E1288" t="b">
         <v>0</v>
@@ -23158,7 +23158,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1289" t="n">
-        <v>-0.8</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E1289" t="b">
         <v>0</v>
@@ -23177,7 +23177,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1290" t="n">
-        <v>-0.8</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E1290" t="b">
         <v>1</v>
@@ -23196,7 +23196,7 @@
         <v>0</v>
       </c>
       <c r="D1291" t="n">
-        <v>-0.8</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E1291" t="b">
         <v>1</v>
@@ -24054,13 +24054,13 @@
         </is>
       </c>
       <c r="B1341" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C1341" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1341" t="n">
-        <v>0.1</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1341" t="b">
         <v>1</v>
@@ -24074,10 +24074,10 @@
       </c>
       <c r="B1342" t="inlineStr"/>
       <c r="C1342" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D1342" t="n">
-        <v>0.2</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1342" t="b">
         <v>0</v>
@@ -24093,10 +24093,10 @@
         <v>0</v>
       </c>
       <c r="C1343" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D1343" t="n">
-        <v>0.2</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1343" t="b">
         <v>1</v>
@@ -24110,10 +24110,10 @@
       </c>
       <c r="B1344" t="inlineStr"/>
       <c r="C1344" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D1344" t="n">
-        <v>0.2</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1344" t="b">
         <v>0</v>
@@ -24129,10 +24129,10 @@
         <v>0</v>
       </c>
       <c r="C1345" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D1345" t="n">
-        <v>0.2</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1345" t="b">
         <v>1</v>
@@ -24146,10 +24146,10 @@
       </c>
       <c r="B1346" t="inlineStr"/>
       <c r="C1346" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D1346" t="n">
-        <v>0.2</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1346" t="b">
         <v>0</v>
@@ -24165,10 +24165,10 @@
         <v>0</v>
       </c>
       <c r="C1347" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D1347" t="n">
-        <v>0.2</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1347" t="b">
         <v>1</v>
@@ -24182,10 +24182,10 @@
       </c>
       <c r="B1348" t="inlineStr"/>
       <c r="C1348" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1348" t="n">
-        <v>0.2</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1348" t="b">
         <v>0</v>
@@ -24202,7 +24202,7 @@
         <v>0</v>
       </c>
       <c r="D1349" t="n">
-        <v>0.2</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1349" t="b">
         <v>0</v>
@@ -24215,13 +24215,13 @@
         </is>
       </c>
       <c r="B1350" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="C1350" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D1350" t="n">
-        <v>0.1</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1350" t="b">
         <v>1</v>
@@ -24235,7 +24235,7 @@
       </c>
       <c r="B1351" t="inlineStr"/>
       <c r="C1351" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1351" t="n">
         <v>0</v>
@@ -24254,7 +24254,7 @@
         <v>-3</v>
       </c>
       <c r="C1352" t="n">
-        <v>-1.285714285714286</v>
+        <v>-1</v>
       </c>
       <c r="D1352" t="n">
         <v>-0.1</v>
@@ -24273,7 +24273,7 @@
         <v>0</v>
       </c>
       <c r="C1353" t="n">
-        <v>-1.285714285714286</v>
+        <v>-1</v>
       </c>
       <c r="D1353" t="n">
         <v>-0.1</v>
@@ -24292,7 +24292,7 @@
         <v>0</v>
       </c>
       <c r="C1354" t="n">
-        <v>-1.285714285714286</v>
+        <v>-1</v>
       </c>
       <c r="D1354" t="n">
         <v>-0.1</v>
@@ -24309,7 +24309,7 @@
       </c>
       <c r="B1355" t="inlineStr"/>
       <c r="C1355" t="n">
-        <v>-1.285714285714286</v>
+        <v>-1</v>
       </c>
       <c r="D1355" t="n">
         <v>-0.1</v>
@@ -24328,7 +24328,7 @@
         <v>0</v>
       </c>
       <c r="C1356" t="n">
-        <v>-1.285714285714286</v>
+        <v>-1</v>
       </c>
       <c r="D1356" t="n">
         <v>-0.1</v>
@@ -24347,7 +24347,7 @@
         <v>0</v>
       </c>
       <c r="C1357" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D1357" t="n">
         <v>-0.1</v>
@@ -24520,13 +24520,13 @@
         </is>
       </c>
       <c r="B1367" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
       <c r="C1367" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1367" t="n">
-        <v>-0.2</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E1367" t="b">
         <v>1</v>
@@ -24540,10 +24540,10 @@
       </c>
       <c r="B1368" t="inlineStr"/>
       <c r="C1368" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D1368" t="n">
-        <v>-0.3</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E1368" t="b">
         <v>0</v>
@@ -24557,10 +24557,10 @@
       </c>
       <c r="B1369" t="inlineStr"/>
       <c r="C1369" t="n">
-        <v>-1.285714285714286</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D1369" t="n">
-        <v>-0.4</v>
+        <v>0.1</v>
       </c>
       <c r="E1369" t="b">
         <v>0</v>
@@ -24574,10 +24574,10 @@
       </c>
       <c r="B1370" t="inlineStr"/>
       <c r="C1370" t="n">
-        <v>-1.714285714285714</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="D1370" t="n">
-        <v>-0.5</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E1370" t="b">
         <v>0</v>
@@ -24591,10 +24591,10 @@
       </c>
       <c r="B1371" t="inlineStr"/>
       <c r="C1371" t="n">
-        <v>-2.142857142857143</v>
+        <v>1.428571428571429</v>
       </c>
       <c r="D1371" t="n">
-        <v>-0.7</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E1371" t="b">
         <v>0</v>
@@ -24610,10 +24610,10 @@
         <v>0</v>
       </c>
       <c r="C1372" t="n">
-        <v>-2.142857142857143</v>
+        <v>1.428571428571429</v>
       </c>
       <c r="D1372" t="n">
-        <v>-0.8</v>
+        <v>0.1</v>
       </c>
       <c r="E1372" t="b">
         <v>1</v>
@@ -24626,13 +24626,13 @@
         </is>
       </c>
       <c r="B1373" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="C1373" t="n">
-        <v>-2.571428571428572</v>
+        <v>1.428571428571429</v>
       </c>
       <c r="D1373" t="n">
-        <v>-0.9</v>
+        <v>0.1</v>
       </c>
       <c r="E1373" t="b">
         <v>1</v>
@@ -24646,10 +24646,10 @@
       </c>
       <c r="B1374" t="inlineStr"/>
       <c r="C1374" t="n">
-        <v>-2.571428571428572</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="D1374" t="n">
-        <v>-1</v>
+        <v>0.1</v>
       </c>
       <c r="E1374" t="b">
         <v>0</v>
@@ -24665,10 +24665,10 @@
         <v>0</v>
       </c>
       <c r="C1375" t="n">
-        <v>-2.142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D1375" t="n">
-        <v>-1</v>
+        <v>0.1</v>
       </c>
       <c r="E1375" t="b">
         <v>1</v>
@@ -24684,10 +24684,10 @@
         <v>0</v>
       </c>
       <c r="C1376" t="n">
-        <v>-1.714285714285714</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D1376" t="n">
-        <v>-1</v>
+        <v>0.1</v>
       </c>
       <c r="E1376" t="b">
         <v>1</v>
@@ -24703,10 +24703,10 @@
         <v>0</v>
       </c>
       <c r="C1377" t="n">
-        <v>-1.285714285714286</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1377" t="n">
-        <v>-1</v>
+        <v>0.1</v>
       </c>
       <c r="E1377" t="b">
         <v>1</v>
@@ -24720,10 +24720,10 @@
       </c>
       <c r="B1378" t="inlineStr"/>
       <c r="C1378" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="D1378" t="n">
-        <v>-1</v>
+        <v>0.1</v>
       </c>
       <c r="E1378" t="b">
         <v>0</v>
@@ -24739,10 +24739,10 @@
         <v>0</v>
       </c>
       <c r="C1379" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="D1379" t="n">
-        <v>-1</v>
+        <v>0.1</v>
       </c>
       <c r="E1379" t="b">
         <v>1</v>
@@ -24756,10 +24756,10 @@
       </c>
       <c r="B1380" t="inlineStr"/>
       <c r="C1380" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D1380" t="n">
-        <v>-0.9</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E1380" t="b">
         <v>0</v>
@@ -24776,7 +24776,7 @@
         <v>0</v>
       </c>
       <c r="D1381" t="n">
-        <v>-0.8</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="E1381" t="b">
         <v>0</v>
@@ -24793,7 +24793,7 @@
         <v>0</v>
       </c>
       <c r="D1382" t="n">
-        <v>-0.7</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E1382" t="b">
         <v>0</v>
@@ -24812,7 +24812,7 @@
         <v>0</v>
       </c>
       <c r="D1383" t="n">
-        <v>-0.7</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E1383" t="b">
         <v>1</v>
@@ -24829,7 +24829,7 @@
         <v>0</v>
       </c>
       <c r="D1384" t="n">
-        <v>-0.7</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E1384" t="b">
         <v>0</v>
@@ -24846,7 +24846,7 @@
         <v>0</v>
       </c>
       <c r="D1385" t="n">
-        <v>-0.7</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E1385" t="b">
         <v>0</v>
@@ -24863,7 +24863,7 @@
         <v>0</v>
       </c>
       <c r="D1386" t="n">
-        <v>-0.7</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E1386" t="b">
         <v>0</v>
@@ -24876,13 +24876,13 @@
         </is>
       </c>
       <c r="B1387" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C1387" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1387" t="n">
-        <v>-0.6</v>
+        <v>0.4</v>
       </c>
       <c r="E1387" t="b">
         <v>1</v>
@@ -24898,10 +24898,10 @@
         <v>0</v>
       </c>
       <c r="C1388" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1388" t="n">
-        <v>-0.6</v>
+        <v>0.4</v>
       </c>
       <c r="E1388" t="b">
         <v>1</v>
@@ -24915,10 +24915,10 @@
       </c>
       <c r="B1389" t="inlineStr"/>
       <c r="C1389" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1389" t="n">
-        <v>-0.6</v>
+        <v>0.4</v>
       </c>
       <c r="E1389" t="b">
         <v>0</v>
@@ -24932,10 +24932,10 @@
       </c>
       <c r="B1390" t="inlineStr"/>
       <c r="C1390" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1390" t="n">
-        <v>-0.6</v>
+        <v>0.4</v>
       </c>
       <c r="E1390" t="b">
         <v>0</v>
@@ -24949,10 +24949,10 @@
       </c>
       <c r="B1391" t="inlineStr"/>
       <c r="C1391" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1391" t="n">
-        <v>-0.6</v>
+        <v>0.4</v>
       </c>
       <c r="E1391" t="b">
         <v>0</v>
@@ -24966,10 +24966,10 @@
       </c>
       <c r="B1392" t="inlineStr"/>
       <c r="C1392" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1392" t="n">
-        <v>-0.6</v>
+        <v>0.4</v>
       </c>
       <c r="E1392" t="b">
         <v>0</v>
@@ -24983,10 +24983,10 @@
       </c>
       <c r="B1393" t="inlineStr"/>
       <c r="C1393" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D1393" t="n">
-        <v>-0.6</v>
+        <v>0.4</v>
       </c>
       <c r="E1393" t="b">
         <v>0</v>
@@ -25005,7 +25005,7 @@
         <v>0</v>
       </c>
       <c r="D1394" t="n">
-        <v>-0.6</v>
+        <v>0.4</v>
       </c>
       <c r="E1394" t="b">
         <v>1</v>
@@ -25022,7 +25022,7 @@
         <v>0</v>
       </c>
       <c r="D1395" t="n">
-        <v>-0.6</v>
+        <v>0.4</v>
       </c>
       <c r="E1395" t="b">
         <v>0</v>
@@ -25039,7 +25039,7 @@
         <v>0</v>
       </c>
       <c r="D1396" t="n">
-        <v>-0.6</v>
+        <v>0.4</v>
       </c>
       <c r="E1396" t="b">
         <v>0</v>
@@ -25056,7 +25056,7 @@
         <v>0</v>
       </c>
       <c r="D1397" t="n">
-        <v>-0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E1397" t="b">
         <v>0</v>
@@ -25075,7 +25075,7 @@
         <v>0</v>
       </c>
       <c r="D1398" t="n">
-        <v>-0.4</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="E1398" t="b">
         <v>1</v>
@@ -25092,7 +25092,7 @@
         <v>0</v>
       </c>
       <c r="D1399" t="n">
-        <v>-0.3</v>
+        <v>0.2</v>
       </c>
       <c r="E1399" t="b">
         <v>0</v>
@@ -25109,7 +25109,7 @@
         <v>0</v>
       </c>
       <c r="D1400" t="n">
-        <v>-0.2</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E1400" t="b">
         <v>0</v>
@@ -25128,7 +25128,7 @@
         <v>0</v>
       </c>
       <c r="D1401" t="n">
-        <v>-0.1</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1401" t="b">
         <v>1</v>
@@ -25145,7 +25145,7 @@
         <v>0</v>
       </c>
       <c r="D1402" t="n">
-        <v>-0.1</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1402" t="b">
         <v>0</v>
@@ -25162,7 +25162,7 @@
         <v>0</v>
       </c>
       <c r="D1403" t="n">
-        <v>0</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1403" t="b">
         <v>0</v>
@@ -25179,7 +25179,7 @@
         <v>0</v>
       </c>
       <c r="D1404" t="n">
-        <v>0.1</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1404" t="b">
         <v>0</v>
@@ -25196,7 +25196,7 @@
         <v>0</v>
       </c>
       <c r="D1405" t="n">
-        <v>0.1</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1405" t="b">
         <v>0</v>
@@ -25215,7 +25215,7 @@
         <v>0</v>
       </c>
       <c r="D1406" t="n">
-        <v>0.1</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1406" t="b">
         <v>1</v>
@@ -25232,7 +25232,7 @@
         <v>0</v>
       </c>
       <c r="D1407" t="n">
-        <v>0.1</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1407" t="b">
         <v>0</v>
@@ -25251,7 +25251,7 @@
         <v>0</v>
       </c>
       <c r="D1408" t="n">
-        <v>0.1</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1408" t="b">
         <v>1</v>
@@ -25270,7 +25270,7 @@
         <v>0</v>
       </c>
       <c r="D1409" t="n">
-        <v>0.1</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1409" t="b">
         <v>1</v>
@@ -25287,7 +25287,7 @@
         <v>0</v>
       </c>
       <c r="D1410" t="n">
-        <v>0.1</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1410" t="b">
         <v>0</v>
@@ -25306,7 +25306,7 @@
         <v>0</v>
       </c>
       <c r="D1411" t="n">
-        <v>0.1</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1411" t="b">
         <v>1</v>
@@ -25323,7 +25323,7 @@
         <v>0</v>
       </c>
       <c r="D1412" t="n">
-        <v>0.1</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="E1412" t="b">
         <v>0</v>
@@ -25342,7 +25342,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D1413" t="n">
-        <v>0.03333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E1413" t="b">
         <v>1</v>
@@ -25359,7 +25359,7 @@
         <v>-0.5714285714285714</v>
       </c>
       <c r="D1414" t="n">
-        <v>-0.03333333333333333</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E1414" t="b">
         <v>0</v>
@@ -25376,7 +25376,7 @@
         <v>-0.8571428571428571</v>
       </c>
       <c r="D1415" t="n">
-        <v>-0.1</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E1415" t="b">
         <v>0</v>
@@ -25395,7 +25395,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D1416" t="n">
-        <v>0</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E1416" t="b">
         <v>1</v>
@@ -25434,6 +25434,23 @@
         <v>0.1</v>
       </c>
       <c r="E1418" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B1419" t="inlineStr"/>
+      <c r="C1419" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="D1419" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E1419" t="b">
         <v>0</v>
       </c>
     </row>
@@ -25467,7 +25484,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-05-25 to 2026-04-10 | Publication days: 479</t>
+          <t>Coverage: 2022-05-25 to 2026-04-11 | Publication days: 479</t>
         </is>
       </c>
     </row>

--- a/data/AU.xlsx
+++ b/data/AU.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1419"/>
+  <dimension ref="A1:E1420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -25451,6 +25451,23 @@
         <v>0.2</v>
       </c>
       <c r="E1419" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B1420" t="inlineStr"/>
+      <c r="C1420" t="n">
+        <v>1.571428571428571</v>
+      </c>
+      <c r="D1420" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E1420" t="b">
         <v>0</v>
       </c>
     </row>
@@ -25484,7 +25501,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2022-05-25 to 2026-04-11 | Publication days: 479</t>
+          <t>Coverage: 2022-05-25 to 2026-04-12 | Publication days: 479</t>
         </is>
       </c>
     </row>
